--- a/songs_data.xlsx
+++ b/songs_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y\Desktop\Nagi Live Archives\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{208E3AC1-AD6F-4307-A0DA-039A106AED50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98A5F024-D661-46A6-81C1-DBCC19C661E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{90EDF358-D884-4DF4-A049-DD2596755BAC}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3689" uniqueCount="937">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3690" uniqueCount="937">
   <si>
     <t>配信タイトル</t>
     <rPh sb="0" eb="2">
@@ -21375,6 +21375,9 @@
       <c r="G606" s="6" t="s">
         <v>605</v>
       </c>
+      <c r="H606" s="6" t="s">
+        <v>54</v>
+      </c>
       <c r="I606" s="29">
         <v>3.5185185185185185E-3</v>
       </c>

--- a/songs_data.xlsx
+++ b/songs_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y\Desktop\Nagi Live Archives\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37FE7FFC-0826-4FDC-87D6-5AE93461CD1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59C8758-F6F8-4AB2-AEAF-9AC6A33766EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{90EDF358-D884-4DF4-A049-DD2596755BAC}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{90EDF358-D884-4DF4-A049-DD2596755BAC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3658" uniqueCount="933">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3658" uniqueCount="934">
   <si>
     <t>配信タイトル</t>
     <rPh sb="0" eb="2">
@@ -2350,13 +2350,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>動画</t>
-    <rPh sb="0" eb="2">
-      <t>ドウガ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>リレー</t>
   </si>
   <si>
@@ -3230,6 +3223,17 @@
   </si>
   <si>
     <t>if唯一無二(即興曲)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オリ曲</t>
+    <rPh sb="2" eb="3">
+      <t>キョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カバー</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3778,7 +3782,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -3822,13 +3826,13 @@
         <v>10</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F2" s="22" t="s">
+        <v>680</v>
+      </c>
+      <c r="G2" s="22" t="s">
         <v>681</v>
-      </c>
-      <c r="G2" s="22" t="s">
-        <v>682</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>222</v>
@@ -3837,7 +3841,7 @@
         <v>117</v>
       </c>
       <c r="J2" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -3854,22 +3858,22 @@
         <v>21</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F3" s="22" t="s">
+        <v>682</v>
+      </c>
+      <c r="G3" s="22" t="s">
         <v>683</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="H3" s="22" t="s">
         <v>684</v>
-      </c>
-      <c r="H3" s="22" t="s">
-        <v>685</v>
       </c>
       <c r="I3" s="22" t="s">
         <v>117</v>
       </c>
       <c r="J3" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -3886,22 +3890,22 @@
         <v>22</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F4" s="22" t="s">
+        <v>685</v>
+      </c>
+      <c r="G4" s="22" t="s">
         <v>686</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="H4" s="22" t="s">
         <v>687</v>
-      </c>
-      <c r="H4" s="22" t="s">
-        <v>688</v>
       </c>
       <c r="I4" s="22" t="s">
         <v>117</v>
       </c>
       <c r="J4" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -3918,22 +3922,22 @@
         <v>27</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F5" s="22" t="s">
+        <v>688</v>
+      </c>
+      <c r="G5" s="22" t="s">
         <v>689</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="H5" s="22" t="s">
         <v>690</v>
-      </c>
-      <c r="H5" s="22" t="s">
-        <v>691</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>117</v>
       </c>
       <c r="J5" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -3950,22 +3954,22 @@
         <v>30</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>664</v>
+        <v>933</v>
       </c>
       <c r="F6" s="22" t="s">
+        <v>691</v>
+      </c>
+      <c r="G6" s="22" t="s">
         <v>692</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="H6" s="22" t="s">
         <v>693</v>
       </c>
-      <c r="H6" s="22" t="s">
+      <c r="I6" s="22" t="s">
         <v>694</v>
       </c>
-      <c r="I6" s="22" t="s">
-        <v>695</v>
-      </c>
       <c r="J6" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
@@ -3982,7 +3986,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>6</v>
@@ -4014,13 +4018,13 @@
         <v>28</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F8" s="22" t="s">
+        <v>695</v>
+      </c>
+      <c r="G8" s="22" t="s">
         <v>696</v>
-      </c>
-      <c r="G8" s="22" t="s">
-        <v>697</v>
       </c>
       <c r="H8" s="22" t="s">
         <v>124</v>
@@ -4029,7 +4033,7 @@
         <v>117</v>
       </c>
       <c r="J8" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -4046,13 +4050,13 @@
         <v>11</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F9" s="22" t="s">
+        <v>697</v>
+      </c>
+      <c r="G9" s="22" t="s">
         <v>698</v>
-      </c>
-      <c r="G9" s="22" t="s">
-        <v>699</v>
       </c>
       <c r="H9" s="22" t="s">
         <v>53</v>
@@ -4061,7 +4065,7 @@
         <v>117</v>
       </c>
       <c r="J9" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -4078,13 +4082,13 @@
         <v>4</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F10" s="22" t="s">
+        <v>699</v>
+      </c>
+      <c r="G10" s="22" t="s">
         <v>700</v>
-      </c>
-      <c r="G10" s="22" t="s">
-        <v>701</v>
       </c>
       <c r="H10" s="22" t="s">
         <v>201</v>
@@ -4093,7 +4097,7 @@
         <v>117</v>
       </c>
       <c r="J10" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -4110,22 +4114,22 @@
         <v>24</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>664</v>
+        <v>933</v>
       </c>
       <c r="F11" s="22" t="s">
+        <v>701</v>
+      </c>
+      <c r="G11" s="22" t="s">
         <v>702</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="H11" s="22" t="s">
         <v>703</v>
       </c>
-      <c r="H11" s="22" t="s">
+      <c r="I11" s="22" t="s">
         <v>704</v>
       </c>
-      <c r="I11" s="22" t="s">
-        <v>705</v>
-      </c>
       <c r="J11" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -4142,13 +4146,13 @@
         <v>6</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F12" s="22" t="s">
+        <v>705</v>
+      </c>
+      <c r="G12" s="22" t="s">
         <v>706</v>
-      </c>
-      <c r="G12" s="22" t="s">
-        <v>707</v>
       </c>
       <c r="H12" s="22" t="s">
         <v>111</v>
@@ -4157,7 +4161,7 @@
         <v>117</v>
       </c>
       <c r="J12" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -4174,22 +4178,22 @@
         <v>10</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>664</v>
+        <v>933</v>
       </c>
       <c r="F13" s="22" t="s">
+        <v>707</v>
+      </c>
+      <c r="G13" s="22" t="s">
         <v>708</v>
-      </c>
-      <c r="G13" s="22" t="s">
-        <v>709</v>
       </c>
       <c r="H13" s="22" t="s">
         <v>236</v>
       </c>
       <c r="I13" s="22" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="J13" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -4206,7 +4210,7 @@
         <v>23</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>43</v>
@@ -4238,7 +4242,7 @@
         <v>23</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>43</v>
@@ -4270,7 +4274,7 @@
         <v>23</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>43</v>
@@ -4302,7 +4306,7 @@
         <v>23</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>43</v>
@@ -4334,7 +4338,7 @@
         <v>23</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>43</v>
@@ -4366,7 +4370,7 @@
         <v>23</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>43</v>
@@ -4398,22 +4402,22 @@
         <v>24</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F20" s="22" t="s">
+        <v>710</v>
+      </c>
+      <c r="G20" s="22" t="s">
         <v>711</v>
       </c>
-      <c r="G20" s="22" t="s">
+      <c r="H20" s="22" t="s">
         <v>712</v>
-      </c>
-      <c r="H20" s="22" t="s">
-        <v>713</v>
       </c>
       <c r="I20" s="22" t="s">
         <v>117</v>
       </c>
       <c r="J20" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
@@ -4430,7 +4434,7 @@
         <v>28</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>55</v>
@@ -4462,7 +4466,7 @@
         <v>28</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>55</v>
@@ -4494,7 +4498,7 @@
         <v>28</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>55</v>
@@ -4526,7 +4530,7 @@
         <v>28</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>55</v>
@@ -4558,7 +4562,7 @@
         <v>28</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>55</v>
@@ -4590,7 +4594,7 @@
         <v>28</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>55</v>
@@ -4622,7 +4626,7 @@
         <v>28</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>55</v>
@@ -4654,7 +4658,7 @@
         <v>28</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>55</v>
@@ -4686,7 +4690,7 @@
         <v>28</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>55</v>
@@ -4718,7 +4722,7 @@
         <v>28</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>55</v>
@@ -4750,7 +4754,7 @@
         <v>28</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>55</v>
@@ -4782,7 +4786,7 @@
         <v>28</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>55</v>
@@ -4814,7 +4818,7 @@
         <v>28</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>55</v>
@@ -4846,22 +4850,22 @@
         <v>22</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F34" s="22" t="s">
+        <v>713</v>
+      </c>
+      <c r="G34" s="22" t="s">
         <v>714</v>
       </c>
-      <c r="G34" s="22" t="s">
+      <c r="H34" s="22" t="s">
         <v>715</v>
-      </c>
-      <c r="H34" s="22" t="s">
-        <v>716</v>
       </c>
       <c r="I34" s="22" t="s">
         <v>117</v>
       </c>
       <c r="J34" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -4878,22 +4882,22 @@
         <v>23</v>
       </c>
       <c r="E35" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F35" s="22" t="s">
+        <v>716</v>
+      </c>
+      <c r="G35" s="22" t="s">
         <v>717</v>
       </c>
-      <c r="G35" s="22" t="s">
+      <c r="H35" s="22" t="s">
         <v>718</v>
-      </c>
-      <c r="H35" s="22" t="s">
-        <v>719</v>
       </c>
       <c r="I35" s="22" t="s">
         <v>117</v>
       </c>
       <c r="J35" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -4910,13 +4914,13 @@
         <v>24</v>
       </c>
       <c r="E36" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F36" s="22" t="s">
+        <v>719</v>
+      </c>
+      <c r="G36" s="22" t="s">
         <v>720</v>
-      </c>
-      <c r="G36" s="22" t="s">
-        <v>721</v>
       </c>
       <c r="H36" s="22" t="s">
         <v>189</v>
@@ -4925,7 +4929,7 @@
         <v>117</v>
       </c>
       <c r="J36" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="37" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -4942,22 +4946,22 @@
         <v>1</v>
       </c>
       <c r="E37" s="21" t="s">
-        <v>664</v>
+        <v>933</v>
       </c>
       <c r="F37" s="22" t="s">
+        <v>721</v>
+      </c>
+      <c r="G37" s="22" t="s">
         <v>722</v>
       </c>
-      <c r="G37" s="22" t="s">
+      <c r="H37" s="22" t="s">
         <v>723</v>
       </c>
-      <c r="H37" s="22" t="s">
+      <c r="I37" s="22" t="s">
         <v>724</v>
       </c>
-      <c r="I37" s="22" t="s">
-        <v>725</v>
-      </c>
       <c r="J37" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="38" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -4974,7 +4978,7 @@
         <v>17</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>14</v>
@@ -5006,7 +5010,7 @@
         <v>17</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>14</v>
@@ -5038,7 +5042,7 @@
         <v>17</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>14</v>
@@ -5070,7 +5074,7 @@
         <v>17</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>14</v>
@@ -5102,7 +5106,7 @@
         <v>17</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>14</v>
@@ -5134,7 +5138,7 @@
         <v>17</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>14</v>
@@ -5166,7 +5170,7 @@
         <v>17</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>14</v>
@@ -5198,7 +5202,7 @@
         <v>17</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>14</v>
@@ -5230,7 +5234,7 @@
         <v>17</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>14</v>
@@ -5262,7 +5266,7 @@
         <v>17</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>14</v>
@@ -5294,7 +5298,7 @@
         <v>17</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>14</v>
@@ -5326,7 +5330,7 @@
         <v>17</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>14</v>
@@ -5358,7 +5362,7 @@
         <v>24</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>84</v>
@@ -5390,7 +5394,7 @@
         <v>24</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F51" s="6" t="s">
         <v>84</v>
@@ -5422,7 +5426,7 @@
         <v>24</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>84</v>
@@ -5454,7 +5458,7 @@
         <v>24</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>84</v>
@@ -5486,7 +5490,7 @@
         <v>24</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>84</v>
@@ -5518,7 +5522,7 @@
         <v>24</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>84</v>
@@ -5550,7 +5554,7 @@
         <v>24</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>84</v>
@@ -5582,7 +5586,7 @@
         <v>24</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F57" s="6" t="s">
         <v>84</v>
@@ -5614,7 +5618,7 @@
         <v>24</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>84</v>
@@ -5646,7 +5650,7 @@
         <v>24</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F59" s="6" t="s">
         <v>84</v>
@@ -5678,13 +5682,13 @@
         <v>31</v>
       </c>
       <c r="E60" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F60" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="G60" s="22" t="s">
         <v>726</v>
-      </c>
-      <c r="G60" s="22" t="s">
-        <v>727</v>
       </c>
       <c r="H60" s="22" t="s">
         <v>164</v>
@@ -5693,7 +5697,7 @@
         <v>117</v>
       </c>
       <c r="J60" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -5710,7 +5714,7 @@
         <v>4</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>105</v>
@@ -5742,7 +5746,7 @@
         <v>4</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>105</v>
@@ -5774,7 +5778,7 @@
         <v>4</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>105</v>
@@ -5806,7 +5810,7 @@
         <v>4</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>105</v>
@@ -5838,7 +5842,7 @@
         <v>4</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>105</v>
@@ -5870,7 +5874,7 @@
         <v>4</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>105</v>
@@ -5902,7 +5906,7 @@
         <v>11</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F67" s="6" t="s">
         <v>131</v>
@@ -5934,7 +5938,7 @@
         <v>11</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>131</v>
@@ -5966,7 +5970,7 @@
         <v>11</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F69" s="6" t="s">
         <v>131</v>
@@ -5998,7 +6002,7 @@
         <v>11</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>131</v>
@@ -6030,7 +6034,7 @@
         <v>11</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F71" s="6" t="s">
         <v>131</v>
@@ -6062,7 +6066,7 @@
         <v>11</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>131</v>
@@ -6094,22 +6098,22 @@
         <v>13</v>
       </c>
       <c r="E73" s="21" t="s">
-        <v>664</v>
+        <v>933</v>
       </c>
       <c r="F73" s="22" t="s">
+        <v>727</v>
+      </c>
+      <c r="G73" s="22" t="s">
         <v>728</v>
       </c>
-      <c r="G73" s="22" t="s">
+      <c r="H73" s="22" t="s">
         <v>729</v>
       </c>
-      <c r="H73" s="22" t="s">
+      <c r="I73" s="22" t="s">
         <v>730</v>
       </c>
-      <c r="I73" s="22" t="s">
-        <v>731</v>
-      </c>
       <c r="J73" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="74" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -6126,7 +6130,7 @@
         <v>21</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>132</v>
@@ -6158,7 +6162,7 @@
         <v>21</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>132</v>
@@ -6190,7 +6194,7 @@
         <v>21</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>132</v>
@@ -6222,7 +6226,7 @@
         <v>21</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>132</v>
@@ -6254,7 +6258,7 @@
         <v>21</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>132</v>
@@ -6286,7 +6290,7 @@
         <v>21</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>132</v>
@@ -6318,7 +6322,7 @@
         <v>21</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>132</v>
@@ -6350,7 +6354,7 @@
         <v>21</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>132</v>
@@ -6359,7 +6363,7 @@
         <v>133</v>
       </c>
       <c r="H81" s="30" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="I81" s="4" t="s">
         <v>148</v>
@@ -6382,7 +6386,7 @@
         <v>21</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>132</v>
@@ -6414,7 +6418,7 @@
         <v>21</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>132</v>
@@ -6446,7 +6450,7 @@
         <v>21</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F84" s="4" t="s">
         <v>132</v>
@@ -6478,7 +6482,7 @@
         <v>21</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>132</v>
@@ -6510,7 +6514,7 @@
         <v>21</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>132</v>
@@ -6542,13 +6546,13 @@
         <v>28</v>
       </c>
       <c r="E87" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F87" s="22" t="s">
+        <v>731</v>
+      </c>
+      <c r="G87" s="22" t="s">
         <v>732</v>
-      </c>
-      <c r="G87" s="22" t="s">
-        <v>733</v>
       </c>
       <c r="H87" s="22" t="s">
         <v>188</v>
@@ -6557,7 +6561,7 @@
         <v>117</v>
       </c>
       <c r="J87" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="88" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
@@ -6574,7 +6578,7 @@
         <v>6</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>152</v>
@@ -6606,7 +6610,7 @@
         <v>6</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F89" s="6" t="s">
         <v>152</v>
@@ -6638,7 +6642,7 @@
         <v>6</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>152</v>
@@ -6670,7 +6674,7 @@
         <v>6</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F91" s="6" t="s">
         <v>152</v>
@@ -6702,7 +6706,7 @@
         <v>6</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>152</v>
@@ -6734,7 +6738,7 @@
         <v>6</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F93" s="6" t="s">
         <v>152</v>
@@ -6766,7 +6770,7 @@
         <v>6</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>152</v>
@@ -6798,7 +6802,7 @@
         <v>6</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F95" s="6" t="s">
         <v>152</v>
@@ -6830,7 +6834,7 @@
         <v>6</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>152</v>
@@ -6862,7 +6866,7 @@
         <v>6</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F97" s="6" t="s">
         <v>152</v>
@@ -6894,7 +6898,7 @@
         <v>10</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F98" s="4" t="s">
         <v>175</v>
@@ -6926,7 +6930,7 @@
         <v>10</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>175</v>
@@ -6958,7 +6962,7 @@
         <v>10</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>175</v>
@@ -6990,7 +6994,7 @@
         <v>10</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>175</v>
@@ -7022,7 +7026,7 @@
         <v>10</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>175</v>
@@ -7054,7 +7058,7 @@
         <v>10</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>175</v>
@@ -7086,13 +7090,13 @@
         <v>15</v>
       </c>
       <c r="E104" s="21" t="s">
-        <v>664</v>
+        <v>933</v>
       </c>
       <c r="F104" s="22" t="s">
+        <v>733</v>
+      </c>
+      <c r="G104" s="22" t="s">
         <v>734</v>
-      </c>
-      <c r="G104" s="22" t="s">
-        <v>735</v>
       </c>
       <c r="H104" s="22" t="s">
         <v>444</v>
@@ -7101,7 +7105,7 @@
         <v>445</v>
       </c>
       <c r="J104" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="105" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -7118,22 +7122,22 @@
         <v>25</v>
       </c>
       <c r="E105" s="21" t="s">
-        <v>664</v>
+        <v>933</v>
       </c>
       <c r="F105" s="22" t="s">
+        <v>735</v>
+      </c>
+      <c r="G105" s="22" t="s">
         <v>736</v>
       </c>
-      <c r="G105" s="22" t="s">
+      <c r="H105" s="22" t="s">
         <v>737</v>
       </c>
-      <c r="H105" s="22" t="s">
+      <c r="I105" s="22" t="s">
         <v>738</v>
       </c>
-      <c r="I105" s="22" t="s">
-        <v>739</v>
-      </c>
       <c r="J105" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="106" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -7150,22 +7154,22 @@
         <v>27</v>
       </c>
       <c r="E106" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F106" s="22" t="s">
+        <v>739</v>
+      </c>
+      <c r="G106" s="22" t="s">
         <v>740</v>
       </c>
-      <c r="G106" s="22" t="s">
+      <c r="H106" s="22" t="s">
         <v>741</v>
-      </c>
-      <c r="H106" s="22" t="s">
-        <v>742</v>
       </c>
       <c r="I106" s="22" t="s">
         <v>117</v>
       </c>
       <c r="J106" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="107" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
@@ -7182,13 +7186,13 @@
         <v>3</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F107" s="6" t="s">
         <v>177</v>
       </c>
       <c r="G107" s="6" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H107" s="6" t="s">
         <v>179</v>
@@ -7214,7 +7218,7 @@
         <v>3</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>177</v>
@@ -7246,7 +7250,7 @@
         <v>3</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F109" s="6" t="s">
         <v>177</v>
@@ -7278,7 +7282,7 @@
         <v>3</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>177</v>
@@ -7310,7 +7314,7 @@
         <v>3</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F111" s="6" t="s">
         <v>177</v>
@@ -7342,7 +7346,7 @@
         <v>3</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>177</v>
@@ -7374,7 +7378,7 @@
         <v>3</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F113" s="6" t="s">
         <v>177</v>
@@ -7406,7 +7410,7 @@
         <v>3</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>177</v>
@@ -7438,7 +7442,7 @@
         <v>3</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F115" s="6" t="s">
         <v>177</v>
@@ -7470,7 +7474,7 @@
         <v>3</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>177</v>
@@ -7502,7 +7506,7 @@
         <v>10</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F117" s="4" t="s">
         <v>190</v>
@@ -7534,7 +7538,7 @@
         <v>10</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F118" s="4" t="s">
         <v>190</v>
@@ -7566,7 +7570,7 @@
         <v>10</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F119" s="4" t="s">
         <v>190</v>
@@ -7598,7 +7602,7 @@
         <v>10</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F120" s="4" t="s">
         <v>190</v>
@@ -7630,7 +7634,7 @@
         <v>10</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F121" s="4" t="s">
         <v>190</v>
@@ -7662,7 +7666,7 @@
         <v>10</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F122" s="4" t="s">
         <v>190</v>
@@ -7694,7 +7698,7 @@
         <v>10</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F123" s="4" t="s">
         <v>190</v>
@@ -7726,7 +7730,7 @@
         <v>10</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F124" s="4" t="s">
         <v>190</v>
@@ -7758,7 +7762,7 @@
         <v>10</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F125" s="4" t="s">
         <v>190</v>
@@ -7790,7 +7794,7 @@
         <v>10</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F126" s="4" t="s">
         <v>190</v>
@@ -7822,7 +7826,7 @@
         <v>10</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>190</v>
@@ -7854,22 +7858,22 @@
         <v>12</v>
       </c>
       <c r="E128" s="21" t="s">
-        <v>664</v>
+        <v>933</v>
       </c>
       <c r="F128" s="22" t="s">
+        <v>742</v>
+      </c>
+      <c r="G128" s="22" t="s">
         <v>743</v>
       </c>
-      <c r="G128" s="22" t="s">
+      <c r="H128" s="22" t="s">
         <v>744</v>
       </c>
-      <c r="H128" s="22" t="s">
+      <c r="I128" s="22" t="s">
         <v>745</v>
       </c>
-      <c r="I128" s="22" t="s">
-        <v>746</v>
-      </c>
       <c r="J128" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="129" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
@@ -7886,7 +7890,7 @@
         <v>13</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F129" s="6" t="s">
         <v>207</v>
@@ -7918,7 +7922,7 @@
         <v>13</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>207</v>
@@ -7950,7 +7954,7 @@
         <v>13</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F131" s="6" t="s">
         <v>207</v>
@@ -7982,7 +7986,7 @@
         <v>13</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>207</v>
@@ -8014,7 +8018,7 @@
         <v>13</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F133" s="6" t="s">
         <v>207</v>
@@ -8046,7 +8050,7 @@
         <v>13</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>207</v>
@@ -8078,7 +8082,7 @@
         <v>15</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F135" s="4" t="s">
         <v>216</v>
@@ -8110,7 +8114,7 @@
         <v>15</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F136" s="4" t="s">
         <v>216</v>
@@ -8142,7 +8146,7 @@
         <v>15</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F137" s="4" t="s">
         <v>216</v>
@@ -8174,7 +8178,7 @@
         <v>15</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F138" s="4" t="s">
         <v>216</v>
@@ -8206,7 +8210,7 @@
         <v>15</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F139" s="4" t="s">
         <v>216</v>
@@ -8238,7 +8242,7 @@
         <v>15</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F140" s="4" t="s">
         <v>216</v>
@@ -8270,7 +8274,7 @@
         <v>15</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F141" s="4" t="s">
         <v>216</v>
@@ -8302,7 +8306,7 @@
         <v>15</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F142" s="4" t="s">
         <v>216</v>
@@ -8334,13 +8338,13 @@
         <v>24</v>
       </c>
       <c r="E143" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F143" s="22" t="s">
+        <v>746</v>
+      </c>
+      <c r="G143" s="22" t="s">
         <v>747</v>
-      </c>
-      <c r="G143" s="22" t="s">
-        <v>748</v>
       </c>
       <c r="H143" s="22" t="s">
         <v>237</v>
@@ -8349,7 +8353,7 @@
         <v>662</v>
       </c>
       <c r="J143" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="144" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
@@ -8366,7 +8370,7 @@
         <v>1</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>226</v>
@@ -8398,7 +8402,7 @@
         <v>1</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F145" s="6" t="s">
         <v>226</v>
@@ -8430,7 +8434,7 @@
         <v>1</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>226</v>
@@ -8462,7 +8466,7 @@
         <v>1</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F147" s="6" t="s">
         <v>226</v>
@@ -8494,7 +8498,7 @@
         <v>1</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>226</v>
@@ -8526,7 +8530,7 @@
         <v>1</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F149" s="6" t="s">
         <v>226</v>
@@ -8558,7 +8562,7 @@
         <v>1</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>226</v>
@@ -8590,7 +8594,7 @@
         <v>1</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F151" s="6" t="s">
         <v>226</v>
@@ -8622,7 +8626,7 @@
         <v>1</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>226</v>
@@ -8654,7 +8658,7 @@
         <v>1</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F153" s="6" t="s">
         <v>226</v>
@@ -8686,7 +8690,7 @@
         <v>1</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>226</v>
@@ -8718,7 +8722,7 @@
         <v>1</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F155" s="6" t="s">
         <v>226</v>
@@ -8750,7 +8754,7 @@
         <v>1</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>226</v>
@@ -8782,7 +8786,7 @@
         <v>1</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F157" s="6" t="s">
         <v>226</v>
@@ -8814,7 +8818,7 @@
         <v>1</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>226</v>
@@ -8846,7 +8850,7 @@
         <v>1</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F159" s="6" t="s">
         <v>226</v>
@@ -8878,7 +8882,7 @@
         <v>1</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>226</v>
@@ -8910,7 +8914,7 @@
         <v>8</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F161" s="4" t="s">
         <v>244</v>
@@ -8942,7 +8946,7 @@
         <v>8</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F162" s="4" t="s">
         <v>244</v>
@@ -8974,7 +8978,7 @@
         <v>8</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F163" s="4" t="s">
         <v>244</v>
@@ -9006,7 +9010,7 @@
         <v>8</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F164" s="4" t="s">
         <v>244</v>
@@ -9038,7 +9042,7 @@
         <v>8</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F165" s="4" t="s">
         <v>244</v>
@@ -9070,22 +9074,22 @@
         <v>15</v>
       </c>
       <c r="E166" s="21" t="s">
-        <v>664</v>
+        <v>933</v>
       </c>
       <c r="F166" s="22" t="s">
+        <v>748</v>
+      </c>
+      <c r="G166" s="22" t="s">
         <v>749</v>
-      </c>
-      <c r="G166" s="22" t="s">
-        <v>750</v>
       </c>
       <c r="H166" s="22" t="s">
         <v>76</v>
       </c>
       <c r="I166" s="22" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="J166" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="167" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -9102,13 +9106,13 @@
         <v>29</v>
       </c>
       <c r="E167" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F167" s="22" t="s">
+        <v>750</v>
+      </c>
+      <c r="G167" s="22" t="s">
         <v>751</v>
-      </c>
-      <c r="G167" s="22" t="s">
-        <v>752</v>
       </c>
       <c r="H167" s="22" t="s">
         <v>274</v>
@@ -9117,7 +9121,7 @@
         <v>662</v>
       </c>
       <c r="J167" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="168" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
@@ -9134,7 +9138,7 @@
         <v>9</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>252</v>
@@ -9166,7 +9170,7 @@
         <v>9</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F169" s="6" t="s">
         <v>252</v>
@@ -9198,7 +9202,7 @@
         <v>9</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>252</v>
@@ -9230,7 +9234,7 @@
         <v>9</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F171" s="6" t="s">
         <v>252</v>
@@ -9262,7 +9266,7 @@
         <v>9</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>252</v>
@@ -9294,7 +9298,7 @@
         <v>9</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F173" s="6" t="s">
         <v>252</v>
@@ -9326,7 +9330,7 @@
         <v>9</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>256</v>
@@ -9358,13 +9362,13 @@
         <v>26</v>
       </c>
       <c r="E175" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F175" s="22" t="s">
+        <v>752</v>
+      </c>
+      <c r="G175" s="22" t="s">
         <v>753</v>
-      </c>
-      <c r="G175" s="22" t="s">
-        <v>754</v>
       </c>
       <c r="H175" s="22" t="s">
         <v>265</v>
@@ -9373,7 +9377,7 @@
         <v>117</v>
       </c>
       <c r="J175" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="176" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -9390,22 +9394,22 @@
         <v>28</v>
       </c>
       <c r="E176" s="21" t="s">
-        <v>664</v>
+        <v>933</v>
       </c>
       <c r="F176" s="22" t="s">
+        <v>754</v>
+      </c>
+      <c r="G176" s="22" t="s">
         <v>755</v>
       </c>
-      <c r="G176" s="22" t="s">
+      <c r="H176" s="22" t="s">
         <v>756</v>
       </c>
-      <c r="H176" s="22" t="s">
+      <c r="I176" s="22" t="s">
         <v>757</v>
       </c>
-      <c r="I176" s="22" t="s">
-        <v>758</v>
-      </c>
       <c r="J176" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="177" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -9422,7 +9426,7 @@
         <v>10</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F177" s="4" t="s">
         <v>255</v>
@@ -9454,7 +9458,7 @@
         <v>10</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F178" s="4" t="s">
         <v>255</v>
@@ -9486,7 +9490,7 @@
         <v>10</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F179" s="4" t="s">
         <v>255</v>
@@ -9518,7 +9522,7 @@
         <v>10</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F180" s="4" t="s">
         <v>255</v>
@@ -9550,7 +9554,7 @@
         <v>10</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F181" s="4" t="s">
         <v>255</v>
@@ -9582,7 +9586,7 @@
         <v>10</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F182" s="4" t="s">
         <v>255</v>
@@ -9614,7 +9618,7 @@
         <v>10</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F183" s="4" t="s">
         <v>255</v>
@@ -9646,7 +9650,7 @@
         <v>10</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F184" s="4" t="s">
         <v>255</v>
@@ -9678,7 +9682,7 @@
         <v>10</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F185" s="4" t="s">
         <v>255</v>
@@ -9710,7 +9714,7 @@
         <v>10</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F186" s="4" t="s">
         <v>255</v>
@@ -9742,7 +9746,7 @@
         <v>10</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F187" s="4" t="s">
         <v>255</v>
@@ -9774,7 +9778,7 @@
         <v>10</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F188" s="4" t="s">
         <v>255</v>
@@ -9806,7 +9810,7 @@
         <v>10</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F189" s="4" t="s">
         <v>255</v>
@@ -9838,7 +9842,7 @@
         <v>10</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F190" s="4" t="s">
         <v>255</v>
@@ -9870,7 +9874,7 @@
         <v>13</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F191" s="6" t="s">
         <v>268</v>
@@ -9902,7 +9906,7 @@
         <v>13</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>268</v>
@@ -9934,7 +9938,7 @@
         <v>13</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F193" s="6" t="s">
         <v>268</v>
@@ -9966,7 +9970,7 @@
         <v>13</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>268</v>
@@ -9998,7 +10002,7 @@
         <v>13</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F195" s="6" t="s">
         <v>268</v>
@@ -10030,7 +10034,7 @@
         <v>13</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>268</v>
@@ -10062,7 +10066,7 @@
         <v>13</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F197" s="6" t="s">
         <v>268</v>
@@ -10094,7 +10098,7 @@
         <v>14</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F198" s="4" t="s">
         <v>280</v>
@@ -10126,7 +10130,7 @@
         <v>14</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F199" s="4" t="s">
         <v>280</v>
@@ -10158,7 +10162,7 @@
         <v>14</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F200" s="4" t="s">
         <v>280</v>
@@ -10190,7 +10194,7 @@
         <v>14</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F201" s="4" t="s">
         <v>280</v>
@@ -10222,7 +10226,7 @@
         <v>19</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>289</v>
@@ -10254,7 +10258,7 @@
         <v>19</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F203" s="6" t="s">
         <v>289</v>
@@ -10286,7 +10290,7 @@
         <v>19</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>289</v>
@@ -10318,7 +10322,7 @@
         <v>19</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F205" s="6" t="s">
         <v>289</v>
@@ -10350,7 +10354,7 @@
         <v>19</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>289</v>
@@ -10382,7 +10386,7 @@
         <v>19</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F207" s="6" t="s">
         <v>289</v>
@@ -10414,7 +10418,7 @@
         <v>19</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>289</v>
@@ -10446,7 +10450,7 @@
         <v>19</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F209" s="6" t="s">
         <v>289</v>
@@ -10478,7 +10482,7 @@
         <v>19</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>289</v>
@@ -10510,7 +10514,7 @@
         <v>19</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F211" s="6" t="s">
         <v>289</v>
@@ -10542,7 +10546,7 @@
         <v>19</v>
       </c>
       <c r="E212" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>289</v>
@@ -10574,7 +10578,7 @@
         <v>19</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F213" s="6" t="s">
         <v>289</v>
@@ -10606,7 +10610,7 @@
         <v>27</v>
       </c>
       <c r="E214" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F214" s="13" t="s">
         <v>477</v>
@@ -10638,7 +10642,7 @@
         <v>27</v>
       </c>
       <c r="E215" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F215" s="13" t="s">
         <v>477</v>
@@ -10670,7 +10674,7 @@
         <v>27</v>
       </c>
       <c r="E216" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F216" s="13" t="s">
         <v>477</v>
@@ -10702,7 +10706,7 @@
         <v>27</v>
       </c>
       <c r="E217" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F217" s="13" t="s">
         <v>477</v>
@@ -10734,7 +10738,7 @@
         <v>27</v>
       </c>
       <c r="E218" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F218" s="13" t="s">
         <v>477</v>
@@ -10766,10 +10770,10 @@
         <v>27</v>
       </c>
       <c r="E219" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F219" s="13" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="G219" s="13" t="s">
         <v>479</v>
@@ -10798,22 +10802,22 @@
         <v>28</v>
       </c>
       <c r="E220" s="21" t="s">
-        <v>664</v>
+        <v>933</v>
       </c>
       <c r="F220" s="22" t="s">
+        <v>758</v>
+      </c>
+      <c r="G220" s="22" t="s">
         <v>759</v>
       </c>
-      <c r="G220" s="22" t="s">
+      <c r="H220" s="22" t="s">
         <v>760</v>
-      </c>
-      <c r="H220" s="22" t="s">
-        <v>761</v>
       </c>
       <c r="I220" s="22" t="s">
         <v>662</v>
       </c>
       <c r="J220" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="221" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -10830,7 +10834,7 @@
         <v>31</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F221" s="4" t="s">
         <v>291</v>
@@ -10862,7 +10866,7 @@
         <v>31</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F222" s="4" t="s">
         <v>291</v>
@@ -10894,7 +10898,7 @@
         <v>31</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F223" s="4" t="s">
         <v>291</v>
@@ -10926,7 +10930,7 @@
         <v>31</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F224" s="4" t="s">
         <v>291</v>
@@ -10958,7 +10962,7 @@
         <v>31</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F225" s="4" t="s">
         <v>291</v>
@@ -10990,7 +10994,7 @@
         <v>31</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F226" s="4" t="s">
         <v>291</v>
@@ -11022,7 +11026,7 @@
         <v>31</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F227" s="4" t="s">
         <v>291</v>
@@ -11054,22 +11058,22 @@
         <v>31</v>
       </c>
       <c r="E228" s="21" t="s">
-        <v>664</v>
+        <v>933</v>
       </c>
       <c r="F228" s="22" t="s">
+        <v>761</v>
+      </c>
+      <c r="G228" s="22" t="s">
         <v>762</v>
       </c>
-      <c r="G228" s="22" t="s">
+      <c r="H228" s="22" t="s">
         <v>763</v>
       </c>
-      <c r="H228" s="22" t="s">
+      <c r="I228" s="22" t="s">
         <v>764</v>
       </c>
-      <c r="I228" s="22" t="s">
-        <v>765</v>
-      </c>
       <c r="J228" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="229" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -11086,22 +11090,22 @@
         <v>4</v>
       </c>
       <c r="E229" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F229" s="22" t="s">
+        <v>765</v>
+      </c>
+      <c r="G229" s="22" t="s">
         <v>766</v>
       </c>
-      <c r="G229" s="22" t="s">
+      <c r="H229" s="22" t="s">
         <v>767</v>
       </c>
-      <c r="H229" s="22" t="s">
+      <c r="I229" s="22" t="s">
         <v>768</v>
       </c>
-      <c r="I229" s="22" t="s">
-        <v>769</v>
-      </c>
       <c r="J229" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="230" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
@@ -11118,7 +11122,7 @@
         <v>20</v>
       </c>
       <c r="E230" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F230" s="6" t="s">
         <v>303</v>
@@ -11150,7 +11154,7 @@
         <v>20</v>
       </c>
       <c r="E231" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F231" s="6" t="s">
         <v>303</v>
@@ -11182,7 +11186,7 @@
         <v>20</v>
       </c>
       <c r="E232" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F232" s="6" t="s">
         <v>303</v>
@@ -11214,7 +11218,7 @@
         <v>20</v>
       </c>
       <c r="E233" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F233" s="6" t="s">
         <v>303</v>
@@ -11246,7 +11250,7 @@
         <v>20</v>
       </c>
       <c r="E234" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F234" s="6" t="s">
         <v>303</v>
@@ -11278,7 +11282,7 @@
         <v>20</v>
       </c>
       <c r="E235" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F235" s="6" t="s">
         <v>303</v>
@@ -11310,7 +11314,7 @@
         <v>20</v>
       </c>
       <c r="E236" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F236" s="6" t="s">
         <v>303</v>
@@ -11342,7 +11346,7 @@
         <v>20</v>
       </c>
       <c r="E237" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F237" s="6" t="s">
         <v>303</v>
@@ -11374,7 +11378,7 @@
         <v>20</v>
       </c>
       <c r="E238" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F238" s="6" t="s">
         <v>303</v>
@@ -11406,7 +11410,7 @@
         <v>20</v>
       </c>
       <c r="E239" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F239" s="6" t="s">
         <v>303</v>
@@ -11438,7 +11442,7 @@
         <v>20</v>
       </c>
       <c r="E240" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F240" s="6" t="s">
         <v>303</v>
@@ -11470,7 +11474,7 @@
         <v>20</v>
       </c>
       <c r="E241" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F241" s="6" t="s">
         <v>303</v>
@@ -11502,13 +11506,13 @@
         <v>24</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F242" s="4" t="s">
         <v>329</v>
       </c>
       <c r="G242" s="4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H242" s="4" t="s">
         <v>154</v>
@@ -11534,7 +11538,7 @@
         <v>24</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F243" s="4" t="s">
         <v>329</v>
@@ -11566,7 +11570,7 @@
         <v>24</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F244" s="4" t="s">
         <v>329</v>
@@ -11598,7 +11602,7 @@
         <v>24</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F245" s="4" t="s">
         <v>329</v>
@@ -11630,22 +11634,22 @@
         <v>26</v>
       </c>
       <c r="E246" s="21" t="s">
-        <v>664</v>
+        <v>933</v>
       </c>
       <c r="F246" s="22" t="s">
+        <v>769</v>
+      </c>
+      <c r="G246" s="22" t="s">
         <v>770</v>
       </c>
-      <c r="G246" s="22" t="s">
+      <c r="H246" s="22" t="s">
         <v>771</v>
       </c>
-      <c r="H246" s="22" t="s">
+      <c r="I246" s="22" t="s">
         <v>772</v>
       </c>
-      <c r="I246" s="22" t="s">
-        <v>773</v>
-      </c>
       <c r="J246" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="247" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -11662,22 +11666,22 @@
         <v>26</v>
       </c>
       <c r="E247" s="21" t="s">
-        <v>664</v>
+        <v>933</v>
       </c>
       <c r="F247" s="22" t="s">
+        <v>773</v>
+      </c>
+      <c r="G247" s="22" t="s">
         <v>774</v>
       </c>
-      <c r="G247" s="22" t="s">
+      <c r="H247" s="22" t="s">
         <v>775</v>
       </c>
-      <c r="H247" s="22" t="s">
-        <v>776</v>
-      </c>
       <c r="I247" s="22" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="J247" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="248" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -11694,13 +11698,13 @@
         <v>26</v>
       </c>
       <c r="E248" s="21" t="s">
-        <v>664</v>
+        <v>933</v>
       </c>
       <c r="F248" s="22" t="s">
+        <v>776</v>
+      </c>
+      <c r="G248" s="22" t="s">
         <v>777</v>
-      </c>
-      <c r="G248" s="22" t="s">
-        <v>778</v>
       </c>
       <c r="H248" s="22" t="s">
         <v>529</v>
@@ -11709,7 +11713,7 @@
         <v>534</v>
       </c>
       <c r="J248" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="249" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -11726,22 +11730,22 @@
         <v>27</v>
       </c>
       <c r="E249" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F249" s="22" t="s">
+        <v>778</v>
+      </c>
+      <c r="G249" s="22" t="s">
         <v>779</v>
       </c>
-      <c r="G249" s="22" t="s">
+      <c r="H249" s="22" t="s">
         <v>780</v>
-      </c>
-      <c r="H249" s="22" t="s">
-        <v>781</v>
       </c>
       <c r="I249" s="22" t="s">
         <v>54</v>
       </c>
       <c r="J249" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="250" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -11758,13 +11762,13 @@
         <v>28</v>
       </c>
       <c r="E250" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F250" s="22" t="s">
+        <v>781</v>
+      </c>
+      <c r="G250" s="22" t="s">
         <v>782</v>
-      </c>
-      <c r="G250" s="22" t="s">
-        <v>783</v>
       </c>
       <c r="H250" s="22" t="s">
         <v>634</v>
@@ -11773,7 +11777,7 @@
         <v>54</v>
       </c>
       <c r="J250" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="251" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
@@ -11790,7 +11794,7 @@
         <v>4</v>
       </c>
       <c r="E251" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F251" s="6" t="s">
         <v>331</v>
@@ -11822,7 +11826,7 @@
         <v>4</v>
       </c>
       <c r="E252" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F252" s="6" t="s">
         <v>331</v>
@@ -11854,7 +11858,7 @@
         <v>4</v>
       </c>
       <c r="E253" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F253" s="6" t="s">
         <v>331</v>
@@ -11886,7 +11890,7 @@
         <v>4</v>
       </c>
       <c r="E254" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F254" s="6" t="s">
         <v>331</v>
@@ -11918,7 +11922,7 @@
         <v>4</v>
       </c>
       <c r="E255" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F255" s="6" t="s">
         <v>331</v>
@@ -11950,7 +11954,7 @@
         <v>4</v>
       </c>
       <c r="E256" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F256" s="6" t="s">
         <v>331</v>
@@ -11982,7 +11986,7 @@
         <v>4</v>
       </c>
       <c r="E257" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F257" s="6" t="s">
         <v>331</v>
@@ -12014,7 +12018,7 @@
         <v>4</v>
       </c>
       <c r="E258" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F258" s="6" t="s">
         <v>331</v>
@@ -12046,7 +12050,7 @@
         <v>4</v>
       </c>
       <c r="E259" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F259" s="6" t="s">
         <v>331</v>
@@ -12078,7 +12082,7 @@
         <v>4</v>
       </c>
       <c r="E260" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F260" s="6" t="s">
         <v>331</v>
@@ -12110,7 +12114,7 @@
         <v>4</v>
       </c>
       <c r="E261" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F261" s="6" t="s">
         <v>331</v>
@@ -12142,7 +12146,7 @@
         <v>4</v>
       </c>
       <c r="E262" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F262" s="6" t="s">
         <v>331</v>
@@ -12174,7 +12178,7 @@
         <v>7</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F263" s="4" t="s">
         <v>364</v>
@@ -12206,7 +12210,7 @@
         <v>7</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F264" s="4" t="s">
         <v>346</v>
@@ -12238,7 +12242,7 @@
         <v>7</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F265" s="4" t="s">
         <v>346</v>
@@ -12270,7 +12274,7 @@
         <v>7</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F266" s="4" t="s">
         <v>346</v>
@@ -12302,7 +12306,7 @@
         <v>7</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F267" s="4" t="s">
         <v>346</v>
@@ -12334,7 +12338,7 @@
         <v>7</v>
       </c>
       <c r="E268" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F268" s="4" t="s">
         <v>346</v>
@@ -12366,7 +12370,7 @@
         <v>14</v>
       </c>
       <c r="E269" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F269" s="6" t="s">
         <v>363</v>
@@ -12398,7 +12402,7 @@
         <v>14</v>
       </c>
       <c r="E270" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F270" s="6" t="s">
         <v>349</v>
@@ -12430,7 +12434,7 @@
         <v>14</v>
       </c>
       <c r="E271" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F271" s="6" t="s">
         <v>349</v>
@@ -12462,7 +12466,7 @@
         <v>14</v>
       </c>
       <c r="E272" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F272" s="6" t="s">
         <v>349</v>
@@ -12494,7 +12498,7 @@
         <v>14</v>
       </c>
       <c r="E273" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F273" s="6" t="s">
         <v>349</v>
@@ -12526,7 +12530,7 @@
         <v>14</v>
       </c>
       <c r="E274" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F274" s="6" t="s">
         <v>349</v>
@@ -12558,7 +12562,7 @@
         <v>14</v>
       </c>
       <c r="E275" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F275" s="6" t="s">
         <v>349</v>
@@ -12590,13 +12594,13 @@
         <v>21</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F276" s="4" t="s">
         <v>356</v>
       </c>
       <c r="G276" s="4" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H276" s="4" t="s">
         <v>224</v>
@@ -12622,7 +12626,7 @@
         <v>21</v>
       </c>
       <c r="E277" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F277" s="4" t="s">
         <v>356</v>
@@ -12654,7 +12658,7 @@
         <v>21</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F278" s="4" t="s">
         <v>356</v>
@@ -12686,7 +12690,7 @@
         <v>21</v>
       </c>
       <c r="E279" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F279" s="4" t="s">
         <v>356</v>
@@ -12718,7 +12722,7 @@
         <v>21</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F280" s="4" t="s">
         <v>356</v>
@@ -12750,7 +12754,7 @@
         <v>21</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F281" s="4" t="s">
         <v>356</v>
@@ -12782,7 +12786,7 @@
         <v>21</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F282" s="4" t="s">
         <v>356</v>
@@ -12814,7 +12818,7 @@
         <v>21</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F283" s="4" t="s">
         <v>356</v>
@@ -12846,7 +12850,7 @@
         <v>21</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F284" s="4" t="s">
         <v>356</v>
@@ -12878,7 +12882,7 @@
         <v>21</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F285" s="4" t="s">
         <v>356</v>
@@ -12910,22 +12914,22 @@
         <v>24</v>
       </c>
       <c r="E286" s="21" t="s">
-        <v>664</v>
+        <v>933</v>
       </c>
       <c r="F286" s="22" t="s">
+        <v>785</v>
+      </c>
+      <c r="G286" s="22" t="s">
         <v>786</v>
       </c>
-      <c r="G286" s="22" t="s">
+      <c r="H286" s="22" t="s">
         <v>787</v>
       </c>
-      <c r="H286" s="22" t="s">
+      <c r="I286" s="22" t="s">
         <v>788</v>
       </c>
-      <c r="I286" s="22" t="s">
-        <v>789</v>
-      </c>
       <c r="J286" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="287" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -12942,13 +12946,13 @@
         <v>25</v>
       </c>
       <c r="E287" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F287" s="22" t="s">
+        <v>783</v>
+      </c>
+      <c r="G287" s="22" t="s">
         <v>784</v>
-      </c>
-      <c r="G287" s="22" t="s">
-        <v>785</v>
       </c>
       <c r="H287" s="22" t="s">
         <v>369</v>
@@ -12957,7 +12961,7 @@
         <v>117</v>
       </c>
       <c r="J287" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="288" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -12974,22 +12978,22 @@
         <v>5</v>
       </c>
       <c r="E288" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F288" s="22" t="s">
+        <v>789</v>
+      </c>
+      <c r="G288" s="22" t="s">
         <v>790</v>
       </c>
-      <c r="G288" s="22" t="s">
-        <v>791</v>
-      </c>
       <c r="H288" s="22" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="I288" s="22" t="s">
         <v>117</v>
       </c>
       <c r="J288" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="289" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -13006,22 +13010,22 @@
         <v>10</v>
       </c>
       <c r="E289" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F289" s="22" t="s">
+        <v>791</v>
+      </c>
+      <c r="G289" s="22" t="s">
         <v>792</v>
       </c>
-      <c r="G289" s="22" t="s">
+      <c r="H289" s="22" t="s">
         <v>793</v>
-      </c>
-      <c r="H289" s="22" t="s">
-        <v>794</v>
       </c>
       <c r="I289" s="22" t="s">
         <v>117</v>
       </c>
       <c r="J289" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="290" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
@@ -13038,7 +13042,7 @@
         <v>18</v>
       </c>
       <c r="E290" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F290" s="6" t="s">
         <v>365</v>
@@ -13070,7 +13074,7 @@
         <v>18</v>
       </c>
       <c r="E291" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F291" s="6" t="s">
         <v>365</v>
@@ -13102,7 +13106,7 @@
         <v>18</v>
       </c>
       <c r="E292" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F292" s="6" t="s">
         <v>365</v>
@@ -13134,7 +13138,7 @@
         <v>18</v>
       </c>
       <c r="E293" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F293" s="6" t="s">
         <v>365</v>
@@ -13166,7 +13170,7 @@
         <v>18</v>
       </c>
       <c r="E294" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F294" s="6" t="s">
         <v>365</v>
@@ -13198,7 +13202,7 @@
         <v>18</v>
       </c>
       <c r="E295" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F295" s="6" t="s">
         <v>365</v>
@@ -13230,7 +13234,7 @@
         <v>18</v>
       </c>
       <c r="E296" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F296" s="6" t="s">
         <v>365</v>
@@ -13262,7 +13266,7 @@
         <v>25</v>
       </c>
       <c r="E297" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F297" s="4" t="s">
         <v>372</v>
@@ -13294,7 +13298,7 @@
         <v>25</v>
       </c>
       <c r="E298" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F298" s="4" t="s">
         <v>372</v>
@@ -13326,7 +13330,7 @@
         <v>25</v>
       </c>
       <c r="E299" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F299" s="4" t="s">
         <v>372</v>
@@ -13358,7 +13362,7 @@
         <v>25</v>
       </c>
       <c r="E300" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F300" s="4" t="s">
         <v>372</v>
@@ -13390,7 +13394,7 @@
         <v>25</v>
       </c>
       <c r="E301" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F301" s="4" t="s">
         <v>372</v>
@@ -13422,7 +13426,7 @@
         <v>25</v>
       </c>
       <c r="E302" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F302" s="4" t="s">
         <v>372</v>
@@ -13454,7 +13458,7 @@
         <v>25</v>
       </c>
       <c r="E303" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F303" s="4" t="s">
         <v>372</v>
@@ -13486,7 +13490,7 @@
         <v>25</v>
       </c>
       <c r="E304" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F304" s="4" t="s">
         <v>372</v>
@@ -13518,7 +13522,7 @@
         <v>25</v>
       </c>
       <c r="E305" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F305" s="4" t="s">
         <v>372</v>
@@ -13550,7 +13554,7 @@
         <v>25</v>
       </c>
       <c r="E306" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F306" s="4" t="s">
         <v>372</v>
@@ -13582,7 +13586,7 @@
         <v>25</v>
       </c>
       <c r="E307" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F307" s="4" t="s">
         <v>372</v>
@@ -13614,7 +13618,7 @@
         <v>30</v>
       </c>
       <c r="E308" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F308" s="6" t="s">
         <v>379</v>
@@ -13646,7 +13650,7 @@
         <v>30</v>
       </c>
       <c r="E309" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F309" s="6" t="s">
         <v>379</v>
@@ -13678,7 +13682,7 @@
         <v>30</v>
       </c>
       <c r="E310" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F310" s="6" t="s">
         <v>379</v>
@@ -13710,7 +13714,7 @@
         <v>30</v>
       </c>
       <c r="E311" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F311" s="6" t="s">
         <v>379</v>
@@ -13742,7 +13746,7 @@
         <v>30</v>
       </c>
       <c r="E312" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F312" s="6" t="s">
         <v>379</v>
@@ -13774,7 +13778,7 @@
         <v>30</v>
       </c>
       <c r="E313" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F313" s="6" t="s">
         <v>379</v>
@@ -13806,7 +13810,7 @@
         <v>30</v>
       </c>
       <c r="E314" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F314" s="6" t="s">
         <v>379</v>
@@ -13838,7 +13842,7 @@
         <v>30</v>
       </c>
       <c r="E315" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F315" s="6" t="s">
         <v>379</v>
@@ -13870,7 +13874,7 @@
         <v>30</v>
       </c>
       <c r="E316" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F316" s="6" t="s">
         <v>379</v>
@@ -13902,7 +13906,7 @@
         <v>30</v>
       </c>
       <c r="E317" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F317" s="6" t="s">
         <v>379</v>
@@ -13934,7 +13938,7 @@
         <v>30</v>
       </c>
       <c r="E318" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F318" s="6" t="s">
         <v>379</v>
@@ -13966,22 +13970,22 @@
         <v>30</v>
       </c>
       <c r="E319" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F319" s="22" t="s">
+        <v>794</v>
+      </c>
+      <c r="G319" s="22" t="s">
         <v>795</v>
       </c>
-      <c r="G319" s="22" t="s">
+      <c r="H319" s="22" t="s">
         <v>796</v>
-      </c>
-      <c r="H319" s="22" t="s">
-        <v>797</v>
       </c>
       <c r="I319" s="22" t="s">
         <v>117</v>
       </c>
       <c r="J319" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="320" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -13998,22 +14002,22 @@
         <v>1</v>
       </c>
       <c r="E320" s="21" t="s">
-        <v>664</v>
+        <v>933</v>
       </c>
       <c r="F320" s="22" t="s">
+        <v>797</v>
+      </c>
+      <c r="G320" s="22" t="s">
         <v>798</v>
-      </c>
-      <c r="G320" s="22" t="s">
-        <v>799</v>
       </c>
       <c r="H320" s="22" t="s">
         <v>57</v>
       </c>
       <c r="I320" s="22" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J320" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="321" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -14030,22 +14034,22 @@
         <v>6</v>
       </c>
       <c r="E321" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F321" s="22" t="s">
+        <v>800</v>
+      </c>
+      <c r="G321" s="22" t="s">
         <v>801</v>
       </c>
-      <c r="G321" s="22" t="s">
+      <c r="H321" s="22" t="s">
         <v>802</v>
-      </c>
-      <c r="H321" s="22" t="s">
-        <v>803</v>
       </c>
       <c r="I321" s="22" t="s">
         <v>662</v>
       </c>
       <c r="J321" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="322" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -14062,7 +14066,7 @@
         <v>13</v>
       </c>
       <c r="E322" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F322" s="4" t="s">
         <v>390</v>
@@ -14094,7 +14098,7 @@
         <v>13</v>
       </c>
       <c r="E323" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F323" s="4" t="s">
         <v>390</v>
@@ -14126,7 +14130,7 @@
         <v>13</v>
       </c>
       <c r="E324" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F324" s="4" t="s">
         <v>390</v>
@@ -14158,7 +14162,7 @@
         <v>13</v>
       </c>
       <c r="E325" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F325" s="4" t="s">
         <v>390</v>
@@ -14190,7 +14194,7 @@
         <v>13</v>
       </c>
       <c r="E326" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F326" s="4" t="s">
         <v>390</v>
@@ -14222,7 +14226,7 @@
         <v>13</v>
       </c>
       <c r="E327" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F327" s="4" t="s">
         <v>390</v>
@@ -14254,7 +14258,7 @@
         <v>13</v>
       </c>
       <c r="E328" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F328" s="4" t="s">
         <v>390</v>
@@ -14286,7 +14290,7 @@
         <v>13</v>
       </c>
       <c r="E329" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F329" s="4" t="s">
         <v>390</v>
@@ -14318,7 +14322,7 @@
         <v>13</v>
       </c>
       <c r="E330" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F330" s="4" t="s">
         <v>390</v>
@@ -14350,7 +14354,7 @@
         <v>13</v>
       </c>
       <c r="E331" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F331" s="4" t="s">
         <v>390</v>
@@ -14382,7 +14386,7 @@
         <v>13</v>
       </c>
       <c r="E332" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F332" s="4" t="s">
         <v>390</v>
@@ -14414,7 +14418,7 @@
         <v>13</v>
       </c>
       <c r="E333" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F333" s="4" t="s">
         <v>390</v>
@@ -14446,13 +14450,13 @@
         <v>13</v>
       </c>
       <c r="E334" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F334" s="22" t="s">
+        <v>803</v>
+      </c>
+      <c r="G334" s="22" t="s">
         <v>804</v>
-      </c>
-      <c r="G334" s="22" t="s">
-        <v>805</v>
       </c>
       <c r="H334" s="22" t="s">
         <v>399</v>
@@ -14461,7 +14465,7 @@
         <v>662</v>
       </c>
       <c r="J334" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="335" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
@@ -14478,7 +14482,7 @@
         <v>20</v>
       </c>
       <c r="E335" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F335" s="6" t="s">
         <v>404</v>
@@ -14510,7 +14514,7 @@
         <v>20</v>
       </c>
       <c r="E336" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F336" s="6" t="s">
         <v>404</v>
@@ -14542,7 +14546,7 @@
         <v>20</v>
       </c>
       <c r="E337" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F337" s="6" t="s">
         <v>404</v>
@@ -14574,7 +14578,7 @@
         <v>20</v>
       </c>
       <c r="E338" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F338" s="6" t="s">
         <v>404</v>
@@ -14606,7 +14610,7 @@
         <v>20</v>
       </c>
       <c r="E339" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F339" s="6" t="s">
         <v>404</v>
@@ -14638,7 +14642,7 @@
         <v>20</v>
       </c>
       <c r="E340" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F340" s="6" t="s">
         <v>404</v>
@@ -14670,7 +14674,7 @@
         <v>20</v>
       </c>
       <c r="E341" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F341" s="6" t="s">
         <v>404</v>
@@ -14702,7 +14706,7 @@
         <v>20</v>
       </c>
       <c r="E342" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F342" s="6" t="s">
         <v>404</v>
@@ -14734,7 +14738,7 @@
         <v>20</v>
       </c>
       <c r="E343" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F343" s="6" t="s">
         <v>404</v>
@@ -14766,7 +14770,7 @@
         <v>20</v>
       </c>
       <c r="E344" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F344" s="6" t="s">
         <v>404</v>
@@ -14798,7 +14802,7 @@
         <v>20</v>
       </c>
       <c r="E345" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F345" s="6" t="s">
         <v>404</v>
@@ -14830,7 +14834,7 @@
         <v>20</v>
       </c>
       <c r="E346" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F346" s="6" t="s">
         <v>404</v>
@@ -14862,7 +14866,7 @@
         <v>20</v>
       </c>
       <c r="E347" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F347" s="6" t="s">
         <v>404</v>
@@ -14894,22 +14898,22 @@
         <v>20</v>
       </c>
       <c r="E348" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F348" s="22" t="s">
+        <v>805</v>
+      </c>
+      <c r="G348" s="22" t="s">
         <v>806</v>
       </c>
-      <c r="G348" s="22" t="s">
+      <c r="H348" s="22" t="s">
         <v>807</v>
-      </c>
-      <c r="H348" s="22" t="s">
-        <v>808</v>
       </c>
       <c r="I348" s="22" t="s">
         <v>662</v>
       </c>
       <c r="J348" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="349" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -14926,22 +14930,22 @@
         <v>27</v>
       </c>
       <c r="E349" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F349" s="22" t="s">
+        <v>808</v>
+      </c>
+      <c r="G349" s="22" t="s">
         <v>809</v>
       </c>
-      <c r="G349" s="22" t="s">
+      <c r="H349" s="22" t="s">
         <v>810</v>
-      </c>
-      <c r="H349" s="22" t="s">
-        <v>811</v>
       </c>
       <c r="I349" s="22" t="s">
         <v>662</v>
       </c>
       <c r="J349" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="350" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -14958,22 +14962,22 @@
         <v>30</v>
       </c>
       <c r="E350" s="21" t="s">
-        <v>664</v>
+        <v>933</v>
       </c>
       <c r="F350" s="22" t="s">
+        <v>811</v>
+      </c>
+      <c r="G350" s="22" t="s">
         <v>812</v>
       </c>
-      <c r="G350" s="22" t="s">
+      <c r="H350" s="22" t="s">
         <v>813</v>
-      </c>
-      <c r="H350" s="22" t="s">
-        <v>814</v>
       </c>
       <c r="I350" s="22" t="s">
         <v>202</v>
       </c>
       <c r="J350" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="351" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -14990,22 +14994,22 @@
         <v>4</v>
       </c>
       <c r="E351" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F351" s="22" t="s">
+        <v>814</v>
+      </c>
+      <c r="G351" s="22" t="s">
         <v>815</v>
       </c>
-      <c r="G351" s="22" t="s">
+      <c r="H351" s="22" t="s">
         <v>816</v>
-      </c>
-      <c r="H351" s="22" t="s">
-        <v>817</v>
       </c>
       <c r="I351" s="22" t="s">
         <v>117</v>
       </c>
       <c r="J351" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="352" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -15022,22 +15026,22 @@
         <v>11</v>
       </c>
       <c r="E352" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F352" s="22" t="s">
+        <v>817</v>
+      </c>
+      <c r="G352" s="22" t="s">
         <v>818</v>
       </c>
-      <c r="G352" s="22" t="s">
-        <v>819</v>
-      </c>
       <c r="H352" s="22" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="I352" s="22" t="s">
         <v>117</v>
       </c>
       <c r="J352" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="353" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -15054,13 +15058,13 @@
         <v>18</v>
       </c>
       <c r="E353" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F353" s="22" t="s">
+        <v>819</v>
+      </c>
+      <c r="G353" s="22" t="s">
         <v>820</v>
-      </c>
-      <c r="G353" s="22" t="s">
-        <v>821</v>
       </c>
       <c r="H353" s="22" t="s">
         <v>422</v>
@@ -15069,7 +15073,7 @@
         <v>117</v>
       </c>
       <c r="J353" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="354" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -15086,13 +15090,13 @@
         <v>23</v>
       </c>
       <c r="E354" s="21" t="s">
-        <v>664</v>
+        <v>933</v>
       </c>
       <c r="F354" s="22" t="s">
+        <v>821</v>
+      </c>
+      <c r="G354" s="22" t="s">
         <v>822</v>
-      </c>
-      <c r="G354" s="22" t="s">
-        <v>823</v>
       </c>
       <c r="H354" s="22" t="s">
         <v>170</v>
@@ -15101,7 +15105,7 @@
         <v>97</v>
       </c>
       <c r="J354" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="355" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -15118,7 +15122,7 @@
         <v>29</v>
       </c>
       <c r="E355" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F355" s="4" t="s">
         <v>410</v>
@@ -15127,13 +15131,13 @@
         <v>411</v>
       </c>
       <c r="H355" s="29" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="I355" s="4" t="s">
         <v>54</v>
       </c>
       <c r="J355" s="26" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="356" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.45">
@@ -15150,13 +15154,13 @@
         <v>5</v>
       </c>
       <c r="E356" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F356" s="13" t="s">
         <v>660</v>
       </c>
       <c r="G356" s="13" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H356" s="13" t="s">
         <v>661</v>
@@ -15182,16 +15186,16 @@
         <v>5</v>
       </c>
       <c r="E357" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F357" s="13" t="s">
         <v>660</v>
       </c>
       <c r="G357" s="13" t="s">
+        <v>675</v>
+      </c>
+      <c r="H357" s="13" t="s">
         <v>676</v>
-      </c>
-      <c r="H357" s="13" t="s">
-        <v>677</v>
       </c>
       <c r="I357" s="13" t="s">
         <v>54</v>
@@ -15214,16 +15218,16 @@
         <v>5</v>
       </c>
       <c r="E358" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F358" s="13" t="s">
         <v>660</v>
       </c>
       <c r="G358" s="13" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H358" s="13" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="I358" s="13" t="s">
         <v>54</v>
@@ -15246,16 +15250,16 @@
         <v>5</v>
       </c>
       <c r="E359" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F359" s="13" t="s">
         <v>660</v>
       </c>
       <c r="G359" s="13" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H359" s="13" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="I359" s="13" t="s">
         <v>54</v>
@@ -15278,16 +15282,16 @@
         <v>5</v>
       </c>
       <c r="E360" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F360" s="13" t="s">
         <v>660</v>
       </c>
       <c r="G360" s="13" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H360" s="13" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="I360" s="13" t="s">
         <v>54</v>
@@ -15310,7 +15314,7 @@
         <v>15</v>
       </c>
       <c r="E361" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F361" s="6" t="s">
         <v>412</v>
@@ -15342,7 +15346,7 @@
         <v>15</v>
       </c>
       <c r="E362" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F362" s="6" t="s">
         <v>412</v>
@@ -15374,7 +15378,7 @@
         <v>15</v>
       </c>
       <c r="E363" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F363" s="6" t="s">
         <v>412</v>
@@ -15406,7 +15410,7 @@
         <v>15</v>
       </c>
       <c r="E364" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F364" s="6" t="s">
         <v>412</v>
@@ -15438,7 +15442,7 @@
         <v>15</v>
       </c>
       <c r="E365" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F365" s="6" t="s">
         <v>412</v>
@@ -15470,7 +15474,7 @@
         <v>15</v>
       </c>
       <c r="E366" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F366" s="6" t="s">
         <v>412</v>
@@ -15502,7 +15506,7 @@
         <v>15</v>
       </c>
       <c r="E367" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F367" s="6" t="s">
         <v>412</v>
@@ -15534,7 +15538,7 @@
         <v>15</v>
       </c>
       <c r="E368" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F368" s="6" t="s">
         <v>412</v>
@@ -15566,7 +15570,7 @@
         <v>15</v>
       </c>
       <c r="E369" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F369" s="6" t="s">
         <v>412</v>
@@ -15598,7 +15602,7 @@
         <v>22</v>
       </c>
       <c r="E370" s="10" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F370" s="11" t="s">
         <v>425</v>
@@ -15630,7 +15634,7 @@
         <v>22</v>
       </c>
       <c r="E371" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F371" s="11" t="s">
         <v>425</v>
@@ -15662,7 +15666,7 @@
         <v>22</v>
       </c>
       <c r="E372" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F372" s="11" t="s">
         <v>425</v>
@@ -15694,7 +15698,7 @@
         <v>22</v>
       </c>
       <c r="E373" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F373" s="11" t="s">
         <v>425</v>
@@ -15726,7 +15730,7 @@
         <v>22</v>
       </c>
       <c r="E374" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F374" s="11" t="s">
         <v>425</v>
@@ -15758,7 +15762,7 @@
         <v>22</v>
       </c>
       <c r="E375" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F375" s="11" t="s">
         <v>425</v>
@@ -15790,7 +15794,7 @@
         <v>22</v>
       </c>
       <c r="E376" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F376" s="11" t="s">
         <v>425</v>
@@ -15822,7 +15826,7 @@
         <v>22</v>
       </c>
       <c r="E377" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F377" s="11" t="s">
         <v>425</v>
@@ -15854,7 +15858,7 @@
         <v>22</v>
       </c>
       <c r="E378" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F378" s="11" t="s">
         <v>425</v>
@@ -15886,7 +15890,7 @@
         <v>22</v>
       </c>
       <c r="E379" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F379" s="11" t="s">
         <v>425</v>
@@ -15918,7 +15922,7 @@
         <v>22</v>
       </c>
       <c r="E380" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F380" s="11" t="s">
         <v>425</v>
@@ -15950,13 +15954,13 @@
         <v>29</v>
       </c>
       <c r="E381" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F381" s="22" t="s">
+        <v>823</v>
+      </c>
+      <c r="G381" s="22" t="s">
         <v>824</v>
-      </c>
-      <c r="G381" s="22" t="s">
-        <v>825</v>
       </c>
       <c r="H381" s="22" t="s">
         <v>454</v>
@@ -15965,7 +15969,7 @@
         <v>117</v>
       </c>
       <c r="J381" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="382" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -15982,13 +15986,13 @@
         <v>31</v>
       </c>
       <c r="E382" s="21" t="s">
-        <v>664</v>
+        <v>933</v>
       </c>
       <c r="F382" s="22" t="s">
+        <v>825</v>
+      </c>
+      <c r="G382" s="22" t="s">
         <v>826</v>
-      </c>
-      <c r="G382" s="22" t="s">
-        <v>827</v>
       </c>
       <c r="H382" s="22" t="s">
         <v>68</v>
@@ -15997,7 +16001,7 @@
         <v>69</v>
       </c>
       <c r="J382" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="383" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
@@ -16014,7 +16018,7 @@
         <v>5</v>
       </c>
       <c r="E383" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F383" s="6" t="s">
         <v>433</v>
@@ -16046,7 +16050,7 @@
         <v>5</v>
       </c>
       <c r="E384" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F384" s="6" t="s">
         <v>433</v>
@@ -16078,7 +16082,7 @@
         <v>5</v>
       </c>
       <c r="E385" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F385" s="6" t="s">
         <v>433</v>
@@ -16110,7 +16114,7 @@
         <v>5</v>
       </c>
       <c r="E386" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F386" s="6" t="s">
         <v>433</v>
@@ -16142,7 +16146,7 @@
         <v>5</v>
       </c>
       <c r="E387" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F387" s="6" t="s">
         <v>433</v>
@@ -16174,7 +16178,7 @@
         <v>5</v>
       </c>
       <c r="E388" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F388" s="6" t="s">
         <v>433</v>
@@ -16206,7 +16210,7 @@
         <v>5</v>
       </c>
       <c r="E389" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F389" s="6" t="s">
         <v>433</v>
@@ -16238,7 +16242,7 @@
         <v>5</v>
       </c>
       <c r="E390" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F390" s="6" t="s">
         <v>433</v>
@@ -16270,7 +16274,7 @@
         <v>5</v>
       </c>
       <c r="E391" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F391" s="6" t="s">
         <v>433</v>
@@ -16302,7 +16306,7 @@
         <v>5</v>
       </c>
       <c r="E392" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F392" s="6" t="s">
         <v>433</v>
@@ -16334,7 +16338,7 @@
         <v>5</v>
       </c>
       <c r="E393" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F393" s="6" t="s">
         <v>433</v>
@@ -16366,7 +16370,7 @@
         <v>5</v>
       </c>
       <c r="E394" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F394" s="6" t="s">
         <v>433</v>
@@ -16398,7 +16402,7 @@
         <v>12</v>
       </c>
       <c r="E395" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F395" s="11" t="s">
         <v>442</v>
@@ -16430,7 +16434,7 @@
         <v>12</v>
       </c>
       <c r="E396" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F396" s="11" t="s">
         <v>442</v>
@@ -16462,7 +16466,7 @@
         <v>12</v>
       </c>
       <c r="E397" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F397" s="11" t="s">
         <v>442</v>
@@ -16494,7 +16498,7 @@
         <v>12</v>
       </c>
       <c r="E398" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F398" s="11" t="s">
         <v>442</v>
@@ -16526,7 +16530,7 @@
         <v>12</v>
       </c>
       <c r="E399" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F399" s="11" t="s">
         <v>442</v>
@@ -16558,7 +16562,7 @@
         <v>12</v>
       </c>
       <c r="E400" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F400" s="11" t="s">
         <v>442</v>
@@ -16590,7 +16594,7 @@
         <v>12</v>
       </c>
       <c r="E401" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F401" s="11" t="s">
         <v>442</v>
@@ -16622,7 +16626,7 @@
         <v>12</v>
       </c>
       <c r="E402" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F402" s="11" t="s">
         <v>442</v>
@@ -16654,7 +16658,7 @@
         <v>12</v>
       </c>
       <c r="E403" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F403" s="11" t="s">
         <v>442</v>
@@ -16686,7 +16690,7 @@
         <v>12</v>
       </c>
       <c r="E404" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F404" s="11" t="s">
         <v>442</v>
@@ -16718,7 +16722,7 @@
         <v>12</v>
       </c>
       <c r="E405" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F405" s="11" t="s">
         <v>442</v>
@@ -16750,7 +16754,7 @@
         <v>19</v>
       </c>
       <c r="E406" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F406" s="6" t="s">
         <v>455</v>
@@ -16782,7 +16786,7 @@
         <v>19</v>
       </c>
       <c r="E407" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F407" s="6" t="s">
         <v>455</v>
@@ -16814,7 +16818,7 @@
         <v>19</v>
       </c>
       <c r="E408" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F408" s="6" t="s">
         <v>455</v>
@@ -16846,7 +16850,7 @@
         <v>19</v>
       </c>
       <c r="E409" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F409" s="6" t="s">
         <v>455</v>
@@ -16878,7 +16882,7 @@
         <v>19</v>
       </c>
       <c r="E410" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F410" s="6" t="s">
         <v>455</v>
@@ -16910,7 +16914,7 @@
         <v>19</v>
       </c>
       <c r="E411" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F411" s="6" t="s">
         <v>455</v>
@@ -16942,7 +16946,7 @@
         <v>19</v>
       </c>
       <c r="E412" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F412" s="6" t="s">
         <v>455</v>
@@ -16974,7 +16978,7 @@
         <v>19</v>
       </c>
       <c r="E413" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F413" s="6" t="s">
         <v>455</v>
@@ -17006,7 +17010,7 @@
         <v>19</v>
       </c>
       <c r="E414" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F414" s="6" t="s">
         <v>455</v>
@@ -17038,7 +17042,7 @@
         <v>19</v>
       </c>
       <c r="E415" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F415" s="6" t="s">
         <v>455</v>
@@ -17070,7 +17074,7 @@
         <v>19</v>
       </c>
       <c r="E416" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F416" s="6" t="s">
         <v>455</v>
@@ -17102,7 +17106,7 @@
         <v>19</v>
       </c>
       <c r="E417" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F417" s="6" t="s">
         <v>455</v>
@@ -17134,13 +17138,13 @@
         <v>26</v>
       </c>
       <c r="E418" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F418" s="22" t="s">
+        <v>827</v>
+      </c>
+      <c r="G418" s="22" t="s">
         <v>828</v>
-      </c>
-      <c r="G418" s="22" t="s">
-        <v>829</v>
       </c>
       <c r="H418" s="22" t="s">
         <v>476</v>
@@ -17149,7 +17153,7 @@
         <v>117</v>
       </c>
       <c r="J418" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="419" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -17166,22 +17170,22 @@
         <v>28</v>
       </c>
       <c r="E419" s="21" t="s">
-        <v>664</v>
+        <v>933</v>
       </c>
       <c r="F419" s="22" t="s">
+        <v>829</v>
+      </c>
+      <c r="G419" s="22" t="s">
         <v>830</v>
       </c>
-      <c r="G419" s="22" t="s">
+      <c r="H419" s="22" t="s">
         <v>831</v>
       </c>
-      <c r="H419" s="22" t="s">
+      <c r="I419" s="22" t="s">
         <v>832</v>
       </c>
-      <c r="I419" s="22" t="s">
-        <v>833</v>
-      </c>
       <c r="J419" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="420" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -17198,13 +17202,13 @@
         <v>7</v>
       </c>
       <c r="E420" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F420" s="22" t="s">
+        <v>833</v>
+      </c>
+      <c r="G420" s="22" t="s">
         <v>834</v>
-      </c>
-      <c r="G420" s="22" t="s">
-        <v>835</v>
       </c>
       <c r="H420" s="22" t="s">
         <v>532</v>
@@ -17213,7 +17217,7 @@
         <v>535</v>
       </c>
       <c r="J420" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="421" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -17230,22 +17234,22 @@
         <v>14</v>
       </c>
       <c r="E421" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F421" s="22" t="s">
+        <v>835</v>
+      </c>
+      <c r="G421" s="22" t="s">
         <v>836</v>
       </c>
-      <c r="G421" s="22" t="s">
+      <c r="H421" s="22" t="s">
         <v>837</v>
       </c>
-      <c r="H421" s="22" t="s">
+      <c r="I421" s="22" t="s">
         <v>838</v>
       </c>
-      <c r="I421" s="22" t="s">
-        <v>839</v>
-      </c>
       <c r="J421" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="422" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -17262,22 +17266,22 @@
         <v>21</v>
       </c>
       <c r="E422" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F422" s="22" t="s">
+        <v>839</v>
+      </c>
+      <c r="G422" s="22" t="s">
         <v>840</v>
       </c>
-      <c r="G422" s="22" t="s">
+      <c r="H422" s="22" t="s">
         <v>841</v>
       </c>
-      <c r="H422" s="22" t="s">
+      <c r="I422" s="22" t="s">
         <v>842</v>
       </c>
-      <c r="I422" s="22" t="s">
-        <v>843</v>
-      </c>
       <c r="J422" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="423" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -17294,13 +17298,13 @@
         <v>26</v>
       </c>
       <c r="E423" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F423" s="22" t="s">
+        <v>843</v>
+      </c>
+      <c r="G423" s="22" t="s">
         <v>844</v>
-      </c>
-      <c r="G423" s="22" t="s">
-        <v>845</v>
       </c>
       <c r="H423" s="22" t="s">
         <v>475</v>
@@ -17309,7 +17313,7 @@
         <v>117</v>
       </c>
       <c r="J423" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="424" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -17326,22 +17330,22 @@
         <v>28</v>
       </c>
       <c r="E424" s="21" t="s">
-        <v>664</v>
+        <v>933</v>
       </c>
       <c r="F424" s="22" t="s">
+        <v>845</v>
+      </c>
+      <c r="G424" s="22" t="s">
         <v>846</v>
       </c>
-      <c r="G424" s="22" t="s">
+      <c r="H424" s="22" t="s">
         <v>847</v>
-      </c>
-      <c r="H424" s="22" t="s">
-        <v>848</v>
       </c>
       <c r="I424" s="22" t="s">
         <v>98</v>
       </c>
       <c r="J424" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="425" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.45">
@@ -17358,10 +17362,10 @@
         <v>1</v>
       </c>
       <c r="E425" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F425" s="11" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="G425" s="11" t="s">
         <v>465</v>
@@ -17390,7 +17394,7 @@
         <v>1</v>
       </c>
       <c r="E426" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F426" s="11" t="s">
         <v>464</v>
@@ -17422,7 +17426,7 @@
         <v>1</v>
       </c>
       <c r="E427" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F427" s="11" t="s">
         <v>464</v>
@@ -17454,7 +17458,7 @@
         <v>1</v>
       </c>
       <c r="E428" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F428" s="11" t="s">
         <v>464</v>
@@ -17486,7 +17490,7 @@
         <v>1</v>
       </c>
       <c r="E429" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F429" s="11" t="s">
         <v>464</v>
@@ -17518,7 +17522,7 @@
         <v>1</v>
       </c>
       <c r="E430" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F430" s="11" t="s">
         <v>464</v>
@@ -17550,22 +17554,22 @@
         <v>28</v>
       </c>
       <c r="E431" s="21" t="s">
-        <v>664</v>
+        <v>933</v>
       </c>
       <c r="F431" s="22" t="s">
+        <v>848</v>
+      </c>
+      <c r="G431" s="22" t="s">
         <v>849</v>
       </c>
-      <c r="G431" s="22" t="s">
+      <c r="H431" s="22" t="s">
         <v>850</v>
-      </c>
-      <c r="H431" s="22" t="s">
-        <v>851</v>
       </c>
       <c r="I431" s="22" t="s">
         <v>98</v>
       </c>
       <c r="J431" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="432" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -17582,22 +17586,22 @@
         <v>30</v>
       </c>
       <c r="E432" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F432" s="22" t="s">
+        <v>851</v>
+      </c>
+      <c r="G432" s="22" t="s">
         <v>852</v>
       </c>
-      <c r="G432" s="22" t="s">
+      <c r="H432" s="22" t="s">
         <v>853</v>
-      </c>
-      <c r="H432" s="22" t="s">
-        <v>854</v>
       </c>
       <c r="I432" s="22" t="s">
         <v>54</v>
       </c>
       <c r="J432" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="433" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -17614,22 +17618,22 @@
         <v>28</v>
       </c>
       <c r="E433" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F433" s="22" t="s">
+        <v>854</v>
+      </c>
+      <c r="G433" s="22" t="s">
         <v>855</v>
       </c>
-      <c r="G433" s="22" t="s">
+      <c r="H433" s="22" t="s">
         <v>856</v>
-      </c>
-      <c r="H433" s="22" t="s">
-        <v>857</v>
       </c>
       <c r="I433" s="22" t="s">
         <v>54</v>
       </c>
       <c r="J433" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="434" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -17646,22 +17650,22 @@
         <v>30</v>
       </c>
       <c r="E434" s="21" t="s">
-        <v>664</v>
+        <v>933</v>
       </c>
       <c r="F434" s="22" t="s">
+        <v>857</v>
+      </c>
+      <c r="G434" s="22" t="s">
         <v>858</v>
       </c>
-      <c r="G434" s="22" t="s">
+      <c r="H434" s="22" t="s">
         <v>859</v>
-      </c>
-      <c r="H434" s="22" t="s">
-        <v>860</v>
       </c>
       <c r="I434" s="22" t="s">
         <v>333</v>
       </c>
       <c r="J434" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="435" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -17678,22 +17682,22 @@
         <v>25</v>
       </c>
       <c r="E435" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F435" s="22" t="s">
+        <v>860</v>
+      </c>
+      <c r="G435" s="22" t="s">
         <v>861</v>
       </c>
-      <c r="G435" s="22" t="s">
+      <c r="H435" s="22" t="s">
         <v>862</v>
-      </c>
-      <c r="H435" s="22" t="s">
-        <v>863</v>
       </c>
       <c r="I435" s="22" t="s">
         <v>54</v>
       </c>
       <c r="J435" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="436" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -17710,13 +17714,13 @@
         <v>30</v>
       </c>
       <c r="E436" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F436" s="22" t="s">
+        <v>863</v>
+      </c>
+      <c r="G436" s="22" t="s">
         <v>864</v>
-      </c>
-      <c r="G436" s="22" t="s">
-        <v>865</v>
       </c>
       <c r="H436" s="22" t="s">
         <v>472</v>
@@ -17725,7 +17729,7 @@
         <v>54</v>
       </c>
       <c r="J436" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="437" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -17742,22 +17746,22 @@
         <v>27</v>
       </c>
       <c r="E437" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F437" s="22" t="s">
+        <v>865</v>
+      </c>
+      <c r="G437" s="22" t="s">
         <v>866</v>
       </c>
-      <c r="G437" s="22" t="s">
+      <c r="H437" s="22" t="s">
         <v>867</v>
-      </c>
-      <c r="H437" s="22" t="s">
-        <v>868</v>
       </c>
       <c r="I437" s="22" t="s">
         <v>54</v>
       </c>
       <c r="J437" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="438" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
@@ -17774,7 +17778,7 @@
         <v>3</v>
       </c>
       <c r="E438" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F438" s="6" t="s">
         <v>469</v>
@@ -17783,10 +17787,10 @@
         <v>470</v>
       </c>
       <c r="H438" s="6" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="I438" s="6" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="J438" s="25">
         <v>5.0578703703703706E-3</v>
@@ -17806,7 +17810,7 @@
         <v>3</v>
       </c>
       <c r="E439" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F439" s="6" t="s">
         <v>469</v>
@@ -17815,10 +17819,10 @@
         <v>470</v>
       </c>
       <c r="H439" s="6" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="I439" s="6" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="J439" s="25">
         <v>1.0798611111111111E-2</v>
@@ -17838,7 +17842,7 @@
         <v>3</v>
       </c>
       <c r="E440" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F440" s="6" t="s">
         <v>469</v>
@@ -17847,10 +17851,10 @@
         <v>470</v>
       </c>
       <c r="H440" s="6" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="I440" s="6" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="J440" s="25">
         <v>1.5972222222222221E-2</v>
@@ -17870,7 +17874,7 @@
         <v>3</v>
       </c>
       <c r="E441" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F441" s="6" t="s">
         <v>469</v>
@@ -17879,10 +17883,10 @@
         <v>470</v>
       </c>
       <c r="H441" s="6" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I441" s="6" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="J441" s="25">
         <v>2.2314814814814815E-2</v>
@@ -17902,7 +17906,7 @@
         <v>3</v>
       </c>
       <c r="E442" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F442" s="6" t="s">
         <v>469</v>
@@ -17934,7 +17938,7 @@
         <v>3</v>
       </c>
       <c r="E443" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F443" s="6" t="s">
         <v>469</v>
@@ -17966,7 +17970,7 @@
         <v>3</v>
       </c>
       <c r="E444" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F444" s="6" t="s">
         <v>469</v>
@@ -17998,7 +18002,7 @@
         <v>3</v>
       </c>
       <c r="E445" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F445" s="6" t="s">
         <v>469</v>
@@ -18030,7 +18034,7 @@
         <v>3</v>
       </c>
       <c r="E446" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F446" s="6" t="s">
         <v>469</v>
@@ -18062,7 +18066,7 @@
         <v>3</v>
       </c>
       <c r="E447" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F447" s="6" t="s">
         <v>469</v>
@@ -18071,10 +18075,10 @@
         <v>470</v>
       </c>
       <c r="H447" s="6" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="I447" s="6" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="J447" s="25">
         <v>4.6840277777777779E-2</v>
@@ -18094,7 +18098,7 @@
         <v>3</v>
       </c>
       <c r="E448" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F448" s="6" t="s">
         <v>469</v>
@@ -18126,7 +18130,7 @@
         <v>3</v>
       </c>
       <c r="E449" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F449" s="6" t="s">
         <v>469</v>
@@ -18158,22 +18162,22 @@
         <v>3</v>
       </c>
       <c r="E450" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F450" s="22" t="s">
+        <v>868</v>
+      </c>
+      <c r="G450" s="22" t="s">
         <v>869</v>
       </c>
-      <c r="G450" s="22" t="s">
+      <c r="H450" s="22" t="s">
         <v>870</v>
-      </c>
-      <c r="H450" s="22" t="s">
-        <v>871</v>
       </c>
       <c r="I450" s="22" t="s">
         <v>54</v>
       </c>
       <c r="J450" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="451" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -18190,22 +18194,22 @@
         <v>3</v>
       </c>
       <c r="E451" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F451" s="22" t="s">
+        <v>871</v>
+      </c>
+      <c r="G451" s="22" t="s">
+        <v>873</v>
+      </c>
+      <c r="H451" s="22" t="s">
         <v>872</v>
-      </c>
-      <c r="G451" s="22" t="s">
-        <v>874</v>
-      </c>
-      <c r="H451" s="22" t="s">
-        <v>873</v>
       </c>
       <c r="I451" s="22" t="s">
         <v>54</v>
       </c>
       <c r="J451" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="452" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.45">
@@ -18222,7 +18226,7 @@
         <v>14</v>
       </c>
       <c r="E452" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F452" s="11" t="s">
         <v>483</v>
@@ -18254,7 +18258,7 @@
         <v>14</v>
       </c>
       <c r="E453" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F453" s="11" t="s">
         <v>483</v>
@@ -18286,7 +18290,7 @@
         <v>14</v>
       </c>
       <c r="E454" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F454" s="11" t="s">
         <v>483</v>
@@ -18318,7 +18322,7 @@
         <v>14</v>
       </c>
       <c r="E455" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F455" s="11" t="s">
         <v>483</v>
@@ -18350,7 +18354,7 @@
         <v>14</v>
       </c>
       <c r="E456" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F456" s="11" t="s">
         <v>483</v>
@@ -18359,10 +18363,10 @@
         <v>484</v>
       </c>
       <c r="H456" s="11" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I456" s="11" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="J456" s="28">
         <v>1.2361111111111111E-2</v>
@@ -18382,7 +18386,7 @@
         <v>14</v>
       </c>
       <c r="E457" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F457" s="11" t="s">
         <v>483</v>
@@ -18414,7 +18418,7 @@
         <v>15</v>
       </c>
       <c r="E458" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F458" s="13" t="s">
         <v>500</v>
@@ -18429,7 +18433,7 @@
         <v>54</v>
       </c>
       <c r="J458" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="459" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.45">
@@ -18446,7 +18450,7 @@
         <v>15</v>
       </c>
       <c r="E459" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F459" s="13" t="s">
         <v>500</v>
@@ -18461,7 +18465,7 @@
         <v>54</v>
       </c>
       <c r="J459" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="460" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.45">
@@ -18478,7 +18482,7 @@
         <v>15</v>
       </c>
       <c r="E460" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F460" s="13" t="s">
         <v>500</v>
@@ -18493,7 +18497,7 @@
         <v>54</v>
       </c>
       <c r="J460" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="461" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.45">
@@ -18510,7 +18514,7 @@
         <v>15</v>
       </c>
       <c r="E461" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F461" s="13" t="s">
         <v>500</v>
@@ -18525,7 +18529,7 @@
         <v>54</v>
       </c>
       <c r="J461" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="462" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.45">
@@ -18542,7 +18546,7 @@
         <v>15</v>
       </c>
       <c r="E462" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F462" s="13" t="s">
         <v>500</v>
@@ -18557,7 +18561,7 @@
         <v>54</v>
       </c>
       <c r="J462" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="463" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.45">
@@ -18574,7 +18578,7 @@
         <v>15</v>
       </c>
       <c r="E463" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F463" s="13" t="s">
         <v>500</v>
@@ -18589,7 +18593,7 @@
         <v>54</v>
       </c>
       <c r="J463" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="464" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.45">
@@ -18606,7 +18610,7 @@
         <v>15</v>
       </c>
       <c r="E464" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F464" s="13" t="s">
         <v>500</v>
@@ -18621,7 +18625,7 @@
         <v>54</v>
       </c>
       <c r="J464" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="465" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.45">
@@ -18638,7 +18642,7 @@
         <v>15</v>
       </c>
       <c r="E465" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F465" s="13" t="s">
         <v>500</v>
@@ -18653,7 +18657,7 @@
         <v>54</v>
       </c>
       <c r="J465" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="466" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -18670,13 +18674,13 @@
         <v>24</v>
       </c>
       <c r="E466" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F466" s="22" t="s">
+        <v>874</v>
+      </c>
+      <c r="G466" s="22" t="s">
         <v>875</v>
-      </c>
-      <c r="G466" s="22" t="s">
-        <v>876</v>
       </c>
       <c r="H466" s="22" t="s">
         <v>307</v>
@@ -18685,7 +18689,7 @@
         <v>54</v>
       </c>
       <c r="J466" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="467" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
@@ -18702,7 +18706,7 @@
         <v>29</v>
       </c>
       <c r="E467" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F467" s="6" t="s">
         <v>489</v>
@@ -18734,7 +18738,7 @@
         <v>29</v>
       </c>
       <c r="E468" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F468" s="6" t="s">
         <v>489</v>
@@ -18766,7 +18770,7 @@
         <v>29</v>
       </c>
       <c r="E469" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F469" s="6" t="s">
         <v>489</v>
@@ -18798,7 +18802,7 @@
         <v>29</v>
       </c>
       <c r="E470" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F470" s="6" t="s">
         <v>489</v>
@@ -18830,7 +18834,7 @@
         <v>29</v>
       </c>
       <c r="E471" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F471" s="6" t="s">
         <v>489</v>
@@ -18862,7 +18866,7 @@
         <v>29</v>
       </c>
       <c r="E472" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F472" s="6" t="s">
         <v>489</v>
@@ -18894,7 +18898,7 @@
         <v>29</v>
       </c>
       <c r="E473" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F473" s="6" t="s">
         <v>489</v>
@@ -18926,7 +18930,7 @@
         <v>29</v>
       </c>
       <c r="E474" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F474" s="6" t="s">
         <v>489</v>
@@ -18958,22 +18962,22 @@
         <v>29</v>
       </c>
       <c r="E475" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F475" s="22" t="s">
+        <v>876</v>
+      </c>
+      <c r="G475" s="22" t="s">
         <v>877</v>
       </c>
-      <c r="G475" s="22" t="s">
+      <c r="H475" s="22" t="s">
         <v>878</v>
-      </c>
-      <c r="H475" s="22" t="s">
-        <v>879</v>
       </c>
       <c r="I475" s="22" t="s">
         <v>54</v>
       </c>
       <c r="J475" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="476" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.45">
@@ -18990,13 +18994,13 @@
         <v>5</v>
       </c>
       <c r="E476" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F476" s="11" t="s">
         <v>494</v>
       </c>
       <c r="G476" s="11" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H476" s="11" t="s">
         <v>496</v>
@@ -19022,7 +19026,7 @@
         <v>5</v>
       </c>
       <c r="E477" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F477" s="11" t="s">
         <v>494</v>
@@ -19054,7 +19058,7 @@
         <v>5</v>
       </c>
       <c r="E478" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F478" s="11" t="s">
         <v>494</v>
@@ -19086,7 +19090,7 @@
         <v>5</v>
       </c>
       <c r="E479" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F479" s="11" t="s">
         <v>494</v>
@@ -19118,7 +19122,7 @@
         <v>5</v>
       </c>
       <c r="E480" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F480" s="11" t="s">
         <v>494</v>
@@ -19150,7 +19154,7 @@
         <v>5</v>
       </c>
       <c r="E481" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F481" s="11" t="s">
         <v>494</v>
@@ -19182,7 +19186,7 @@
         <v>5</v>
       </c>
       <c r="E482" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F482" s="11" t="s">
         <v>494</v>
@@ -19214,7 +19218,7 @@
         <v>5</v>
       </c>
       <c r="E483" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F483" s="11" t="s">
         <v>494</v>
@@ -19246,7 +19250,7 @@
         <v>5</v>
       </c>
       <c r="E484" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F484" s="11" t="s">
         <v>494</v>
@@ -19278,7 +19282,7 @@
         <v>5</v>
       </c>
       <c r="E485" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F485" s="11" t="s">
         <v>494</v>
@@ -19310,7 +19314,7 @@
         <v>5</v>
       </c>
       <c r="E486" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F486" s="11" t="s">
         <v>494</v>
@@ -19342,7 +19346,7 @@
         <v>5</v>
       </c>
       <c r="E487" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F487" s="11" t="s">
         <v>494</v>
@@ -19374,7 +19378,7 @@
         <v>5</v>
       </c>
       <c r="E488" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F488" s="11" t="s">
         <v>494</v>
@@ -19406,7 +19410,7 @@
         <v>15</v>
       </c>
       <c r="E489" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F489" s="6" t="s">
         <v>501</v>
@@ -19438,7 +19442,7 @@
         <v>15</v>
       </c>
       <c r="E490" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F490" s="6" t="s">
         <v>501</v>
@@ -19470,7 +19474,7 @@
         <v>15</v>
       </c>
       <c r="E491" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F491" s="6" t="s">
         <v>501</v>
@@ -19502,7 +19506,7 @@
         <v>15</v>
       </c>
       <c r="E492" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F492" s="6" t="s">
         <v>501</v>
@@ -19534,7 +19538,7 @@
         <v>15</v>
       </c>
       <c r="E493" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F493" s="6" t="s">
         <v>501</v>
@@ -19566,7 +19570,7 @@
         <v>15</v>
       </c>
       <c r="E494" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F494" s="6" t="s">
         <v>501</v>
@@ -19598,13 +19602,13 @@
         <v>24</v>
       </c>
       <c r="E495" s="21" t="s">
-        <v>664</v>
+        <v>933</v>
       </c>
       <c r="F495" s="22" t="s">
+        <v>879</v>
+      </c>
+      <c r="G495" s="22" t="s">
         <v>880</v>
-      </c>
-      <c r="G495" s="22" t="s">
-        <v>881</v>
       </c>
       <c r="H495" s="22" t="s">
         <v>52</v>
@@ -19613,7 +19617,7 @@
         <v>46</v>
       </c>
       <c r="J495" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="496" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -19630,7 +19634,7 @@
         <v>26</v>
       </c>
       <c r="E496" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F496" s="4" t="s">
         <v>505</v>
@@ -19662,7 +19666,7 @@
         <v>26</v>
       </c>
       <c r="E497" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F497" s="4" t="s">
         <v>505</v>
@@ -19694,7 +19698,7 @@
         <v>26</v>
       </c>
       <c r="E498" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F498" s="4" t="s">
         <v>505</v>
@@ -19726,7 +19730,7 @@
         <v>26</v>
       </c>
       <c r="E499" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F499" s="4" t="s">
         <v>505</v>
@@ -19758,13 +19762,13 @@
         <v>26</v>
       </c>
       <c r="E500" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F500" s="22" t="s">
+        <v>881</v>
+      </c>
+      <c r="G500" s="22" t="s">
         <v>882</v>
-      </c>
-      <c r="G500" s="22" t="s">
-        <v>883</v>
       </c>
       <c r="H500" s="22" t="s">
         <v>541</v>
@@ -19773,7 +19777,7 @@
         <v>54</v>
       </c>
       <c r="J500" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="501" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
@@ -19790,7 +19794,7 @@
         <v>6</v>
       </c>
       <c r="E501" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F501" s="6" t="s">
         <v>510</v>
@@ -19822,7 +19826,7 @@
         <v>6</v>
       </c>
       <c r="E502" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F502" s="6" t="s">
         <v>510</v>
@@ -19854,7 +19858,7 @@
         <v>6</v>
       </c>
       <c r="E503" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F503" s="6" t="s">
         <v>510</v>
@@ -19886,7 +19890,7 @@
         <v>6</v>
       </c>
       <c r="E504" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F504" s="6" t="s">
         <v>510</v>
@@ -19918,7 +19922,7 @@
         <v>6</v>
       </c>
       <c r="E505" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F505" s="6" t="s">
         <v>510</v>
@@ -19950,7 +19954,7 @@
         <v>6</v>
       </c>
       <c r="E506" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F506" s="6" t="s">
         <v>510</v>
@@ -19982,7 +19986,7 @@
         <v>6</v>
       </c>
       <c r="E507" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F507" s="6" t="s">
         <v>510</v>
@@ -20014,7 +20018,7 @@
         <v>6</v>
       </c>
       <c r="E508" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F508" s="6" t="s">
         <v>510</v>
@@ -20046,7 +20050,7 @@
         <v>22</v>
       </c>
       <c r="E509" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F509" s="4" t="s">
         <v>516</v>
@@ -20078,7 +20082,7 @@
         <v>22</v>
       </c>
       <c r="E510" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F510" s="4" t="s">
         <v>516</v>
@@ -20110,22 +20114,22 @@
         <v>27</v>
       </c>
       <c r="E511" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F511" s="6" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="G511" s="6" t="s">
         <v>519</v>
       </c>
       <c r="H511" s="14" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="I511" s="6" t="s">
         <v>54</v>
       </c>
       <c r="J511" s="25" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="512" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -20142,13 +20146,13 @@
         <v>27</v>
       </c>
       <c r="E512" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F512" s="22" t="s">
+        <v>883</v>
+      </c>
+      <c r="G512" s="22" t="s">
         <v>884</v>
-      </c>
-      <c r="G512" s="22" t="s">
-        <v>885</v>
       </c>
       <c r="H512" s="22" t="s">
         <v>542</v>
@@ -20157,7 +20161,7 @@
         <v>54</v>
       </c>
       <c r="J512" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="513" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -20174,7 +20178,7 @@
         <v>1</v>
       </c>
       <c r="E513" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F513" s="4" t="s">
         <v>520</v>
@@ -20206,7 +20210,7 @@
         <v>1</v>
       </c>
       <c r="E514" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F514" s="4" t="s">
         <v>520</v>
@@ -20238,7 +20242,7 @@
         <v>1</v>
       </c>
       <c r="E515" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F515" s="4" t="s">
         <v>520</v>
@@ -20270,7 +20274,7 @@
         <v>1</v>
       </c>
       <c r="E516" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F516" s="4" t="s">
         <v>520</v>
@@ -20302,7 +20306,7 @@
         <v>1</v>
       </c>
       <c r="E517" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F517" s="4" t="s">
         <v>520</v>
@@ -20334,7 +20338,7 @@
         <v>1</v>
       </c>
       <c r="E518" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F518" s="4" t="s">
         <v>520</v>
@@ -20366,7 +20370,7 @@
         <v>1</v>
       </c>
       <c r="E519" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F519" s="4" t="s">
         <v>520</v>
@@ -20398,7 +20402,7 @@
         <v>1</v>
       </c>
       <c r="E520" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F520" s="4" t="s">
         <v>520</v>
@@ -20430,7 +20434,7 @@
         <v>1</v>
       </c>
       <c r="E521" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F521" s="4" t="s">
         <v>520</v>
@@ -20442,7 +20446,7 @@
         <v>498</v>
       </c>
       <c r="I521" s="4" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="J521" s="26">
         <v>5.4837962962962963E-2</v>
@@ -20462,7 +20466,7 @@
         <v>1</v>
       </c>
       <c r="E522" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F522" s="4" t="s">
         <v>520</v>
@@ -20494,7 +20498,7 @@
         <v>1</v>
       </c>
       <c r="E523" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F523" s="4" t="s">
         <v>520</v>
@@ -20526,7 +20530,7 @@
         <v>1</v>
       </c>
       <c r="E524" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F524" s="4" t="s">
         <v>520</v>
@@ -20558,7 +20562,7 @@
         <v>1</v>
       </c>
       <c r="E525" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F525" s="4" t="s">
         <v>520</v>
@@ -20590,7 +20594,7 @@
         <v>1</v>
       </c>
       <c r="E526" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F526" s="4" t="s">
         <v>520</v>
@@ -20622,7 +20626,7 @@
         <v>1</v>
       </c>
       <c r="E527" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F527" s="4" t="s">
         <v>520</v>
@@ -20654,7 +20658,7 @@
         <v>1</v>
       </c>
       <c r="E528" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F528" s="4" t="s">
         <v>520</v>
@@ -20686,7 +20690,7 @@
         <v>1</v>
       </c>
       <c r="E529" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F529" s="4" t="s">
         <v>520</v>
@@ -20718,7 +20722,7 @@
         <v>7</v>
       </c>
       <c r="E530" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F530" s="6" t="s">
         <v>536</v>
@@ -20750,7 +20754,7 @@
         <v>7</v>
       </c>
       <c r="E531" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F531" s="6" t="s">
         <v>536</v>
@@ -20782,7 +20786,7 @@
         <v>7</v>
       </c>
       <c r="E532" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F532" s="6" t="s">
         <v>536</v>
@@ -20814,7 +20818,7 @@
         <v>7</v>
       </c>
       <c r="E533" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F533" s="6" t="s">
         <v>536</v>
@@ -20846,7 +20850,7 @@
         <v>7</v>
       </c>
       <c r="E534" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F534" s="6" t="s">
         <v>536</v>
@@ -20878,7 +20882,7 @@
         <v>7</v>
       </c>
       <c r="E535" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F535" s="6" t="s">
         <v>536</v>
@@ -20910,7 +20914,7 @@
         <v>7</v>
       </c>
       <c r="E536" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F536" s="6" t="s">
         <v>536</v>
@@ -20942,7 +20946,7 @@
         <v>7</v>
       </c>
       <c r="E537" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F537" s="6" t="s">
         <v>536</v>
@@ -20974,7 +20978,7 @@
         <v>7</v>
       </c>
       <c r="E538" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F538" s="6" t="s">
         <v>536</v>
@@ -21006,7 +21010,7 @@
         <v>7</v>
       </c>
       <c r="E539" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F539" s="6" t="s">
         <v>536</v>
@@ -21038,7 +21042,7 @@
         <v>7</v>
       </c>
       <c r="E540" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F540" s="6" t="s">
         <v>536</v>
@@ -21070,22 +21074,22 @@
         <v>21</v>
       </c>
       <c r="E541" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F541" s="22" t="s">
+        <v>886</v>
+      </c>
+      <c r="G541" s="22" t="s">
+        <v>885</v>
+      </c>
+      <c r="H541" s="22" t="s">
         <v>887</v>
-      </c>
-      <c r="G541" s="22" t="s">
-        <v>886</v>
-      </c>
-      <c r="H541" s="22" t="s">
-        <v>888</v>
       </c>
       <c r="I541" s="22" t="s">
         <v>54</v>
       </c>
       <c r="J541" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="542" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -21102,22 +21106,22 @@
         <v>28</v>
       </c>
       <c r="E542" s="21" t="s">
-        <v>664</v>
+        <v>933</v>
       </c>
       <c r="F542" s="22" t="s">
+        <v>888</v>
+      </c>
+      <c r="G542" s="22" t="s">
         <v>889</v>
       </c>
-      <c r="G542" s="22" t="s">
+      <c r="H542" s="23" t="s">
         <v>890</v>
-      </c>
-      <c r="H542" s="23" t="s">
-        <v>891</v>
       </c>
       <c r="I542" s="22" t="s">
         <v>46</v>
       </c>
       <c r="J542" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="543" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.45">
@@ -21134,7 +21138,7 @@
         <v>18</v>
       </c>
       <c r="E543" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F543" s="15" t="s">
         <v>545</v>
@@ -21143,7 +21147,7 @@
         <v>546</v>
       </c>
       <c r="H543" s="11" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="I543" s="11" t="s">
         <v>435</v>
@@ -21166,7 +21170,7 @@
         <v>18</v>
       </c>
       <c r="E544" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F544" s="15" t="s">
         <v>545</v>
@@ -21198,7 +21202,7 @@
         <v>18</v>
       </c>
       <c r="E545" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F545" s="15" t="s">
         <v>545</v>
@@ -21230,7 +21234,7 @@
         <v>18</v>
       </c>
       <c r="E546" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F546" s="15" t="s">
         <v>545</v>
@@ -21262,7 +21266,7 @@
         <v>18</v>
       </c>
       <c r="E547" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F547" s="15" t="s">
         <v>545</v>
@@ -21294,7 +21298,7 @@
         <v>18</v>
       </c>
       <c r="E548" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F548" s="15" t="s">
         <v>545</v>
@@ -21326,7 +21330,7 @@
         <v>18</v>
       </c>
       <c r="E549" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F549" s="15" t="s">
         <v>545</v>
@@ -21358,7 +21362,7 @@
         <v>18</v>
       </c>
       <c r="E550" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F550" s="15" t="s">
         <v>545</v>
@@ -21390,7 +21394,7 @@
         <v>18</v>
       </c>
       <c r="E551" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F551" s="15" t="s">
         <v>545</v>
@@ -21422,7 +21426,7 @@
         <v>18</v>
       </c>
       <c r="E552" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F552" s="15" t="s">
         <v>545</v>
@@ -21454,7 +21458,7 @@
         <v>25</v>
       </c>
       <c r="E553" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F553" s="6" t="s">
         <v>558</v>
@@ -21486,7 +21490,7 @@
         <v>25</v>
       </c>
       <c r="E554" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F554" s="6" t="s">
         <v>558</v>
@@ -21518,7 +21522,7 @@
         <v>25</v>
       </c>
       <c r="E555" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F555" s="6" t="s">
         <v>558</v>
@@ -21550,7 +21554,7 @@
         <v>25</v>
       </c>
       <c r="E556" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F556" s="6" t="s">
         <v>558</v>
@@ -21582,7 +21586,7 @@
         <v>25</v>
       </c>
       <c r="E557" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F557" s="6" t="s">
         <v>558</v>
@@ -21614,7 +21618,7 @@
         <v>25</v>
       </c>
       <c r="E558" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F558" s="6" t="s">
         <v>558</v>
@@ -21646,7 +21650,7 @@
         <v>25</v>
       </c>
       <c r="E559" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F559" s="6" t="s">
         <v>558</v>
@@ -21678,7 +21682,7 @@
         <v>25</v>
       </c>
       <c r="E560" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F560" s="6" t="s">
         <v>558</v>
@@ -21710,7 +21714,7 @@
         <v>25</v>
       </c>
       <c r="E561" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F561" s="6" t="s">
         <v>558</v>
@@ -21742,22 +21746,22 @@
         <v>25</v>
       </c>
       <c r="E562" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F562" s="22" t="s">
+        <v>892</v>
+      </c>
+      <c r="G562" s="22" t="s">
         <v>893</v>
       </c>
-      <c r="G562" s="22" t="s">
+      <c r="H562" s="22" t="s">
         <v>894</v>
-      </c>
-      <c r="H562" s="22" t="s">
-        <v>895</v>
       </c>
       <c r="I562" s="22" t="s">
         <v>54</v>
       </c>
       <c r="J562" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="563" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.45">
@@ -21774,7 +21778,7 @@
         <v>4</v>
       </c>
       <c r="E563" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F563" s="11" t="s">
         <v>569</v>
@@ -21806,7 +21810,7 @@
         <v>4</v>
       </c>
       <c r="E564" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F564" s="11" t="s">
         <v>569</v>
@@ -21838,7 +21842,7 @@
         <v>4</v>
       </c>
       <c r="E565" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F565" s="11" t="s">
         <v>569</v>
@@ -21870,7 +21874,7 @@
         <v>4</v>
       </c>
       <c r="E566" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F566" s="11" t="s">
         <v>569</v>
@@ -21902,7 +21906,7 @@
         <v>4</v>
       </c>
       <c r="E567" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F567" s="11" t="s">
         <v>569</v>
@@ -21934,7 +21938,7 @@
         <v>4</v>
       </c>
       <c r="E568" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F568" s="11" t="s">
         <v>569</v>
@@ -21966,7 +21970,7 @@
         <v>4</v>
       </c>
       <c r="E569" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F569" s="11" t="s">
         <v>569</v>
@@ -21998,7 +22002,7 @@
         <v>4</v>
       </c>
       <c r="E570" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F570" s="11" t="s">
         <v>569</v>
@@ -22030,7 +22034,7 @@
         <v>4</v>
       </c>
       <c r="E571" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F571" s="11" t="s">
         <v>569</v>
@@ -22062,7 +22066,7 @@
         <v>4</v>
       </c>
       <c r="E572" s="10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F572" s="11" t="s">
         <v>569</v>
@@ -22094,7 +22098,7 @@
         <v>12</v>
       </c>
       <c r="E573" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F573" s="6" t="s">
         <v>576</v>
@@ -22126,7 +22130,7 @@
         <v>12</v>
       </c>
       <c r="E574" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F574" s="6" t="s">
         <v>576</v>
@@ -22158,7 +22162,7 @@
         <v>12</v>
       </c>
       <c r="E575" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F575" s="6" t="s">
         <v>576</v>
@@ -22190,7 +22194,7 @@
         <v>12</v>
       </c>
       <c r="E576" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F576" s="6" t="s">
         <v>576</v>
@@ -22222,7 +22226,7 @@
         <v>12</v>
       </c>
       <c r="E577" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F577" s="6" t="s">
         <v>576</v>
@@ -22254,7 +22258,7 @@
         <v>12</v>
       </c>
       <c r="E578" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F578" s="6" t="s">
         <v>576</v>
@@ -22286,7 +22290,7 @@
         <v>12</v>
       </c>
       <c r="E579" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F579" s="6" t="s">
         <v>576</v>
@@ -22318,7 +22322,7 @@
         <v>12</v>
       </c>
       <c r="E580" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F580" s="6" t="s">
         <v>576</v>
@@ -22350,7 +22354,7 @@
         <v>12</v>
       </c>
       <c r="E581" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F581" s="6" t="s">
         <v>576</v>
@@ -22382,7 +22386,7 @@
         <v>12</v>
       </c>
       <c r="E582" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F582" s="6" t="s">
         <v>576</v>
@@ -22414,7 +22418,7 @@
         <v>12</v>
       </c>
       <c r="E583" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F583" s="6" t="s">
         <v>576</v>
@@ -22446,7 +22450,7 @@
         <v>12</v>
       </c>
       <c r="E584" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F584" s="6" t="s">
         <v>576</v>
@@ -22478,7 +22482,7 @@
         <v>12</v>
       </c>
       <c r="E585" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F585" s="6" t="s">
         <v>576</v>
@@ -22510,7 +22514,7 @@
         <v>12</v>
       </c>
       <c r="E586" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F586" s="6" t="s">
         <v>576</v>
@@ -22542,7 +22546,7 @@
         <v>12</v>
       </c>
       <c r="E587" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F587" s="6" t="s">
         <v>576</v>
@@ -22574,7 +22578,7 @@
         <v>12</v>
       </c>
       <c r="E588" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F588" s="6" t="s">
         <v>576</v>
@@ -22606,22 +22610,22 @@
         <v>25</v>
       </c>
       <c r="E589" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F589" s="22" t="s">
+        <v>895</v>
+      </c>
+      <c r="G589" s="22" t="s">
         <v>896</v>
       </c>
-      <c r="G589" s="22" t="s">
+      <c r="H589" s="22" t="s">
         <v>897</v>
-      </c>
-      <c r="H589" s="22" t="s">
-        <v>898</v>
       </c>
       <c r="I589" s="22" t="s">
         <v>54</v>
       </c>
       <c r="J589" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="590" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -22638,22 +22642,22 @@
         <v>25</v>
       </c>
       <c r="E590" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F590" s="22" t="s">
+        <v>898</v>
+      </c>
+      <c r="G590" s="22" t="s">
         <v>899</v>
       </c>
-      <c r="G590" s="22" t="s">
+      <c r="H590" s="22" t="s">
         <v>900</v>
-      </c>
-      <c r="H590" s="22" t="s">
-        <v>901</v>
       </c>
       <c r="I590" s="22" t="s">
         <v>54</v>
       </c>
       <c r="J590" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="591" spans="1:10" s="22" customFormat="1" x14ac:dyDescent="0.45">
@@ -22670,22 +22674,22 @@
         <v>1</v>
       </c>
       <c r="E591" s="21" t="s">
-        <v>664</v>
+        <v>933</v>
       </c>
       <c r="F591" s="22" t="s">
+        <v>901</v>
+      </c>
+      <c r="G591" s="22" t="s">
         <v>902</v>
       </c>
-      <c r="G591" s="22" t="s">
+      <c r="H591" s="22" t="s">
         <v>903</v>
       </c>
-      <c r="H591" s="22" t="s">
+      <c r="I591" s="22" t="s">
         <v>904</v>
       </c>
-      <c r="I591" s="22" t="s">
-        <v>905</v>
-      </c>
       <c r="J591" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="592" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -22702,7 +22706,7 @@
         <v>8</v>
       </c>
       <c r="E592" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F592" s="4" t="s">
         <v>584</v>
@@ -22734,7 +22738,7 @@
         <v>8</v>
       </c>
       <c r="E593" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F593" s="4" t="s">
         <v>584</v>
@@ -22766,7 +22770,7 @@
         <v>8</v>
       </c>
       <c r="E594" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F594" s="4" t="s">
         <v>584</v>
@@ -22798,7 +22802,7 @@
         <v>8</v>
       </c>
       <c r="E595" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F595" s="4" t="s">
         <v>584</v>
@@ -22830,7 +22834,7 @@
         <v>8</v>
       </c>
       <c r="E596" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F596" s="4" t="s">
         <v>584</v>
@@ -22862,7 +22866,7 @@
         <v>8</v>
       </c>
       <c r="E597" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F597" s="4" t="s">
         <v>584</v>
@@ -22894,7 +22898,7 @@
         <v>8</v>
       </c>
       <c r="E598" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F598" s="4" t="s">
         <v>584</v>
@@ -22926,7 +22930,7 @@
         <v>8</v>
       </c>
       <c r="E599" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F599" s="4" t="s">
         <v>584</v>
@@ -22958,7 +22962,7 @@
         <v>8</v>
       </c>
       <c r="E600" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F600" s="4" t="s">
         <v>584</v>
@@ -22990,7 +22994,7 @@
         <v>8</v>
       </c>
       <c r="E601" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F601" s="4" t="s">
         <v>584</v>
@@ -23022,7 +23026,7 @@
         <v>8</v>
       </c>
       <c r="E602" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F602" s="4" t="s">
         <v>584</v>
@@ -23054,7 +23058,7 @@
         <v>8</v>
       </c>
       <c r="E603" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F603" s="4" t="s">
         <v>584</v>
@@ -23086,7 +23090,7 @@
         <v>8</v>
       </c>
       <c r="E604" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F604" s="4" t="s">
         <v>584</v>
@@ -23118,7 +23122,7 @@
         <v>8</v>
       </c>
       <c r="E605" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F605" s="4" t="s">
         <v>584</v>
@@ -23150,10 +23154,10 @@
         <v>25</v>
       </c>
       <c r="E606" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F606" s="6" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="G606" s="6" t="s">
         <v>595</v>
@@ -23182,7 +23186,7 @@
         <v>25</v>
       </c>
       <c r="E607" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F607" s="6" t="s">
         <v>594</v>
@@ -23214,7 +23218,7 @@
         <v>25</v>
       </c>
       <c r="E608" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F608" s="6" t="s">
         <v>594</v>
@@ -23246,7 +23250,7 @@
         <v>25</v>
       </c>
       <c r="E609" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F609" s="6" t="s">
         <v>594</v>
@@ -23278,7 +23282,7 @@
         <v>25</v>
       </c>
       <c r="E610" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F610" s="6" t="s">
         <v>594</v>
@@ -23310,7 +23314,7 @@
         <v>25</v>
       </c>
       <c r="E611" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F611" s="6" t="s">
         <v>594</v>
@@ -23342,7 +23346,7 @@
         <v>25</v>
       </c>
       <c r="E612" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F612" s="6" t="s">
         <v>594</v>
@@ -23374,7 +23378,7 @@
         <v>25</v>
       </c>
       <c r="E613" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F613" s="6" t="s">
         <v>594</v>
@@ -23406,7 +23410,7 @@
         <v>25</v>
       </c>
       <c r="E614" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F614" s="6" t="s">
         <v>594</v>
@@ -23438,22 +23442,22 @@
         <v>29</v>
       </c>
       <c r="E615" s="21" t="s">
-        <v>664</v>
+        <v>932</v>
       </c>
       <c r="F615" s="22" t="s">
+        <v>905</v>
+      </c>
+      <c r="G615" s="22" t="s">
         <v>906</v>
       </c>
-      <c r="G615" s="22" t="s">
+      <c r="H615" s="22" t="s">
         <v>907</v>
-      </c>
-      <c r="H615" s="22" t="s">
-        <v>908</v>
       </c>
       <c r="I615" s="22" t="s">
         <v>54</v>
       </c>
       <c r="J615" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="616" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -23470,7 +23474,7 @@
         <v>16</v>
       </c>
       <c r="E616" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F616" s="17" t="s">
         <v>598</v>
@@ -23502,7 +23506,7 @@
         <v>16</v>
       </c>
       <c r="E617" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F617" s="17" t="s">
         <v>598</v>
@@ -23534,7 +23538,7 @@
         <v>16</v>
       </c>
       <c r="E618" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F618" s="17" t="s">
         <v>598</v>
@@ -23566,7 +23570,7 @@
         <v>16</v>
       </c>
       <c r="E619" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F619" s="17" t="s">
         <v>598</v>
@@ -23598,7 +23602,7 @@
         <v>16</v>
       </c>
       <c r="E620" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F620" s="17" t="s">
         <v>598</v>
@@ -23630,7 +23634,7 @@
         <v>16</v>
       </c>
       <c r="E621" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F621" s="17" t="s">
         <v>598</v>
@@ -23662,7 +23666,7 @@
         <v>16</v>
       </c>
       <c r="E622" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F622" s="17" t="s">
         <v>598</v>
@@ -23694,7 +23698,7 @@
         <v>16</v>
       </c>
       <c r="E623" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F623" s="17" t="s">
         <v>598</v>
@@ -23726,7 +23730,7 @@
         <v>2</v>
       </c>
       <c r="E624" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F624" s="18" t="s">
         <v>607</v>
@@ -23758,7 +23762,7 @@
         <v>2</v>
       </c>
       <c r="E625" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F625" s="18" t="s">
         <v>607</v>
@@ -23790,7 +23794,7 @@
         <v>2</v>
       </c>
       <c r="E626" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F626" s="18" t="s">
         <v>607</v>
@@ -23822,7 +23826,7 @@
         <v>2</v>
       </c>
       <c r="E627" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F627" s="18" t="s">
         <v>607</v>
@@ -23854,7 +23858,7 @@
         <v>2</v>
       </c>
       <c r="E628" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F628" s="18" t="s">
         <v>607</v>
@@ -23886,7 +23890,7 @@
         <v>2</v>
       </c>
       <c r="E629" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F629" s="18" t="s">
         <v>607</v>
@@ -23918,7 +23922,7 @@
         <v>2</v>
       </c>
       <c r="E630" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F630" s="18" t="s">
         <v>607</v>
@@ -23950,7 +23954,7 @@
         <v>2</v>
       </c>
       <c r="E631" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F631" s="18" t="s">
         <v>607</v>
@@ -23982,7 +23986,7 @@
         <v>2</v>
       </c>
       <c r="E632" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F632" s="18" t="s">
         <v>607</v>
@@ -23991,10 +23995,10 @@
         <v>608</v>
       </c>
       <c r="H632" s="6" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I632" s="6" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="J632" s="25">
         <v>4.9895833333333334E-2</v>
@@ -24014,7 +24018,7 @@
         <v>2</v>
       </c>
       <c r="E633" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F633" s="18" t="s">
         <v>607</v>
@@ -24046,7 +24050,7 @@
         <v>2</v>
       </c>
       <c r="E634" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F634" s="18" t="s">
         <v>607</v>
@@ -24078,7 +24082,7 @@
         <v>2</v>
       </c>
       <c r="E635" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F635" s="18" t="s">
         <v>607</v>
@@ -24110,7 +24114,7 @@
         <v>2</v>
       </c>
       <c r="E636" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F636" s="18" t="s">
         <v>607</v>
@@ -24142,7 +24146,7 @@
         <v>2</v>
       </c>
       <c r="E637" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F637" s="18" t="s">
         <v>607</v>
@@ -24174,7 +24178,7 @@
         <v>2</v>
       </c>
       <c r="E638" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F638" s="18" t="s">
         <v>607</v>
@@ -24206,7 +24210,7 @@
         <v>2</v>
       </c>
       <c r="E639" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F639" s="18" t="s">
         <v>607</v>
@@ -24238,7 +24242,7 @@
         <v>2</v>
       </c>
       <c r="E640" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F640" s="18" t="s">
         <v>607</v>
@@ -24270,7 +24274,7 @@
         <v>2</v>
       </c>
       <c r="E641" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F641" s="18" t="s">
         <v>607</v>
@@ -24302,7 +24306,7 @@
         <v>2</v>
       </c>
       <c r="E642" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F642" s="18" t="s">
         <v>607</v>
@@ -24334,7 +24338,7 @@
         <v>2</v>
       </c>
       <c r="E643" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F643" s="18" t="s">
         <v>607</v>
@@ -24343,10 +24347,10 @@
         <v>608</v>
       </c>
       <c r="H643" s="6" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I643" s="6" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="J643" s="25">
         <v>0.11259259259259259</v>
@@ -24366,7 +24370,7 @@
         <v>2</v>
       </c>
       <c r="E644" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F644" s="18" t="s">
         <v>607</v>
@@ -24398,7 +24402,7 @@
         <v>2</v>
       </c>
       <c r="E645" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F645" s="18" t="s">
         <v>607</v>
@@ -24407,10 +24411,10 @@
         <v>608</v>
       </c>
       <c r="H645" s="6" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="I645" s="6" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="J645" s="25">
         <v>0.11967592592592592</v>
@@ -24430,7 +24434,7 @@
         <v>2</v>
       </c>
       <c r="E646" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F646" s="18" t="s">
         <v>607</v>
@@ -24462,7 +24466,7 @@
         <v>2</v>
       </c>
       <c r="E647" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F647" s="18" t="s">
         <v>607</v>
@@ -24494,7 +24498,7 @@
         <v>2</v>
       </c>
       <c r="E648" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F648" s="18" t="s">
         <v>607</v>
@@ -24503,10 +24507,10 @@
         <v>608</v>
       </c>
       <c r="H648" s="6" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="I648" s="6" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="J648" s="25">
         <v>0.13688657407407406</v>
@@ -24526,7 +24530,7 @@
         <v>2</v>
       </c>
       <c r="E649" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F649" s="18" t="s">
         <v>607</v>
@@ -24558,7 +24562,7 @@
         <v>2</v>
       </c>
       <c r="E650" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F650" s="18" t="s">
         <v>607</v>
@@ -24590,13 +24594,13 @@
         <v>15</v>
       </c>
       <c r="E651" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F651" s="19" t="s">
         <v>617</v>
       </c>
       <c r="G651" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H651" s="13" t="s">
         <v>618</v>
@@ -24605,7 +24609,7 @@
         <v>54</v>
       </c>
       <c r="J651" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="652" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.45">
@@ -24622,13 +24626,13 @@
         <v>15</v>
       </c>
       <c r="E652" s="12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F652" s="19" t="s">
         <v>617</v>
       </c>
       <c r="G652" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H652" s="13" t="s">
         <v>619</v>
@@ -24637,7 +24641,7 @@
         <v>54</v>
       </c>
       <c r="J652" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="653" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.45">
@@ -24654,13 +24658,13 @@
         <v>15</v>
       </c>
       <c r="E653" s="12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F653" s="19" t="s">
         <v>617</v>
       </c>
       <c r="G653" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H653" s="13" t="s">
         <v>620</v>
@@ -24669,7 +24673,7 @@
         <v>54</v>
       </c>
       <c r="J653" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="654" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.45">
@@ -24686,13 +24690,13 @@
         <v>15</v>
       </c>
       <c r="E654" s="12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F654" s="19" t="s">
         <v>617</v>
       </c>
       <c r="G654" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H654" s="13" t="s">
         <v>621</v>
@@ -24701,7 +24705,7 @@
         <v>54</v>
       </c>
       <c r="J654" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="655" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.45">
@@ -24718,13 +24722,13 @@
         <v>15</v>
       </c>
       <c r="E655" s="12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F655" s="19" t="s">
         <v>617</v>
       </c>
       <c r="G655" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H655" s="13" t="s">
         <v>622</v>
@@ -24733,7 +24737,7 @@
         <v>54</v>
       </c>
       <c r="J655" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="656" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.45">
@@ -24750,13 +24754,13 @@
         <v>15</v>
       </c>
       <c r="E656" s="12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F656" s="19" t="s">
         <v>617</v>
       </c>
       <c r="G656" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H656" s="13" t="s">
         <v>623</v>
@@ -24765,7 +24769,7 @@
         <v>54</v>
       </c>
       <c r="J656" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="657" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.45">
@@ -24782,13 +24786,13 @@
         <v>15</v>
       </c>
       <c r="E657" s="12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F657" s="19" t="s">
         <v>617</v>
       </c>
       <c r="G657" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H657" s="13" t="s">
         <v>624</v>
@@ -24797,7 +24801,7 @@
         <v>54</v>
       </c>
       <c r="J657" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="658" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -24814,7 +24818,7 @@
         <v>23</v>
       </c>
       <c r="E658" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F658" s="4" t="s">
         <v>625</v>
@@ -24846,7 +24850,7 @@
         <v>23</v>
       </c>
       <c r="E659" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F659" s="4" t="s">
         <v>625</v>
@@ -24878,7 +24882,7 @@
         <v>23</v>
       </c>
       <c r="E660" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F660" s="4" t="s">
         <v>625</v>
@@ -24910,7 +24914,7 @@
         <v>23</v>
       </c>
       <c r="E661" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F661" s="4" t="s">
         <v>625</v>
@@ -24942,7 +24946,7 @@
         <v>23</v>
       </c>
       <c r="E662" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F662" s="4" t="s">
         <v>625</v>
@@ -24974,7 +24978,7 @@
         <v>23</v>
       </c>
       <c r="E663" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F663" s="4" t="s">
         <v>625</v>
@@ -25006,7 +25010,7 @@
         <v>23</v>
       </c>
       <c r="E664" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F664" s="4" t="s">
         <v>625</v>
@@ -25038,7 +25042,7 @@
         <v>23</v>
       </c>
       <c r="E665" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F665" s="4" t="s">
         <v>625</v>
@@ -25070,7 +25074,7 @@
         <v>23</v>
       </c>
       <c r="E666" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F666" s="4" t="s">
         <v>625</v>
@@ -25102,7 +25106,7 @@
         <v>23</v>
       </c>
       <c r="E667" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F667" s="4" t="s">
         <v>625</v>
@@ -25134,7 +25138,7 @@
         <v>23</v>
       </c>
       <c r="E668" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F668" s="4" t="s">
         <v>625</v>
@@ -25166,7 +25170,7 @@
         <v>23</v>
       </c>
       <c r="E669" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F669" s="4" t="s">
         <v>625</v>
@@ -25198,7 +25202,7 @@
         <v>23</v>
       </c>
       <c r="E670" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F670" s="4" t="s">
         <v>625</v>
@@ -25230,7 +25234,7 @@
         <v>23</v>
       </c>
       <c r="E671" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F671" s="4" t="s">
         <v>625</v>
@@ -25262,7 +25266,7 @@
         <v>23</v>
       </c>
       <c r="E672" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F672" s="4" t="s">
         <v>625</v>
@@ -25294,7 +25298,7 @@
         <v>23</v>
       </c>
       <c r="E673" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F673" s="4" t="s">
         <v>625</v>
@@ -25326,7 +25330,7 @@
         <v>23</v>
       </c>
       <c r="E674" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F674" s="4" t="s">
         <v>625</v>
@@ -25358,7 +25362,7 @@
         <v>23</v>
       </c>
       <c r="E675" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F675" s="4" t="s">
         <v>625</v>
@@ -25390,7 +25394,7 @@
         <v>6</v>
       </c>
       <c r="E676" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F676" s="6" t="s">
         <v>638</v>
@@ -25422,7 +25426,7 @@
         <v>6</v>
       </c>
       <c r="E677" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F677" s="6" t="s">
         <v>638</v>
@@ -25454,7 +25458,7 @@
         <v>6</v>
       </c>
       <c r="E678" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F678" s="6" t="s">
         <v>638</v>
@@ -25486,7 +25490,7 @@
         <v>6</v>
       </c>
       <c r="E679" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F679" s="6" t="s">
         <v>638</v>
@@ -25518,7 +25522,7 @@
         <v>6</v>
       </c>
       <c r="E680" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F680" s="6" t="s">
         <v>638</v>
@@ -25550,7 +25554,7 @@
         <v>6</v>
       </c>
       <c r="E681" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F681" s="6" t="s">
         <v>638</v>
@@ -25582,7 +25586,7 @@
         <v>6</v>
       </c>
       <c r="E682" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F682" s="6" t="s">
         <v>638</v>
@@ -25614,7 +25618,7 @@
         <v>6</v>
       </c>
       <c r="E683" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F683" s="6" t="s">
         <v>638</v>
@@ -25646,7 +25650,7 @@
         <v>6</v>
       </c>
       <c r="E684" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F684" s="6" t="s">
         <v>638</v>
@@ -25678,7 +25682,7 @@
         <v>6</v>
       </c>
       <c r="E685" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F685" s="6" t="s">
         <v>638</v>
@@ -25710,7 +25714,7 @@
         <v>6</v>
       </c>
       <c r="E686" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F686" s="6" t="s">
         <v>638</v>
@@ -25742,7 +25746,7 @@
         <v>6</v>
       </c>
       <c r="E687" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F687" s="6" t="s">
         <v>638</v>
@@ -25774,7 +25778,7 @@
         <v>6</v>
       </c>
       <c r="E688" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F688" s="6" t="s">
         <v>638</v>
@@ -25806,7 +25810,7 @@
         <v>6</v>
       </c>
       <c r="E689" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F689" s="6" t="s">
         <v>638</v>
@@ -25838,7 +25842,7 @@
         <v>6</v>
       </c>
       <c r="E690" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F690" s="6" t="s">
         <v>638</v>
@@ -25870,7 +25874,7 @@
         <v>6</v>
       </c>
       <c r="E691" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F691" s="6" t="s">
         <v>638</v>
@@ -25902,7 +25906,7 @@
         <v>6</v>
       </c>
       <c r="E692" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F692" s="6" t="s">
         <v>638</v>
@@ -25934,13 +25938,13 @@
         <v>12</v>
       </c>
       <c r="E693" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F693" s="13" t="s">
         <v>648</v>
       </c>
       <c r="G693" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H693" s="13" t="s">
         <v>618</v>
@@ -25949,7 +25953,7 @@
         <v>54</v>
       </c>
       <c r="J693" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="694" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.45">
@@ -25966,13 +25970,13 @@
         <v>12</v>
       </c>
       <c r="E694" s="12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F694" s="13" t="s">
         <v>648</v>
       </c>
       <c r="G694" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H694" s="13" t="s">
         <v>649</v>
@@ -25981,7 +25985,7 @@
         <v>54</v>
       </c>
       <c r="J694" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="695" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.45">
@@ -25998,13 +26002,13 @@
         <v>12</v>
       </c>
       <c r="E695" s="12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F695" s="13" t="s">
         <v>648</v>
       </c>
       <c r="G695" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H695" s="13" t="s">
         <v>624</v>
@@ -26013,7 +26017,7 @@
         <v>54</v>
       </c>
       <c r="J695" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="696" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.45">
@@ -26030,13 +26034,13 @@
         <v>12</v>
       </c>
       <c r="E696" s="12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F696" s="13" t="s">
         <v>648</v>
       </c>
       <c r="G696" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H696" s="13" t="s">
         <v>482</v>
@@ -26045,7 +26049,7 @@
         <v>54</v>
       </c>
       <c r="J696" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="697" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.45">
@@ -26062,13 +26066,13 @@
         <v>12</v>
       </c>
       <c r="E697" s="12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F697" s="13" t="s">
         <v>648</v>
       </c>
       <c r="G697" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H697" s="13" t="s">
         <v>650</v>
@@ -26077,7 +26081,7 @@
         <v>54</v>
       </c>
       <c r="J697" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="698" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.45">
@@ -26094,13 +26098,13 @@
         <v>12</v>
       </c>
       <c r="E698" s="12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F698" s="13" t="s">
         <v>648</v>
       </c>
       <c r="G698" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H698" s="13" t="s">
         <v>651</v>
@@ -26109,7 +26113,7 @@
         <v>54</v>
       </c>
       <c r="J698" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="699" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.45">
@@ -26126,13 +26130,13 @@
         <v>12</v>
       </c>
       <c r="E699" s="12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F699" s="13" t="s">
         <v>648</v>
       </c>
       <c r="G699" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H699" s="13" t="s">
         <v>652</v>
@@ -26141,7 +26145,7 @@
         <v>54</v>
       </c>
       <c r="J699" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="700" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.45">
@@ -26158,13 +26162,13 @@
         <v>12</v>
       </c>
       <c r="E700" s="12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F700" s="13" t="s">
         <v>648</v>
       </c>
       <c r="G700" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H700" s="13" t="s">
         <v>620</v>
@@ -26173,7 +26177,7 @@
         <v>54</v>
       </c>
       <c r="J700" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="701" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.45">
@@ -26190,13 +26194,13 @@
         <v>12</v>
       </c>
       <c r="E701" s="12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F701" s="13" t="s">
         <v>648</v>
       </c>
       <c r="G701" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H701" s="13" t="s">
         <v>653</v>
@@ -26205,7 +26209,7 @@
         <v>54</v>
       </c>
       <c r="J701" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="702" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.45">
@@ -26222,13 +26226,13 @@
         <v>12</v>
       </c>
       <c r="E702" s="12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F702" s="13" t="s">
         <v>648</v>
       </c>
       <c r="G702" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H702" s="13" t="s">
         <v>654</v>
@@ -26237,7 +26241,7 @@
         <v>54</v>
       </c>
       <c r="J702" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="703" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.45">
@@ -26254,13 +26258,13 @@
         <v>12</v>
       </c>
       <c r="E703" s="12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F703" s="13" t="s">
         <v>648</v>
       </c>
       <c r="G703" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H703" s="13" t="s">
         <v>655</v>
@@ -26269,7 +26273,7 @@
         <v>54</v>
       </c>
       <c r="J703" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="704" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -26286,13 +26290,13 @@
         <v>23</v>
       </c>
       <c r="E704" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F704" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="G704" s="4" t="s">
         <v>909</v>
-      </c>
-      <c r="G704" s="4" t="s">
-        <v>910</v>
       </c>
       <c r="H704" s="4" t="s">
         <v>237</v>
@@ -26318,13 +26322,13 @@
         <v>23</v>
       </c>
       <c r="E705" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F705" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="G705" s="4" t="s">
         <v>909</v>
-      </c>
-      <c r="G705" s="4" t="s">
-        <v>910</v>
       </c>
       <c r="H705" s="4" t="s">
         <v>134</v>
@@ -26350,13 +26354,13 @@
         <v>23</v>
       </c>
       <c r="E706" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F706" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="G706" s="4" t="s">
         <v>909</v>
-      </c>
-      <c r="G706" s="4" t="s">
-        <v>910</v>
       </c>
       <c r="H706" s="4" t="s">
         <v>498</v>
@@ -26382,13 +26386,13 @@
         <v>23</v>
       </c>
       <c r="E707" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F707" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="G707" s="4" t="s">
         <v>909</v>
-      </c>
-      <c r="G707" s="4" t="s">
-        <v>910</v>
       </c>
       <c r="H707" s="4" t="s">
         <v>542</v>
@@ -26414,13 +26418,13 @@
         <v>23</v>
       </c>
       <c r="E708" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F708" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="G708" s="4" t="s">
         <v>909</v>
-      </c>
-      <c r="G708" s="4" t="s">
-        <v>910</v>
       </c>
       <c r="H708" s="4" t="s">
         <v>589</v>
@@ -26446,19 +26450,19 @@
         <v>23</v>
       </c>
       <c r="E709" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F709" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="G709" s="4" t="s">
         <v>909</v>
       </c>
-      <c r="G709" s="4" t="s">
+      <c r="H709" s="4" t="s">
         <v>910</v>
       </c>
-      <c r="H709" s="4" t="s">
+      <c r="I709" s="4" t="s">
         <v>911</v>
-      </c>
-      <c r="I709" s="4" t="s">
-        <v>912</v>
       </c>
       <c r="J709" s="26">
         <v>1.787037037037037E-2</v>

--- a/songs_data.xlsx
+++ b/songs_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y\Desktop\Nagi Live Archives\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59C8758-F6F8-4AB2-AEAF-9AC6A33766EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C841DD-EF1D-4A6C-88C1-1A94E39D2315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{90EDF358-D884-4DF4-A049-DD2596755BAC}"/>
   </bookViews>
@@ -10802,7 +10802,7 @@
         <v>28</v>
       </c>
       <c r="E220" s="21" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="F220" s="22" t="s">
         <v>758</v>

--- a/songs_data.xlsx
+++ b/songs_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y\Desktop\Nagi Live Archives\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C841DD-EF1D-4A6C-88C1-1A94E39D2315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAFC8E10-49C5-4E84-8DA8-649285B23808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{90EDF358-D884-4DF4-A049-DD2596755BAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{90EDF358-D884-4DF4-A049-DD2596755BAC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3658" uniqueCount="934">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3723" uniqueCount="955">
   <si>
     <t>配信タイトル</t>
     <rPh sb="0" eb="2">
@@ -3234,6 +3234,105 @@
   </si>
   <si>
     <t>カバー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【実写歌枠】同接50人&amp;高評価100目標！たくさん広まれ俺の歌！！【イザナギ・エルヴァ】</t>
+  </si>
+  <si>
+    <t>【実写歌枠】同接50人&amp;高評価100目標！たくさん広まれ俺の歌！！【イザナギ・エルヴァ】</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/live/9Uop__mtsFg?si=R-l--qZYcn6X_Y8A</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/live/9Uop__mtsFg?si=R-l--qZYcn6X_Y8A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ムスタング</t>
+  </si>
+  <si>
+    <t>ASIAN KUNG-FU GENERATION</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>若者のすべて</t>
+    <rPh sb="0" eb="2">
+      <t>ワカモノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フジファブリック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Clock</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エイプリル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SUGAR</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BROCKHAMPTON</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新宝島</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サカナクション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボイル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>悲しみの果て</t>
+    <rPh sb="0" eb="1">
+      <t>カナ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ハ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エレファントカシマシ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>個人勢Vtuberだってもっと知られたいわい！</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イザナギ・エルヴァ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>恋わずらい</t>
+    <rPh sb="0" eb="1">
+      <t>コイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>少年少女</t>
+    <rPh sb="0" eb="2">
+      <t>ショウネン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショウジョ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3765,7 +3864,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DE68349-627D-443B-8777-75196758F221}">
-  <dimension ref="A1:J709"/>
+  <dimension ref="A1:J722"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.19921875" style="1" customWidth="1"/>
@@ -26468,6 +26567,422 @@
         <v>1.787037037037037E-2</v>
       </c>
     </row>
+    <row r="710" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A710" s="5">
+        <v>147</v>
+      </c>
+      <c r="B710" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C710" s="5">
+        <v>10</v>
+      </c>
+      <c r="D710" s="5">
+        <v>4</v>
+      </c>
+      <c r="E710" s="5" t="s">
+        <v>668</v>
+      </c>
+      <c r="F710" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="G710" s="6" t="s">
+        <v>937</v>
+      </c>
+      <c r="H710" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="I710" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J710" s="25">
+        <v>3.6226851851851854E-3</v>
+      </c>
+    </row>
+    <row r="711" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A711" s="5">
+        <v>147</v>
+      </c>
+      <c r="B711" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C711" s="5">
+        <v>10</v>
+      </c>
+      <c r="D711" s="5">
+        <v>4</v>
+      </c>
+      <c r="E711" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="F711" s="6" t="s">
+        <v>934</v>
+      </c>
+      <c r="G711" s="6" t="s">
+        <v>936</v>
+      </c>
+      <c r="H711" s="6" t="s">
+        <v>938</v>
+      </c>
+      <c r="I711" s="6" t="s">
+        <v>939</v>
+      </c>
+      <c r="J711" s="25">
+        <v>8.3333333333333332E-3</v>
+      </c>
+    </row>
+    <row r="712" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A712" s="5">
+        <v>147</v>
+      </c>
+      <c r="B712" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C712" s="5">
+        <v>10</v>
+      </c>
+      <c r="D712" s="5">
+        <v>4</v>
+      </c>
+      <c r="E712" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="F712" s="6" t="s">
+        <v>934</v>
+      </c>
+      <c r="G712" s="6" t="s">
+        <v>936</v>
+      </c>
+      <c r="H712" s="6" t="s">
+        <v>940</v>
+      </c>
+      <c r="I712" s="6" t="s">
+        <v>941</v>
+      </c>
+      <c r="J712" s="25">
+        <v>1.892361111111111E-2</v>
+      </c>
+    </row>
+    <row r="713" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A713" s="5">
+        <v>147</v>
+      </c>
+      <c r="B713" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C713" s="5">
+        <v>10</v>
+      </c>
+      <c r="D713" s="5">
+        <v>4</v>
+      </c>
+      <c r="E713" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="F713" s="6" t="s">
+        <v>934</v>
+      </c>
+      <c r="G713" s="6" t="s">
+        <v>936</v>
+      </c>
+      <c r="H713" s="6" t="s">
+        <v>942</v>
+      </c>
+      <c r="I713" s="6" t="s">
+        <v>941</v>
+      </c>
+      <c r="J713" s="25">
+        <v>2.4930555555555556E-2</v>
+      </c>
+    </row>
+    <row r="714" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A714" s="5">
+        <v>147</v>
+      </c>
+      <c r="B714" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C714" s="5">
+        <v>10</v>
+      </c>
+      <c r="D714" s="5">
+        <v>4</v>
+      </c>
+      <c r="E714" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="F714" s="6" t="s">
+        <v>934</v>
+      </c>
+      <c r="G714" s="6" t="s">
+        <v>936</v>
+      </c>
+      <c r="H714" s="6" t="s">
+        <v>943</v>
+      </c>
+      <c r="I714" s="6" t="s">
+        <v>941</v>
+      </c>
+      <c r="J714" s="25">
+        <v>2.9108796296296296E-2</v>
+      </c>
+    </row>
+    <row r="715" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A715" s="5">
+        <v>147</v>
+      </c>
+      <c r="B715" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C715" s="5">
+        <v>10</v>
+      </c>
+      <c r="D715" s="5">
+        <v>4</v>
+      </c>
+      <c r="E715" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="F715" s="6" t="s">
+        <v>934</v>
+      </c>
+      <c r="G715" s="6" t="s">
+        <v>936</v>
+      </c>
+      <c r="H715" s="6" t="s">
+        <v>944</v>
+      </c>
+      <c r="I715" s="6" t="s">
+        <v>945</v>
+      </c>
+      <c r="J715" s="25">
+        <v>3.3796296296296297E-2</v>
+      </c>
+    </row>
+    <row r="716" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A716" s="5">
+        <v>147</v>
+      </c>
+      <c r="B716" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C716" s="5">
+        <v>10</v>
+      </c>
+      <c r="D716" s="5">
+        <v>4</v>
+      </c>
+      <c r="E716" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="F716" s="6" t="s">
+        <v>934</v>
+      </c>
+      <c r="G716" s="6" t="s">
+        <v>936</v>
+      </c>
+      <c r="H716" s="6" t="s">
+        <v>946</v>
+      </c>
+      <c r="I716" s="6" t="s">
+        <v>947</v>
+      </c>
+      <c r="J716" s="25">
+        <v>3.6238425925925924E-2</v>
+      </c>
+    </row>
+    <row r="717" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A717" s="5">
+        <v>147</v>
+      </c>
+      <c r="B717" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C717" s="5">
+        <v>10</v>
+      </c>
+      <c r="D717" s="5">
+        <v>4</v>
+      </c>
+      <c r="E717" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="F717" s="6" t="s">
+        <v>934</v>
+      </c>
+      <c r="G717" s="6" t="s">
+        <v>936</v>
+      </c>
+      <c r="H717" s="6" t="s">
+        <v>948</v>
+      </c>
+      <c r="I717" s="6" t="s">
+        <v>947</v>
+      </c>
+      <c r="J717" s="25">
+        <v>4.1828703703703701E-2</v>
+      </c>
+    </row>
+    <row r="718" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A718" s="5">
+        <v>147</v>
+      </c>
+      <c r="B718" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C718" s="5">
+        <v>10</v>
+      </c>
+      <c r="D718" s="5">
+        <v>4</v>
+      </c>
+      <c r="E718" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="F718" s="6" t="s">
+        <v>934</v>
+      </c>
+      <c r="G718" s="6" t="s">
+        <v>936</v>
+      </c>
+      <c r="H718" s="6" t="s">
+        <v>949</v>
+      </c>
+      <c r="I718" s="6" t="s">
+        <v>950</v>
+      </c>
+      <c r="J718" s="25">
+        <v>4.5057870370370373E-2</v>
+      </c>
+    </row>
+    <row r="719" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A719" s="5">
+        <v>147</v>
+      </c>
+      <c r="B719" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C719" s="5">
+        <v>10</v>
+      </c>
+      <c r="D719" s="5">
+        <v>4</v>
+      </c>
+      <c r="E719" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="F719" s="6" t="s">
+        <v>934</v>
+      </c>
+      <c r="G719" s="6" t="s">
+        <v>936</v>
+      </c>
+      <c r="H719" s="6" t="s">
+        <v>951</v>
+      </c>
+      <c r="I719" s="6" t="s">
+        <v>952</v>
+      </c>
+      <c r="J719" s="25">
+        <v>4.821759259259259E-2</v>
+      </c>
+    </row>
+    <row r="720" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A720" s="5">
+        <v>147</v>
+      </c>
+      <c r="B720" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C720" s="5">
+        <v>10</v>
+      </c>
+      <c r="D720" s="5">
+        <v>4</v>
+      </c>
+      <c r="E720" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="F720" s="6" t="s">
+        <v>934</v>
+      </c>
+      <c r="G720" s="6" t="s">
+        <v>936</v>
+      </c>
+      <c r="H720" s="6" t="s">
+        <v>655</v>
+      </c>
+      <c r="I720" s="6" t="s">
+        <v>952</v>
+      </c>
+      <c r="J720" s="25">
+        <v>5.0671296296296298E-2</v>
+      </c>
+    </row>
+    <row r="721" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A721" s="5">
+        <v>147</v>
+      </c>
+      <c r="B721" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C721" s="5">
+        <v>10</v>
+      </c>
+      <c r="D721" s="5">
+        <v>4</v>
+      </c>
+      <c r="E721" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="F721" s="6" t="s">
+        <v>934</v>
+      </c>
+      <c r="G721" s="6" t="s">
+        <v>936</v>
+      </c>
+      <c r="H721" s="6" t="s">
+        <v>953</v>
+      </c>
+      <c r="I721" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="J721" s="25">
+        <v>5.8379629629629629E-2</v>
+      </c>
+    </row>
+    <row r="722" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A722" s="5">
+        <v>147</v>
+      </c>
+      <c r="B722" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C722" s="5">
+        <v>10</v>
+      </c>
+      <c r="D722" s="5">
+        <v>4</v>
+      </c>
+      <c r="E722" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="F722" s="6" t="s">
+        <v>934</v>
+      </c>
+      <c r="G722" s="6" t="s">
+        <v>936</v>
+      </c>
+      <c r="H722" s="6" t="s">
+        <v>954</v>
+      </c>
+      <c r="I722" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="J722" s="25">
+        <v>6.1689814814814815E-2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/songs_data.xlsx
+++ b/songs_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y\Desktop\Nagi Live Archives\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D848F616-5754-4527-ABC4-80645F71512E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DFD4C5E-5733-4E88-A210-1E76C0BCAF76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{90EDF358-D884-4DF4-A049-DD2596755BAC}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3828" uniqueCount="984">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3908" uniqueCount="1013">
   <si>
     <t>配信タイトル</t>
     <rPh sb="0" eb="2">
@@ -2985,10 +2985,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>香水(どアレンジver)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>踊ってばかりの国</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -3598,6 +3594,129 @@
   </si>
   <si>
     <t>蛙鳴蝉噪</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>香水(ドアレンジver)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ライブ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【実写歌枠】同接50人&amp;高評価100目標！アコギと歌で孤独な夜も吹き飛ばすね【イザナギ・エルヴァ】</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/live/e8NXuYwWi54</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OOPARTS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>羊文学</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>beautiful</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>踊ってばかりの国</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>光の中に</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>安藤裕子</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>衝撃</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>平沢進</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>白虎野の娘</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゆらゆら帝国</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>発光体</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Lily</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>気になるあの娘</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相対性理論</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チャイナアドバイス(おじさんver)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ルーキー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>グッドバイ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>銀杏BOYZ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>漂流教室</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>心に雲を持つ少年</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サニーデイ・サービス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>拝啓、少年よ</t>
+    <rPh sb="0" eb="2">
+      <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Hump Back</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>糸</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中島みゆき</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イザナギ・エルヴァ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3665,7 +3784,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3702,6 +3821,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -3720,7 +3845,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3813,6 +3938,15 @@
     </xf>
     <xf numFmtId="56" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4129,7 +4263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DE68349-627D-443B-8777-75196758F221}">
-  <dimension ref="A1:J743"/>
+  <dimension ref="A1:J759"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.19921875" style="1" customWidth="1"/>
@@ -4196,7 +4330,7 @@
         <v>614</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>208</v>
@@ -4228,7 +4362,7 @@
         <v>615</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>616</v>
@@ -4260,7 +4394,7 @@
         <v>617</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H4" s="22" t="s">
         <v>618</v>
@@ -4292,7 +4426,7 @@
         <v>619</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>620</v>
@@ -4324,7 +4458,7 @@
         <v>621</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H6" s="22" t="s">
         <v>622</v>
@@ -4356,7 +4490,7 @@
         <v>6</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>9</v>
@@ -4388,7 +4522,7 @@
         <v>624</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H8" s="22" t="s">
         <v>117</v>
@@ -4420,7 +4554,7 @@
         <v>625</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>50</v>
@@ -4452,7 +4586,7 @@
         <v>626</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H10" s="22" t="s">
         <v>189</v>
@@ -4484,7 +4618,7 @@
         <v>627</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>628</v>
@@ -4516,7 +4650,7 @@
         <v>630</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H12" s="22" t="s">
         <v>105</v>
@@ -4548,7 +4682,7 @@
         <v>631</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>221</v>
@@ -4580,7 +4714,7 @@
         <v>41</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>8</v>
@@ -4612,7 +4746,7 @@
         <v>41</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>42</v>
@@ -4644,7 +4778,7 @@
         <v>41</v>
       </c>
       <c r="G16" s="20" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>45</v>
@@ -4676,7 +4810,7 @@
         <v>41</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>47</v>
@@ -4708,7 +4842,7 @@
         <v>41</v>
       </c>
       <c r="G18" s="20" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>49</v>
@@ -4740,7 +4874,7 @@
         <v>41</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>50</v>
@@ -4772,7 +4906,7 @@
         <v>633</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H20" s="22" t="s">
         <v>634</v>
@@ -4804,7 +4938,7 @@
         <v>52</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>53</v>
@@ -4836,7 +4970,7 @@
         <v>52</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>55</v>
@@ -4868,7 +5002,7 @@
         <v>52</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>57</v>
@@ -4900,7 +5034,7 @@
         <v>52</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>59</v>
@@ -4932,7 +5066,7 @@
         <v>52</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>61</v>
@@ -4964,7 +5098,7 @@
         <v>52</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>64</v>
@@ -4996,7 +5130,7 @@
         <v>52</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>66</v>
@@ -5028,7 +5162,7 @@
         <v>52</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>68</v>
@@ -5060,7 +5194,7 @@
         <v>52</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>71</v>
@@ -5092,7 +5226,7 @@
         <v>52</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>72</v>
@@ -5124,7 +5258,7 @@
         <v>52</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>74</v>
@@ -5156,7 +5290,7 @@
         <v>52</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>76</v>
@@ -5188,7 +5322,7 @@
         <v>52</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H33" s="8" t="s">
         <v>78</v>
@@ -5220,7 +5354,7 @@
         <v>635</v>
       </c>
       <c r="G34" s="22" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H34" s="22" t="s">
         <v>636</v>
@@ -5252,7 +5386,7 @@
         <v>637</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>638</v>
@@ -5284,7 +5418,7 @@
         <v>639</v>
       </c>
       <c r="G36" s="22" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H36" s="22" t="s">
         <v>178</v>
@@ -5316,7 +5450,7 @@
         <v>640</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>641</v>
@@ -5348,7 +5482,7 @@
         <v>13</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H38" s="4" t="s">
         <v>14</v>
@@ -5380,7 +5514,7 @@
         <v>13</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>16</v>
@@ -5412,7 +5546,7 @@
         <v>13</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H40" s="4" t="s">
         <v>20</v>
@@ -5444,7 +5578,7 @@
         <v>13</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>22</v>
@@ -5476,7 +5610,7 @@
         <v>13</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H42" s="4" t="s">
         <v>24</v>
@@ -5508,7 +5642,7 @@
         <v>13</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H43" s="4" t="s">
         <v>26</v>
@@ -5540,7 +5674,7 @@
         <v>13</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H44" s="4" t="s">
         <v>29</v>
@@ -5572,7 +5706,7 @@
         <v>13</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>31</v>
@@ -5604,7 +5738,7 @@
         <v>13</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H46" s="4" t="s">
         <v>34</v>
@@ -5636,7 +5770,7 @@
         <v>13</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H47" s="4" t="s">
         <v>37</v>
@@ -5668,7 +5802,7 @@
         <v>13</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H48" s="4" t="s">
         <v>38</v>
@@ -5700,7 +5834,7 @@
         <v>13</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H49" s="4" t="s">
         <v>39</v>
@@ -5732,7 +5866,7 @@
         <v>80</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>81</v>
@@ -5764,7 +5898,7 @@
         <v>80</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>83</v>
@@ -5796,7 +5930,7 @@
         <v>80</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>84</v>
@@ -5828,7 +5962,7 @@
         <v>80</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>85</v>
@@ -5860,7 +5994,7 @@
         <v>80</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H54" s="6" t="s">
         <v>86</v>
@@ -5892,7 +6026,7 @@
         <v>80</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>87</v>
@@ -5924,7 +6058,7 @@
         <v>80</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H56" s="6" t="s">
         <v>88</v>
@@ -5956,7 +6090,7 @@
         <v>80</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>89</v>
@@ -5988,7 +6122,7 @@
         <v>80</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H58" s="6" t="s">
         <v>90</v>
@@ -6020,7 +6154,7 @@
         <v>80</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H59" s="6" t="s">
         <v>91</v>
@@ -6052,7 +6186,7 @@
         <v>643</v>
       </c>
       <c r="G60" s="22" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H60" s="22" t="s">
         <v>155</v>
@@ -6084,7 +6218,7 @@
         <v>100</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H61" s="4" t="s">
         <v>101</v>
@@ -6116,7 +6250,7 @@
         <v>100</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H62" s="4" t="s">
         <v>102</v>
@@ -6148,7 +6282,7 @@
         <v>100</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H63" s="4" t="s">
         <v>103</v>
@@ -6180,7 +6314,7 @@
         <v>100</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H64" s="4" t="s">
         <v>104</v>
@@ -6212,7 +6346,7 @@
         <v>100</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H65" s="4" t="s">
         <v>105</v>
@@ -6244,7 +6378,7 @@
         <v>100</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H66" s="4" t="s">
         <v>106</v>
@@ -6276,7 +6410,7 @@
         <v>124</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H67" s="6" t="s">
         <v>112</v>
@@ -6308,7 +6442,7 @@
         <v>124</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>113</v>
@@ -6340,7 +6474,7 @@
         <v>124</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H69" s="6" t="s">
         <v>114</v>
@@ -6372,7 +6506,7 @@
         <v>124</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>115</v>
@@ -6404,7 +6538,7 @@
         <v>124</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>116</v>
@@ -6436,7 +6570,7 @@
         <v>124</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>118</v>
@@ -6468,7 +6602,7 @@
         <v>644</v>
       </c>
       <c r="G73" s="22" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H73" s="22" t="s">
         <v>645</v>
@@ -6500,7 +6634,7 @@
         <v>125</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H74" s="4" t="s">
         <v>126</v>
@@ -6532,7 +6666,7 @@
         <v>125</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H75" s="4" t="s">
         <v>127</v>
@@ -6564,7 +6698,7 @@
         <v>125</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H76" s="4" t="s">
         <v>128</v>
@@ -6596,7 +6730,7 @@
         <v>125</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H77" s="4" t="s">
         <v>129</v>
@@ -6628,7 +6762,7 @@
         <v>125</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H78" s="4" t="s">
         <v>130</v>
@@ -6660,7 +6794,7 @@
         <v>125</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H79" s="4" t="s">
         <v>131</v>
@@ -6692,7 +6826,7 @@
         <v>125</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H80" s="4" t="s">
         <v>132</v>
@@ -6724,7 +6858,7 @@
         <v>125</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H81" s="30" t="s">
         <v>770</v>
@@ -6756,7 +6890,7 @@
         <v>125</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H82" s="4" t="s">
         <v>133</v>
@@ -6788,7 +6922,7 @@
         <v>125</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H83" s="4" t="s">
         <v>134</v>
@@ -6820,7 +6954,7 @@
         <v>125</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H84" s="4" t="s">
         <v>135</v>
@@ -6852,7 +6986,7 @@
         <v>125</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H85" s="4" t="s">
         <v>136</v>
@@ -6884,7 +7018,7 @@
         <v>125</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H86" s="4" t="s">
         <v>137</v>
@@ -6916,7 +7050,7 @@
         <v>647</v>
       </c>
       <c r="G87" s="22" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H87" s="22" t="s">
         <v>177</v>
@@ -6948,7 +7082,7 @@
         <v>144</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H88" s="6" t="s">
         <v>145</v>
@@ -6980,7 +7114,7 @@
         <v>144</v>
       </c>
       <c r="G89" s="6" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H89" s="6" t="s">
         <v>146</v>
@@ -7012,7 +7146,7 @@
         <v>144</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H90" s="6" t="s">
         <v>147</v>
@@ -7044,7 +7178,7 @@
         <v>144</v>
       </c>
       <c r="G91" s="6" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H91" s="6" t="s">
         <v>148</v>
@@ -7076,7 +7210,7 @@
         <v>144</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H92" s="6" t="s">
         <v>149</v>
@@ -7108,7 +7242,7 @@
         <v>144</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H93" s="6" t="s">
         <v>150</v>
@@ -7140,7 +7274,7 @@
         <v>144</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H94" s="6" t="s">
         <v>151</v>
@@ -7172,7 +7306,7 @@
         <v>144</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H95" s="6" t="s">
         <v>152</v>
@@ -7204,7 +7338,7 @@
         <v>144</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H96" s="6" t="s">
         <v>154</v>
@@ -7236,7 +7370,7 @@
         <v>144</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H97" s="6" t="s">
         <v>155</v>
@@ -7268,7 +7402,7 @@
         <v>166</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H98" s="4" t="s">
         <v>160</v>
@@ -7300,7 +7434,7 @@
         <v>166</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H99" s="4" t="s">
         <v>161</v>
@@ -7332,7 +7466,7 @@
         <v>166</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H100" s="4" t="s">
         <v>126</v>
@@ -7364,7 +7498,7 @@
         <v>166</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H101" s="4" t="s">
         <v>162</v>
@@ -7396,7 +7530,7 @@
         <v>166</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H102" s="4" t="s">
         <v>163</v>
@@ -7428,7 +7562,7 @@
         <v>166</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H103" s="4" t="s">
         <v>117</v>
@@ -7460,7 +7594,7 @@
         <v>648</v>
       </c>
       <c r="G104" s="22" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H104" s="22" t="s">
         <v>405</v>
@@ -7492,7 +7626,7 @@
         <v>649</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H105" s="4" t="s">
         <v>650</v>
@@ -7524,7 +7658,7 @@
         <v>652</v>
       </c>
       <c r="G106" s="22" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H106" s="22" t="s">
         <v>653</v>
@@ -7556,7 +7690,7 @@
         <v>167</v>
       </c>
       <c r="G107" s="6" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H107" s="6" t="s">
         <v>168</v>
@@ -7588,7 +7722,7 @@
         <v>167</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H108" s="6" t="s">
         <v>170</v>
@@ -7620,7 +7754,7 @@
         <v>167</v>
       </c>
       <c r="G109" s="6" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H109" s="6" t="s">
         <v>172</v>
@@ -7652,7 +7786,7 @@
         <v>167</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H110" s="6" t="s">
         <v>173</v>
@@ -7684,7 +7818,7 @@
         <v>167</v>
       </c>
       <c r="G111" s="6" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H111" s="6" t="s">
         <v>175</v>
@@ -7716,7 +7850,7 @@
         <v>167</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H112" s="6" t="s">
         <v>117</v>
@@ -7748,7 +7882,7 @@
         <v>167</v>
       </c>
       <c r="G113" s="6" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H113" s="6" t="s">
         <v>177</v>
@@ -7780,7 +7914,7 @@
         <v>167</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H114" s="6" t="s">
         <v>178</v>
@@ -7812,7 +7946,7 @@
         <v>167</v>
       </c>
       <c r="G115" s="6" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H115" s="6" t="s">
         <v>50</v>
@@ -7844,7 +7978,7 @@
         <v>167</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H116" s="6" t="s">
         <v>105</v>
@@ -7876,7 +8010,7 @@
         <v>179</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H117" s="4" t="s">
         <v>180</v>
@@ -7908,7 +8042,7 @@
         <v>179</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H118" s="4" t="s">
         <v>181</v>
@@ -7940,7 +8074,7 @@
         <v>179</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H119" s="4" t="s">
         <v>182</v>
@@ -7972,7 +8106,7 @@
         <v>179</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H120" s="4" t="s">
         <v>183</v>
@@ -8004,7 +8138,7 @@
         <v>179</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H121" s="4" t="s">
         <v>184</v>
@@ -8036,7 +8170,7 @@
         <v>179</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H122" s="4" t="s">
         <v>194</v>
@@ -8068,7 +8202,7 @@
         <v>179</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H123" s="4" t="s">
         <v>172</v>
@@ -8100,7 +8234,7 @@
         <v>179</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H124" s="4" t="s">
         <v>185</v>
@@ -8132,7 +8266,7 @@
         <v>179</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H125" s="4" t="s">
         <v>186</v>
@@ -8164,7 +8298,7 @@
         <v>179</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H126" s="4" t="s">
         <v>188</v>
@@ -8196,7 +8330,7 @@
         <v>179</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H127" s="4" t="s">
         <v>189</v>
@@ -8228,7 +8362,7 @@
         <v>654</v>
       </c>
       <c r="G128" s="22" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H128" s="22" t="s">
         <v>655</v>
@@ -8260,7 +8394,7 @@
         <v>195</v>
       </c>
       <c r="G129" s="6" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H129" s="6" t="s">
         <v>196</v>
@@ -8292,7 +8426,7 @@
         <v>195</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H130" s="6" t="s">
         <v>197</v>
@@ -8324,7 +8458,7 @@
         <v>195</v>
       </c>
       <c r="G131" s="6" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H131" s="6" t="s">
         <v>198</v>
@@ -8356,7 +8490,7 @@
         <v>195</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H132" s="6" t="s">
         <v>150</v>
@@ -8388,7 +8522,7 @@
         <v>195</v>
       </c>
       <c r="G133" s="6" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H133" s="6" t="s">
         <v>50</v>
@@ -8420,7 +8554,7 @@
         <v>195</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H134" s="6" t="s">
         <v>199</v>
@@ -8452,7 +8586,7 @@
         <v>203</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H135" s="4" t="s">
         <v>204</v>
@@ -8484,7 +8618,7 @@
         <v>203</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H136" s="4" t="s">
         <v>118</v>
@@ -8516,7 +8650,7 @@
         <v>203</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H137" s="4" t="s">
         <v>205</v>
@@ -8548,7 +8682,7 @@
         <v>203</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H138" s="4" t="s">
         <v>206</v>
@@ -8580,7 +8714,7 @@
         <v>203</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H139" s="4" t="s">
         <v>208</v>
@@ -8612,7 +8746,7 @@
         <v>203</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H140" s="4" t="s">
         <v>209</v>
@@ -8644,7 +8778,7 @@
         <v>203</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H141" s="4" t="s">
         <v>210</v>
@@ -8676,7 +8810,7 @@
         <v>203</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H142" s="4" t="s">
         <v>211</v>
@@ -8708,7 +8842,7 @@
         <v>656</v>
       </c>
       <c r="G143" s="22" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H143" s="22" t="s">
         <v>222</v>
@@ -8740,7 +8874,7 @@
         <v>212</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H144" s="6" t="s">
         <v>112</v>
@@ -8772,7 +8906,7 @@
         <v>212</v>
       </c>
       <c r="G145" s="6" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H145" s="6" t="s">
         <v>57</v>
@@ -8804,7 +8938,7 @@
         <v>212</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H146" s="6" t="s">
         <v>213</v>
@@ -8836,7 +8970,7 @@
         <v>212</v>
       </c>
       <c r="G147" s="6" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H147" s="6" t="s">
         <v>214</v>
@@ -8868,7 +9002,7 @@
         <v>212</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H148" s="6" t="s">
         <v>217</v>
@@ -8900,7 +9034,7 @@
         <v>212</v>
       </c>
       <c r="G149" s="6" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H149" s="6" t="s">
         <v>215</v>
@@ -8932,7 +9066,7 @@
         <v>212</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H150" s="6" t="s">
         <v>216</v>
@@ -8964,7 +9098,7 @@
         <v>212</v>
       </c>
       <c r="G151" s="6" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H151" s="6" t="s">
         <v>90</v>
@@ -8996,7 +9130,7 @@
         <v>212</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H152" s="6" t="s">
         <v>218</v>
@@ -9028,7 +9162,7 @@
         <v>212</v>
       </c>
       <c r="G153" s="6" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H153" s="6" t="s">
         <v>219</v>
@@ -9060,7 +9194,7 @@
         <v>212</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H154" s="6" t="s">
         <v>220</v>
@@ -9092,7 +9226,7 @@
         <v>212</v>
       </c>
       <c r="G155" s="6" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H155" s="6" t="s">
         <v>221</v>
@@ -9124,7 +9258,7 @@
         <v>212</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H156" s="6" t="s">
         <v>103</v>
@@ -9156,7 +9290,7 @@
         <v>212</v>
       </c>
       <c r="G157" s="6" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H157" s="6" t="s">
         <v>222</v>
@@ -9188,7 +9322,7 @@
         <v>212</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H158" s="6" t="s">
         <v>205</v>
@@ -9220,7 +9354,7 @@
         <v>212</v>
       </c>
       <c r="G159" s="6" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H159" s="6" t="s">
         <v>178</v>
@@ -9252,7 +9386,7 @@
         <v>212</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H160" s="6" t="s">
         <v>207</v>
@@ -9284,7 +9418,7 @@
         <v>229</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H161" s="4" t="s">
         <v>351</v>
@@ -9316,7 +9450,7 @@
         <v>229</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H162" s="4" t="s">
         <v>230</v>
@@ -9348,7 +9482,7 @@
         <v>229</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H163" s="4" t="s">
         <v>231</v>
@@ -9380,7 +9514,7 @@
         <v>229</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H164" s="4" t="s">
         <v>233</v>
@@ -9412,7 +9546,7 @@
         <v>229</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H165" s="4" t="s">
         <v>117</v>
@@ -9444,7 +9578,7 @@
         <v>657</v>
       </c>
       <c r="G166" s="22" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H166" s="22" t="s">
         <v>72</v>
@@ -9476,7 +9610,7 @@
         <v>658</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H167" s="4" t="s">
         <v>254</v>
@@ -9508,7 +9642,7 @@
         <v>235</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H168" s="6" t="s">
         <v>187</v>
@@ -9540,7 +9674,7 @@
         <v>235</v>
       </c>
       <c r="G169" s="6" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H169" s="6" t="s">
         <v>236</v>
@@ -9572,7 +9706,7 @@
         <v>235</v>
       </c>
       <c r="G170" s="6" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H170" s="6" t="s">
         <v>132</v>
@@ -9604,7 +9738,7 @@
         <v>235</v>
       </c>
       <c r="G171" s="6" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H171" s="6" t="s">
         <v>222</v>
@@ -9636,7 +9770,7 @@
         <v>235</v>
       </c>
       <c r="G172" s="6" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H172" s="6" t="s">
         <v>178</v>
@@ -9668,7 +9802,7 @@
         <v>235</v>
       </c>
       <c r="G173" s="6" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H173" s="6" t="s">
         <v>105</v>
@@ -9700,7 +9834,7 @@
         <v>238</v>
       </c>
       <c r="G174" s="6" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H174" s="6" t="s">
         <v>117</v>
@@ -9732,7 +9866,7 @@
         <v>659</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H175" s="4" t="s">
         <v>246</v>
@@ -9764,7 +9898,7 @@
         <v>660</v>
       </c>
       <c r="G176" s="22" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H176" s="22" t="s">
         <v>661</v>
@@ -9796,7 +9930,7 @@
         <v>237</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H177" s="4" t="s">
         <v>239</v>
@@ -9828,7 +9962,7 @@
         <v>237</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H178" s="4" t="s">
         <v>173</v>
@@ -9860,7 +9994,7 @@
         <v>237</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H179" s="4" t="s">
         <v>161</v>
@@ -9892,7 +10026,7 @@
         <v>237</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H180" s="4" t="s">
         <v>240</v>
@@ -9924,7 +10058,7 @@
         <v>237</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H181" s="4" t="s">
         <v>241</v>
@@ -9956,7 +10090,7 @@
         <v>237</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H182" s="4" t="s">
         <v>243</v>
@@ -9988,7 +10122,7 @@
         <v>237</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H183" s="4" t="s">
         <v>81</v>
@@ -10020,7 +10154,7 @@
         <v>237</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H184" s="4" t="s">
         <v>244</v>
@@ -10052,7 +10186,7 @@
         <v>237</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H185" s="4" t="s">
         <v>133</v>
@@ -10084,7 +10218,7 @@
         <v>237</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H186" s="4" t="s">
         <v>151</v>
@@ -10116,7 +10250,7 @@
         <v>237</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H187" s="4" t="s">
         <v>245</v>
@@ -10148,7 +10282,7 @@
         <v>237</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H188" s="4" t="s">
         <v>155</v>
@@ -10180,7 +10314,7 @@
         <v>237</v>
       </c>
       <c r="G189" s="4" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H189" s="4" t="s">
         <v>246</v>
@@ -10212,7 +10346,7 @@
         <v>237</v>
       </c>
       <c r="G190" s="4" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H190" s="4" t="s">
         <v>247</v>
@@ -10244,7 +10378,7 @@
         <v>249</v>
       </c>
       <c r="G191" s="6" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H191" s="6" t="s">
         <v>250</v>
@@ -10276,7 +10410,7 @@
         <v>249</v>
       </c>
       <c r="G192" s="6" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H192" s="6" t="s">
         <v>251</v>
@@ -10308,7 +10442,7 @@
         <v>249</v>
       </c>
       <c r="G193" s="6" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H193" s="6" t="s">
         <v>45</v>
@@ -10340,7 +10474,7 @@
         <v>249</v>
       </c>
       <c r="G194" s="6" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H194" s="6" t="s">
         <v>252</v>
@@ -10372,7 +10506,7 @@
         <v>249</v>
       </c>
       <c r="G195" s="6" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H195" s="6" t="s">
         <v>253</v>
@@ -10404,7 +10538,7 @@
         <v>249</v>
       </c>
       <c r="G196" s="6" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H196" s="6" t="s">
         <v>222</v>
@@ -10436,7 +10570,7 @@
         <v>249</v>
       </c>
       <c r="G197" s="6" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H197" s="6" t="s">
         <v>254</v>
@@ -10468,7 +10602,7 @@
         <v>259</v>
       </c>
       <c r="G198" s="4" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H198" s="4" t="s">
         <v>260</v>
@@ -10500,7 +10634,7 @@
         <v>259</v>
       </c>
       <c r="G199" s="4" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H199" s="4" t="s">
         <v>262</v>
@@ -10532,7 +10666,7 @@
         <v>259</v>
       </c>
       <c r="G200" s="4" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H200" s="4" t="s">
         <v>264</v>
@@ -10564,7 +10698,7 @@
         <v>259</v>
       </c>
       <c r="G201" s="4" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H201" s="4" t="s">
         <v>266</v>
@@ -10596,7 +10730,7 @@
         <v>268</v>
       </c>
       <c r="G202" s="6" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H202" s="6" t="s">
         <v>42</v>
@@ -10628,7 +10762,7 @@
         <v>268</v>
       </c>
       <c r="G203" s="6" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H203" s="6" t="s">
         <v>293</v>
@@ -10660,7 +10794,7 @@
         <v>268</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H204" s="6" t="s">
         <v>46</v>
@@ -10692,7 +10826,7 @@
         <v>268</v>
       </c>
       <c r="G205" s="6" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H205" s="6" t="s">
         <v>296</v>
@@ -10724,7 +10858,7 @@
         <v>268</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H206" s="6" t="s">
         <v>298</v>
@@ -10756,7 +10890,7 @@
         <v>268</v>
       </c>
       <c r="G207" s="6" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H207" s="6" t="s">
         <v>74</v>
@@ -10788,7 +10922,7 @@
         <v>268</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H208" s="6" t="s">
         <v>19</v>
@@ -10820,7 +10954,7 @@
         <v>268</v>
       </c>
       <c r="G209" s="6" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H209" s="7" t="s">
         <v>299</v>
@@ -10852,7 +10986,7 @@
         <v>268</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H210" s="6" t="s">
         <v>300</v>
@@ -10884,7 +11018,7 @@
         <v>268</v>
       </c>
       <c r="G211" s="6" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H211" s="6" t="s">
         <v>302</v>
@@ -10916,7 +11050,7 @@
         <v>268</v>
       </c>
       <c r="G212" s="6" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H212" s="6" t="s">
         <v>116</v>
@@ -10948,7 +11082,7 @@
         <v>268</v>
       </c>
       <c r="G213" s="6" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H213" s="6" t="s">
         <v>304</v>
@@ -10980,7 +11114,7 @@
         <v>435</v>
       </c>
       <c r="G214" s="13" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H214" s="13" t="s">
         <v>436</v>
@@ -11172,7 +11306,7 @@
         <v>663</v>
       </c>
       <c r="G220" s="22" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H220" s="22" t="s">
         <v>664</v>
@@ -11204,7 +11338,7 @@
         <v>269</v>
       </c>
       <c r="G221" s="4" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H221" s="4" t="s">
         <v>270</v>
@@ -11236,7 +11370,7 @@
         <v>269</v>
       </c>
       <c r="G222" s="4" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H222" s="4" t="s">
         <v>271</v>
@@ -11268,7 +11402,7 @@
         <v>269</v>
       </c>
       <c r="G223" s="4" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H223" s="4" t="s">
         <v>272</v>
@@ -11300,7 +11434,7 @@
         <v>269</v>
       </c>
       <c r="G224" s="4" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H224" s="4" t="s">
         <v>273</v>
@@ -11332,7 +11466,7 @@
         <v>269</v>
       </c>
       <c r="G225" s="4" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H225" s="4" t="s">
         <v>274</v>
@@ -11364,7 +11498,7 @@
         <v>269</v>
       </c>
       <c r="G226" s="4" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H226" s="4" t="s">
         <v>275</v>
@@ -11396,7 +11530,7 @@
         <v>269</v>
       </c>
       <c r="G227" s="4" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H227" s="4" t="s">
         <v>276</v>
@@ -11428,7 +11562,7 @@
         <v>665</v>
       </c>
       <c r="G228" s="22" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H228" s="22" t="s">
         <v>666</v>
@@ -11460,7 +11594,7 @@
         <v>668</v>
       </c>
       <c r="G229" s="4" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H229" s="4" t="s">
         <v>669</v>
@@ -11492,7 +11626,7 @@
         <v>280</v>
       </c>
       <c r="G230" s="6" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H230" s="6" t="s">
         <v>112</v>
@@ -11524,7 +11658,7 @@
         <v>280</v>
       </c>
       <c r="G231" s="6" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H231" s="6" t="s">
         <v>28</v>
@@ -11556,7 +11690,7 @@
         <v>280</v>
       </c>
       <c r="G232" s="6" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H232" s="6" t="s">
         <v>281</v>
@@ -11588,7 +11722,7 @@
         <v>280</v>
       </c>
       <c r="G233" s="6" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H233" s="6" t="s">
         <v>282</v>
@@ -11620,7 +11754,7 @@
         <v>280</v>
       </c>
       <c r="G234" s="6" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H234" s="6" t="s">
         <v>283</v>
@@ -11652,7 +11786,7 @@
         <v>280</v>
       </c>
       <c r="G235" s="6" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H235" s="6" t="s">
         <v>284</v>
@@ -11684,7 +11818,7 @@
         <v>280</v>
       </c>
       <c r="G236" s="6" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H236" s="6" t="s">
         <v>285</v>
@@ -11716,7 +11850,7 @@
         <v>280</v>
       </c>
       <c r="G237" s="6" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H237" s="6" t="s">
         <v>153</v>
@@ -11748,7 +11882,7 @@
         <v>280</v>
       </c>
       <c r="G238" s="6" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H238" s="6" t="s">
         <v>83</v>
@@ -11780,7 +11914,7 @@
         <v>280</v>
       </c>
       <c r="G239" s="6" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H239" s="6" t="s">
         <v>286</v>
@@ -11812,7 +11946,7 @@
         <v>280</v>
       </c>
       <c r="G240" s="6" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H240" s="6" t="s">
         <v>287</v>
@@ -11844,7 +11978,7 @@
         <v>280</v>
       </c>
       <c r="G241" s="6" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H241" s="6" t="s">
         <v>117</v>
@@ -11876,7 +12010,7 @@
         <v>305</v>
       </c>
       <c r="G242" s="4" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H242" s="4" t="s">
         <v>145</v>
@@ -11908,7 +12042,7 @@
         <v>305</v>
       </c>
       <c r="G243" s="4" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H243" s="4" t="s">
         <v>106</v>
@@ -11940,7 +12074,7 @@
         <v>305</v>
       </c>
       <c r="G244" s="4" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H244" s="4" t="s">
         <v>222</v>
@@ -11972,7 +12106,7 @@
         <v>305</v>
       </c>
       <c r="G245" s="4" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H245" s="4" t="s">
         <v>155</v>
@@ -12004,7 +12138,7 @@
         <v>671</v>
       </c>
       <c r="G246" s="22" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H246" s="22" t="s">
         <v>672</v>
@@ -12036,7 +12170,7 @@
         <v>674</v>
       </c>
       <c r="G247" s="4" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H247" s="4" t="s">
         <v>675</v>
@@ -12068,7 +12202,7 @@
         <v>676</v>
       </c>
       <c r="G248" s="22" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H248" s="22" t="s">
         <v>478</v>
@@ -12100,7 +12234,7 @@
         <v>677</v>
       </c>
       <c r="G249" s="4" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H249" s="4" t="s">
         <v>678</v>
@@ -12132,7 +12266,7 @@
         <v>679</v>
       </c>
       <c r="G250" s="22" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H250" s="22" t="s">
         <v>574</v>
@@ -12164,7 +12298,7 @@
         <v>306</v>
       </c>
       <c r="G251" s="6" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H251" s="6" t="s">
         <v>308</v>
@@ -12196,7 +12330,7 @@
         <v>306</v>
       </c>
       <c r="G252" s="6" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H252" s="6" t="s">
         <v>309</v>
@@ -12228,7 +12362,7 @@
         <v>306</v>
       </c>
       <c r="G253" s="6" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H253" s="6" t="s">
         <v>310</v>
@@ -12260,7 +12394,7 @@
         <v>306</v>
       </c>
       <c r="G254" s="6" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H254" s="6" t="s">
         <v>311</v>
@@ -12292,7 +12426,7 @@
         <v>306</v>
       </c>
       <c r="G255" s="6" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H255" s="6" t="s">
         <v>312</v>
@@ -12324,7 +12458,7 @@
         <v>306</v>
       </c>
       <c r="G256" s="6" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H256" s="6" t="s">
         <v>313</v>
@@ -12356,7 +12490,7 @@
         <v>306</v>
       </c>
       <c r="G257" s="6" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H257" s="6" t="s">
         <v>314</v>
@@ -12388,7 +12522,7 @@
         <v>306</v>
       </c>
       <c r="G258" s="6" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H258" s="6" t="s">
         <v>315</v>
@@ -12420,7 +12554,7 @@
         <v>306</v>
       </c>
       <c r="G259" s="6" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H259" s="6" t="s">
         <v>316</v>
@@ -12452,7 +12586,7 @@
         <v>306</v>
       </c>
       <c r="G260" s="6" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H260" s="6" t="s">
         <v>317</v>
@@ -12484,7 +12618,7 @@
         <v>306</v>
       </c>
       <c r="G261" s="6" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H261" s="6" t="s">
         <v>318</v>
@@ -12516,7 +12650,7 @@
         <v>306</v>
       </c>
       <c r="G262" s="6" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H262" s="6" t="s">
         <v>319</v>
@@ -12548,7 +12682,7 @@
         <v>335</v>
       </c>
       <c r="G263" s="4" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H263" s="4" t="s">
         <v>181</v>
@@ -12580,7 +12714,7 @@
         <v>320</v>
       </c>
       <c r="G264" s="4" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H264" s="4" t="s">
         <v>321</v>
@@ -12612,7 +12746,7 @@
         <v>320</v>
       </c>
       <c r="G265" s="4" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H265" s="4" t="s">
         <v>172</v>
@@ -12644,7 +12778,7 @@
         <v>320</v>
       </c>
       <c r="G266" s="4" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H266" s="4" t="s">
         <v>222</v>
@@ -12676,7 +12810,7 @@
         <v>320</v>
       </c>
       <c r="G267" s="4" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H267" s="4" t="s">
         <v>254</v>
@@ -12708,7 +12842,7 @@
         <v>320</v>
       </c>
       <c r="G268" s="4" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H268" s="4" t="s">
         <v>117</v>
@@ -12740,7 +12874,7 @@
         <v>334</v>
       </c>
       <c r="G269" s="6" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H269" s="6" t="s">
         <v>242</v>
@@ -12772,7 +12906,7 @@
         <v>322</v>
       </c>
       <c r="G270" s="6" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H270" s="6" t="s">
         <v>113</v>
@@ -12804,7 +12938,7 @@
         <v>322</v>
       </c>
       <c r="G271" s="6" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H271" s="6" t="s">
         <v>323</v>
@@ -12836,7 +12970,7 @@
         <v>322</v>
       </c>
       <c r="G272" s="6" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H272" s="6" t="s">
         <v>151</v>
@@ -12868,7 +13002,7 @@
         <v>322</v>
       </c>
       <c r="G273" s="6" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H273" s="6" t="s">
         <v>324</v>
@@ -12900,7 +13034,7 @@
         <v>322</v>
       </c>
       <c r="G274" s="6" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H274" s="6" t="s">
         <v>325</v>
@@ -12932,7 +13066,7 @@
         <v>322</v>
       </c>
       <c r="G275" s="6" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H275" s="6" t="s">
         <v>254</v>
@@ -12964,7 +13098,7 @@
         <v>328</v>
       </c>
       <c r="G276" s="4" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H276" s="4" t="s">
         <v>210</v>
@@ -12996,7 +13130,7 @@
         <v>328</v>
       </c>
       <c r="G277" s="4" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H277" s="4" t="s">
         <v>329</v>
@@ -13028,7 +13162,7 @@
         <v>328</v>
       </c>
       <c r="G278" s="4" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H278" s="4" t="s">
         <v>330</v>
@@ -13060,7 +13194,7 @@
         <v>328</v>
       </c>
       <c r="G279" s="4" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H279" s="4" t="s">
         <v>211</v>
@@ -13092,7 +13226,7 @@
         <v>328</v>
       </c>
       <c r="G280" s="4" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H280" s="4" t="s">
         <v>331</v>
@@ -13124,7 +13258,7 @@
         <v>328</v>
       </c>
       <c r="G281" s="4" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H281" s="4" t="s">
         <v>332</v>
@@ -13156,7 +13290,7 @@
         <v>328</v>
       </c>
       <c r="G282" s="4" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H282" s="4" t="s">
         <v>333</v>
@@ -13188,7 +13322,7 @@
         <v>328</v>
       </c>
       <c r="G283" s="4" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H283" s="4" t="s">
         <v>204</v>
@@ -13220,7 +13354,7 @@
         <v>328</v>
       </c>
       <c r="G284" s="4" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H284" s="4" t="s">
         <v>209</v>
@@ -13252,7 +13386,7 @@
         <v>328</v>
       </c>
       <c r="G285" s="4" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H285" s="4" t="s">
         <v>118</v>
@@ -13284,7 +13418,7 @@
         <v>681</v>
       </c>
       <c r="G286" s="22" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H286" s="22" t="s">
         <v>682</v>
@@ -13316,7 +13450,7 @@
         <v>680</v>
       </c>
       <c r="G287" s="4" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H287" s="4" t="s">
         <v>339</v>
@@ -13348,7 +13482,7 @@
         <v>684</v>
       </c>
       <c r="G288" s="22" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H288" s="22" t="s">
         <v>613</v>
@@ -13380,7 +13514,7 @@
         <v>685</v>
       </c>
       <c r="G289" s="4" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H289" s="4" t="s">
         <v>686</v>
@@ -13412,7 +13546,7 @@
         <v>336</v>
       </c>
       <c r="G290" s="6" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H290" s="6" t="s">
         <v>337</v>
@@ -13444,7 +13578,7 @@
         <v>336</v>
       </c>
       <c r="G291" s="6" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H291" s="6" t="s">
         <v>338</v>
@@ -13476,7 +13610,7 @@
         <v>336</v>
       </c>
       <c r="G292" s="6" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H292" s="6" t="s">
         <v>83</v>
@@ -13508,7 +13642,7 @@
         <v>336</v>
       </c>
       <c r="G293" s="6" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H293" s="6" t="s">
         <v>221</v>
@@ -13540,7 +13674,7 @@
         <v>336</v>
       </c>
       <c r="G294" s="6" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H294" s="6" t="s">
         <v>222</v>
@@ -13572,7 +13706,7 @@
         <v>336</v>
       </c>
       <c r="G295" s="6" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H295" s="6" t="s">
         <v>339</v>
@@ -13604,7 +13738,7 @@
         <v>336</v>
       </c>
       <c r="G296" s="6" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H296" s="6" t="s">
         <v>254</v>
@@ -13636,7 +13770,7 @@
         <v>342</v>
       </c>
       <c r="G297" s="4" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H297" s="4" t="s">
         <v>343</v>
@@ -13668,7 +13802,7 @@
         <v>342</v>
       </c>
       <c r="G298" s="4" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H298" s="4" t="s">
         <v>161</v>
@@ -13700,7 +13834,7 @@
         <v>342</v>
       </c>
       <c r="G299" s="4" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H299" s="4" t="s">
         <v>344</v>
@@ -13732,7 +13866,7 @@
         <v>342</v>
       </c>
       <c r="G300" s="4" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H300" s="4" t="s">
         <v>104</v>
@@ -13764,7 +13898,7 @@
         <v>342</v>
       </c>
       <c r="G301" s="4" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H301" s="4" t="s">
         <v>345</v>
@@ -13796,7 +13930,7 @@
         <v>342</v>
       </c>
       <c r="G302" s="4" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H302" s="4" t="s">
         <v>147</v>
@@ -13828,7 +13962,7 @@
         <v>342</v>
       </c>
       <c r="G303" s="4" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H303" s="4" t="s">
         <v>115</v>
@@ -13860,7 +13994,7 @@
         <v>342</v>
       </c>
       <c r="G304" s="4" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H304" s="4" t="s">
         <v>84</v>
@@ -13892,7 +14026,7 @@
         <v>342</v>
       </c>
       <c r="G305" s="4" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H305" s="4" t="s">
         <v>236</v>
@@ -13924,7 +14058,7 @@
         <v>342</v>
       </c>
       <c r="G306" s="4" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H306" s="4" t="s">
         <v>275</v>
@@ -13956,7 +14090,7 @@
         <v>342</v>
       </c>
       <c r="G307" s="4" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H307" s="4" t="s">
         <v>346</v>
@@ -13988,7 +14122,7 @@
         <v>347</v>
       </c>
       <c r="G308" s="6" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H308" s="6" t="s">
         <v>348</v>
@@ -14020,7 +14154,7 @@
         <v>347</v>
       </c>
       <c r="G309" s="6" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H309" s="6" t="s">
         <v>349</v>
@@ -14052,7 +14186,7 @@
         <v>347</v>
       </c>
       <c r="G310" s="6" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H310" s="6" t="s">
         <v>350</v>
@@ -14084,7 +14218,7 @@
         <v>347</v>
       </c>
       <c r="G311" s="6" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H311" s="6" t="s">
         <v>351</v>
@@ -14116,7 +14250,7 @@
         <v>347</v>
       </c>
       <c r="G312" s="6" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H312" s="6" t="s">
         <v>352</v>
@@ -14148,7 +14282,7 @@
         <v>347</v>
       </c>
       <c r="G313" s="6" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H313" s="6" t="s">
         <v>353</v>
@@ -14180,7 +14314,7 @@
         <v>347</v>
       </c>
       <c r="G314" s="6" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H314" s="9">
         <v>1999</v>
@@ -14212,7 +14346,7 @@
         <v>347</v>
       </c>
       <c r="G315" s="6" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H315" s="6" t="s">
         <v>354</v>
@@ -14244,7 +14378,7 @@
         <v>347</v>
       </c>
       <c r="G316" s="6" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H316" s="6" t="s">
         <v>355</v>
@@ -14276,7 +14410,7 @@
         <v>347</v>
       </c>
       <c r="G317" s="6" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H317" s="6" t="s">
         <v>356</v>
@@ -14308,7 +14442,7 @@
         <v>347</v>
       </c>
       <c r="G318" s="6" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H318" s="6" t="s">
         <v>357</v>
@@ -14340,7 +14474,7 @@
         <v>687</v>
       </c>
       <c r="G319" s="22" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H319" s="22" t="s">
         <v>688</v>
@@ -14372,7 +14506,7 @@
         <v>689</v>
       </c>
       <c r="G320" s="4" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H320" s="4" t="s">
         <v>53</v>
@@ -14404,7 +14538,7 @@
         <v>691</v>
       </c>
       <c r="G321" s="22" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H321" s="22" t="s">
         <v>692</v>
@@ -14436,7 +14570,7 @@
         <v>358</v>
       </c>
       <c r="G322" s="4" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H322" s="4" t="s">
         <v>160</v>
@@ -14468,7 +14602,7 @@
         <v>358</v>
       </c>
       <c r="G323" s="4" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H323" s="4" t="s">
         <v>359</v>
@@ -14500,7 +14634,7 @@
         <v>358</v>
       </c>
       <c r="G324" s="4" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H324" s="4" t="s">
         <v>45</v>
@@ -14532,7 +14666,7 @@
         <v>358</v>
       </c>
       <c r="G325" s="4" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H325" s="4" t="s">
         <v>360</v>
@@ -14564,7 +14698,7 @@
         <v>358</v>
       </c>
       <c r="G326" s="4" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H326" s="4" t="s">
         <v>361</v>
@@ -14596,7 +14730,7 @@
         <v>358</v>
       </c>
       <c r="G327" s="4" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H327" s="4" t="s">
         <v>362</v>
@@ -14628,7 +14762,7 @@
         <v>358</v>
       </c>
       <c r="G328" s="4" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H328" s="4" t="s">
         <v>363</v>
@@ -14660,7 +14794,7 @@
         <v>358</v>
       </c>
       <c r="G329" s="4" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H329" s="4" t="s">
         <v>364</v>
@@ -14692,7 +14826,7 @@
         <v>358</v>
       </c>
       <c r="G330" s="4" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H330" s="4" t="s">
         <v>365</v>
@@ -14724,7 +14858,7 @@
         <v>358</v>
       </c>
       <c r="G331" s="4" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H331" s="4" t="s">
         <v>366</v>
@@ -14756,7 +14890,7 @@
         <v>358</v>
       </c>
       <c r="G332" s="4" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H332" s="4" t="s">
         <v>219</v>
@@ -14788,7 +14922,7 @@
         <v>358</v>
       </c>
       <c r="G333" s="4" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H333" s="4" t="s">
         <v>367</v>
@@ -14820,7 +14954,7 @@
         <v>693</v>
       </c>
       <c r="G334" s="22" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H334" s="22" t="s">
         <v>366</v>
@@ -14852,7 +14986,7 @@
         <v>371</v>
       </c>
       <c r="G335" s="6" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H335" s="6" t="s">
         <v>8</v>
@@ -14884,7 +15018,7 @@
         <v>371</v>
       </c>
       <c r="G336" s="6" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H336" s="6" t="s">
         <v>250</v>
@@ -14916,7 +15050,7 @@
         <v>371</v>
       </c>
       <c r="G337" s="6" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H337" s="6" t="s">
         <v>102</v>
@@ -14948,7 +15082,7 @@
         <v>371</v>
       </c>
       <c r="G338" s="6" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H338" s="6" t="s">
         <v>245</v>
@@ -14980,7 +15114,7 @@
         <v>371</v>
       </c>
       <c r="G339" s="6" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H339" s="6" t="s">
         <v>49</v>
@@ -15012,7 +15146,7 @@
         <v>371</v>
       </c>
       <c r="G340" s="6" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H340" s="6" t="s">
         <v>372</v>
@@ -15044,7 +15178,7 @@
         <v>371</v>
       </c>
       <c r="G341" s="6" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H341" s="6" t="s">
         <v>373</v>
@@ -15076,7 +15210,7 @@
         <v>371</v>
       </c>
       <c r="G342" s="6" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H342" s="6" t="s">
         <v>374</v>
@@ -15108,7 +15242,7 @@
         <v>371</v>
       </c>
       <c r="G343" s="6" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H343" s="6" t="s">
         <v>375</v>
@@ -15140,7 +15274,7 @@
         <v>371</v>
       </c>
       <c r="G344" s="6" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H344" s="6" t="s">
         <v>137</v>
@@ -15172,7 +15306,7 @@
         <v>371</v>
       </c>
       <c r="G345" s="6" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H345" s="6" t="s">
         <v>222</v>
@@ -15204,7 +15338,7 @@
         <v>371</v>
       </c>
       <c r="G346" s="6" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H346" s="6" t="s">
         <v>105</v>
@@ -15236,7 +15370,7 @@
         <v>371</v>
       </c>
       <c r="G347" s="6" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H347" s="6" t="s">
         <v>117</v>
@@ -15268,7 +15402,7 @@
         <v>694</v>
       </c>
       <c r="G348" s="22" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H348" s="22" t="s">
         <v>695</v>
@@ -15300,7 +15434,7 @@
         <v>696</v>
       </c>
       <c r="G349" s="4" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H349" s="4" t="s">
         <v>697</v>
@@ -15332,7 +15466,7 @@
         <v>698</v>
       </c>
       <c r="G350" s="22" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H350" s="22" t="s">
         <v>699</v>
@@ -15364,7 +15498,7 @@
         <v>700</v>
       </c>
       <c r="G351" s="4" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H351" s="4" t="s">
         <v>701</v>
@@ -15396,7 +15530,7 @@
         <v>702</v>
       </c>
       <c r="G352" s="22" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H352" s="22" t="s">
         <v>611</v>
@@ -15428,7 +15562,7 @@
         <v>703</v>
       </c>
       <c r="G353" s="4" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H353" s="4" t="s">
         <v>386</v>
@@ -15460,7 +15594,7 @@
         <v>704</v>
       </c>
       <c r="G354" s="22" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H354" s="22" t="s">
         <v>161</v>
@@ -15492,7 +15626,7 @@
         <v>376</v>
       </c>
       <c r="G355" s="4" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H355" s="29" t="s">
         <v>769</v>
@@ -15524,7 +15658,7 @@
         <v>599</v>
       </c>
       <c r="G356" s="13" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H356" s="13" t="s">
         <v>600</v>
@@ -15556,7 +15690,7 @@
         <v>599</v>
       </c>
       <c r="G357" s="13" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H357" s="13" t="s">
         <v>610</v>
@@ -15588,7 +15722,7 @@
         <v>599</v>
       </c>
       <c r="G358" s="13" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H358" s="13" t="s">
         <v>611</v>
@@ -15620,7 +15754,7 @@
         <v>599</v>
       </c>
       <c r="G359" s="13" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H359" s="13" t="s">
         <v>612</v>
@@ -15652,7 +15786,7 @@
         <v>599</v>
       </c>
       <c r="G360" s="13" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H360" s="13" t="s">
         <v>613</v>
@@ -15684,7 +15818,7 @@
         <v>377</v>
       </c>
       <c r="G361" s="6" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H361" s="6" t="s">
         <v>378</v>
@@ -15716,7 +15850,7 @@
         <v>377</v>
       </c>
       <c r="G362" s="6" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H362" s="6" t="s">
         <v>380</v>
@@ -15748,7 +15882,7 @@
         <v>377</v>
       </c>
       <c r="G363" s="6" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H363" s="6" t="s">
         <v>59</v>
@@ -15780,7 +15914,7 @@
         <v>377</v>
       </c>
       <c r="G364" s="6" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H364" s="6" t="s">
         <v>273</v>
@@ -15812,7 +15946,7 @@
         <v>377</v>
       </c>
       <c r="G365" s="6" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H365" s="6" t="s">
         <v>387</v>
@@ -15844,7 +15978,7 @@
         <v>377</v>
       </c>
       <c r="G366" s="6" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H366" s="6" t="s">
         <v>383</v>
@@ -15876,7 +16010,7 @@
         <v>377</v>
       </c>
       <c r="G367" s="6" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H367" s="6" t="s">
         <v>385</v>
@@ -15908,7 +16042,7 @@
         <v>377</v>
       </c>
       <c r="G368" s="6" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H368" s="6" t="s">
         <v>137</v>
@@ -15940,7 +16074,7 @@
         <v>377</v>
       </c>
       <c r="G369" s="6" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H369" s="6" t="s">
         <v>386</v>
@@ -15972,7 +16106,7 @@
         <v>389</v>
       </c>
       <c r="G370" s="11" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H370" s="11" t="s">
         <v>270</v>
@@ -16004,7 +16138,7 @@
         <v>389</v>
       </c>
       <c r="G371" s="11" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H371" s="11" t="s">
         <v>242</v>
@@ -16036,7 +16170,7 @@
         <v>389</v>
       </c>
       <c r="G372" s="11" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H372" s="11" t="s">
         <v>390</v>
@@ -16068,7 +16202,7 @@
         <v>389</v>
       </c>
       <c r="G373" s="11" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H373" s="11" t="s">
         <v>222</v>
@@ -16100,7 +16234,7 @@
         <v>389</v>
       </c>
       <c r="G374" s="11" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H374" s="11" t="s">
         <v>391</v>
@@ -16132,7 +16266,7 @@
         <v>389</v>
       </c>
       <c r="G375" s="11" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H375" s="11" t="s">
         <v>103</v>
@@ -16164,7 +16298,7 @@
         <v>389</v>
       </c>
       <c r="G376" s="11" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H376" s="11" t="s">
         <v>392</v>
@@ -16196,7 +16330,7 @@
         <v>389</v>
       </c>
       <c r="G377" s="11" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H377" s="11" t="s">
         <v>282</v>
@@ -16228,7 +16362,7 @@
         <v>389</v>
       </c>
       <c r="G378" s="11" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H378" s="11" t="s">
         <v>253</v>
@@ -16260,7 +16394,7 @@
         <v>389</v>
       </c>
       <c r="G379" s="11" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H379" s="11" t="s">
         <v>395</v>
@@ -16292,7 +16426,7 @@
         <v>389</v>
       </c>
       <c r="G380" s="11" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H380" s="11" t="s">
         <v>115</v>
@@ -16324,7 +16458,7 @@
         <v>705</v>
       </c>
       <c r="G381" s="22" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H381" s="22" t="s">
         <v>415</v>
@@ -16356,7 +16490,7 @@
         <v>706</v>
       </c>
       <c r="G382" s="22" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H382" s="22" t="s">
         <v>64</v>
@@ -16388,7 +16522,7 @@
         <v>396</v>
       </c>
       <c r="G383" s="6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H383" s="6" t="s">
         <v>87</v>
@@ -16420,7 +16554,7 @@
         <v>396</v>
       </c>
       <c r="G384" s="6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H384" s="6" t="s">
         <v>271</v>
@@ -16452,7 +16586,7 @@
         <v>396</v>
       </c>
       <c r="G385" s="6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H385" s="6" t="s">
         <v>132</v>
@@ -16484,7 +16618,7 @@
         <v>396</v>
       </c>
       <c r="G386" s="6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H386" s="6" t="s">
         <v>398</v>
@@ -16516,7 +16650,7 @@
         <v>396</v>
       </c>
       <c r="G387" s="6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H387" s="6" t="s">
         <v>312</v>
@@ -16548,7 +16682,7 @@
         <v>396</v>
       </c>
       <c r="G388" s="6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H388" s="6" t="s">
         <v>399</v>
@@ -16580,7 +16714,7 @@
         <v>396</v>
       </c>
       <c r="G389" s="6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H389" s="6" t="s">
         <v>400</v>
@@ -16612,7 +16746,7 @@
         <v>396</v>
       </c>
       <c r="G390" s="6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H390" s="6" t="s">
         <v>372</v>
@@ -16644,7 +16778,7 @@
         <v>396</v>
       </c>
       <c r="G391" s="6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H391" s="6" t="s">
         <v>401</v>
@@ -16676,7 +16810,7 @@
         <v>396</v>
       </c>
       <c r="G392" s="6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H392" s="6" t="s">
         <v>345</v>
@@ -16708,7 +16842,7 @@
         <v>396</v>
       </c>
       <c r="G393" s="6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H393" s="6" t="s">
         <v>155</v>
@@ -16740,7 +16874,7 @@
         <v>396</v>
       </c>
       <c r="G394" s="6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H394" s="6" t="s">
         <v>403</v>
@@ -16772,7 +16906,7 @@
         <v>404</v>
       </c>
       <c r="G395" s="11" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H395" s="11" t="s">
         <v>405</v>
@@ -16804,7 +16938,7 @@
         <v>404</v>
       </c>
       <c r="G396" s="11" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H396" s="11" t="s">
         <v>407</v>
@@ -16836,7 +16970,7 @@
         <v>404</v>
       </c>
       <c r="G397" s="11" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H397" s="11" t="s">
         <v>409</v>
@@ -16868,7 +17002,7 @@
         <v>404</v>
       </c>
       <c r="G398" s="11" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H398" s="11" t="s">
         <v>84</v>
@@ -16900,7 +17034,7 @@
         <v>404</v>
       </c>
       <c r="G399" s="11" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H399" s="11" t="s">
         <v>410</v>
@@ -16932,7 +17066,7 @@
         <v>404</v>
       </c>
       <c r="G400" s="11" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H400" s="11" t="s">
         <v>284</v>
@@ -16964,7 +17098,7 @@
         <v>404</v>
       </c>
       <c r="G401" s="11" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H401" s="11" t="s">
         <v>412</v>
@@ -16996,7 +17130,7 @@
         <v>404</v>
       </c>
       <c r="G402" s="11" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H402" s="11" t="s">
         <v>363</v>
@@ -17028,7 +17162,7 @@
         <v>404</v>
       </c>
       <c r="G403" s="11" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H403" s="11" t="s">
         <v>414</v>
@@ -17060,7 +17194,7 @@
         <v>404</v>
       </c>
       <c r="G404" s="11" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H404" s="11" t="s">
         <v>319</v>
@@ -17092,7 +17226,7 @@
         <v>404</v>
       </c>
       <c r="G405" s="11" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H405" s="11" t="s">
         <v>415</v>
@@ -17124,7 +17258,7 @@
         <v>416</v>
       </c>
       <c r="G406" s="6" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H406" s="6" t="s">
         <v>220</v>
@@ -17156,7 +17290,7 @@
         <v>416</v>
       </c>
       <c r="G407" s="6" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H407" s="6" t="s">
         <v>344</v>
@@ -17188,7 +17322,7 @@
         <v>416</v>
       </c>
       <c r="G408" s="6" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H408" s="6" t="s">
         <v>187</v>
@@ -17220,7 +17354,7 @@
         <v>416</v>
       </c>
       <c r="G409" s="6" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H409" s="6" t="s">
         <v>385</v>
@@ -17252,7 +17386,7 @@
         <v>416</v>
       </c>
       <c r="G410" s="6" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H410" s="6" t="s">
         <v>417</v>
@@ -17284,7 +17418,7 @@
         <v>416</v>
       </c>
       <c r="G411" s="6" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H411" s="6" t="s">
         <v>418</v>
@@ -17316,7 +17450,7 @@
         <v>416</v>
       </c>
       <c r="G412" s="6" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H412" s="6" t="s">
         <v>365</v>
@@ -17348,7 +17482,7 @@
         <v>416</v>
       </c>
       <c r="G413" s="6" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H413" s="6" t="s">
         <v>419</v>
@@ -17380,7 +17514,7 @@
         <v>416</v>
       </c>
       <c r="G414" s="6" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H414" s="6" t="s">
         <v>300</v>
@@ -17412,7 +17546,7 @@
         <v>416</v>
       </c>
       <c r="G415" s="6" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H415" s="6" t="s">
         <v>421</v>
@@ -17444,7 +17578,7 @@
         <v>416</v>
       </c>
       <c r="G416" s="6" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H416" s="6" t="s">
         <v>423</v>
@@ -17476,7 +17610,7 @@
         <v>416</v>
       </c>
       <c r="G417" s="6" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H417" s="6" t="s">
         <v>178</v>
@@ -17508,7 +17642,7 @@
         <v>707</v>
       </c>
       <c r="G418" s="22" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H418" s="22" t="s">
         <v>434</v>
@@ -17540,7 +17674,7 @@
         <v>708</v>
       </c>
       <c r="G419" s="4" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H419" s="4" t="s">
         <v>709</v>
@@ -17572,7 +17706,7 @@
         <v>711</v>
       </c>
       <c r="G420" s="22" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H420" s="22" t="s">
         <v>481</v>
@@ -17604,7 +17738,7 @@
         <v>712</v>
       </c>
       <c r="G421" s="22" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H421" s="22" t="s">
         <v>713</v>
@@ -17636,7 +17770,7 @@
         <v>715</v>
       </c>
       <c r="G422" s="22" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H422" s="22" t="s">
         <v>716</v>
@@ -17668,7 +17802,7 @@
         <v>718</v>
       </c>
       <c r="G423" s="22" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H423" s="22" t="s">
         <v>433</v>
@@ -17700,7 +17834,7 @@
         <v>719</v>
       </c>
       <c r="G424" s="6" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H424" s="6" t="s">
         <v>720</v>
@@ -17732,7 +17866,7 @@
         <v>609</v>
       </c>
       <c r="G425" s="11" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H425" s="11" t="s">
         <v>425</v>
@@ -17764,7 +17898,7 @@
         <v>424</v>
       </c>
       <c r="G426" s="11" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H426" s="11" t="s">
         <v>426</v>
@@ -17796,7 +17930,7 @@
         <v>424</v>
       </c>
       <c r="G427" s="11" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H427" s="11" t="s">
         <v>104</v>
@@ -17828,7 +17962,7 @@
         <v>424</v>
       </c>
       <c r="G428" s="11" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H428" s="11" t="s">
         <v>403</v>
@@ -17860,7 +17994,7 @@
         <v>424</v>
       </c>
       <c r="G429" s="11" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H429" s="11" t="s">
         <v>427</v>
@@ -17892,7 +18026,7 @@
         <v>424</v>
       </c>
       <c r="G430" s="11" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H430" s="11" t="s">
         <v>117</v>
@@ -17924,7 +18058,7 @@
         <v>721</v>
       </c>
       <c r="G431" s="22" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H431" s="22" t="s">
         <v>722</v>
@@ -17956,7 +18090,7 @@
         <v>723</v>
       </c>
       <c r="G432" s="22" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H432" s="22" t="s">
         <v>724</v>
@@ -17988,7 +18122,7 @@
         <v>725</v>
       </c>
       <c r="G433" s="22" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H433" s="22" t="s">
         <v>726</v>
@@ -18020,7 +18154,7 @@
         <v>727</v>
       </c>
       <c r="G434" s="22" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H434" s="22" t="s">
         <v>728</v>
@@ -18052,7 +18186,7 @@
         <v>729</v>
       </c>
       <c r="G435" s="22" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H435" s="22" t="s">
         <v>730</v>
@@ -18084,7 +18218,7 @@
         <v>731</v>
       </c>
       <c r="G436" s="22" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H436" s="22" t="s">
         <v>430</v>
@@ -18116,7 +18250,7 @@
         <v>732</v>
       </c>
       <c r="G437" s="22" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H437" s="22" t="s">
         <v>733</v>
@@ -18148,7 +18282,7 @@
         <v>428</v>
       </c>
       <c r="G438" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H438" s="6" t="s">
         <v>772</v>
@@ -18180,7 +18314,7 @@
         <v>428</v>
       </c>
       <c r="G439" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H439" s="6" t="s">
         <v>773</v>
@@ -18212,7 +18346,7 @@
         <v>428</v>
       </c>
       <c r="G440" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H440" s="6" t="s">
         <v>774</v>
@@ -18244,7 +18378,7 @@
         <v>428</v>
       </c>
       <c r="G441" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H441" s="6" t="s">
         <v>776</v>
@@ -18276,7 +18410,7 @@
         <v>428</v>
       </c>
       <c r="G442" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H442" s="6" t="s">
         <v>429</v>
@@ -18308,7 +18442,7 @@
         <v>428</v>
       </c>
       <c r="G443" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H443" s="6" t="s">
         <v>430</v>
@@ -18340,7 +18474,7 @@
         <v>428</v>
       </c>
       <c r="G444" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H444" s="6" t="s">
         <v>431</v>
@@ -18372,7 +18506,7 @@
         <v>428</v>
       </c>
       <c r="G445" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H445" s="6" t="s">
         <v>432</v>
@@ -18404,7 +18538,7 @@
         <v>428</v>
       </c>
       <c r="G446" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H446" s="6" t="s">
         <v>433</v>
@@ -18436,7 +18570,7 @@
         <v>428</v>
       </c>
       <c r="G447" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H447" s="6" t="s">
         <v>777</v>
@@ -18468,7 +18602,7 @@
         <v>428</v>
       </c>
       <c r="G448" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H448" s="6" t="s">
         <v>434</v>
@@ -18500,7 +18634,7 @@
         <v>428</v>
       </c>
       <c r="G449" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H449" s="6" t="s">
         <v>415</v>
@@ -18532,7 +18666,7 @@
         <v>734</v>
       </c>
       <c r="G450" s="22" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H450" s="22" t="s">
         <v>735</v>
@@ -18564,7 +18698,7 @@
         <v>736</v>
       </c>
       <c r="G451" s="22" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H451" s="22" t="s">
         <v>737</v>
@@ -18596,7 +18730,7 @@
         <v>441</v>
       </c>
       <c r="G452" s="11" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H452" s="11" t="s">
         <v>442</v>
@@ -18628,7 +18762,7 @@
         <v>441</v>
       </c>
       <c r="G453" s="11" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H453" s="11" t="s">
         <v>417</v>
@@ -18660,7 +18794,7 @@
         <v>441</v>
       </c>
       <c r="G454" s="11" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H454" s="11" t="s">
         <v>444</v>
@@ -18692,7 +18826,7 @@
         <v>441</v>
       </c>
       <c r="G455" s="11" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H455" s="11" t="s">
         <v>385</v>
@@ -18724,7 +18858,7 @@
         <v>441</v>
       </c>
       <c r="G456" s="11" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H456" s="11" t="s">
         <v>778</v>
@@ -18756,7 +18890,7 @@
         <v>441</v>
       </c>
       <c r="G457" s="11" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H457" s="11" t="s">
         <v>430</v>
@@ -19044,7 +19178,7 @@
         <v>738</v>
       </c>
       <c r="G466" s="22" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H466" s="22" t="s">
         <v>283</v>
@@ -19076,7 +19210,7 @@
         <v>446</v>
       </c>
       <c r="G467" s="6" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H467" s="6" t="s">
         <v>187</v>
@@ -19108,7 +19242,7 @@
         <v>446</v>
       </c>
       <c r="G468" s="6" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H468" s="6" t="s">
         <v>447</v>
@@ -19140,7 +19274,7 @@
         <v>446</v>
       </c>
       <c r="G469" s="6" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H469" s="6" t="s">
         <v>448</v>
@@ -19172,7 +19306,7 @@
         <v>446</v>
       </c>
       <c r="G470" s="6" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H470" s="6" t="s">
         <v>273</v>
@@ -19204,7 +19338,7 @@
         <v>446</v>
       </c>
       <c r="G471" s="6" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H471" s="6" t="s">
         <v>343</v>
@@ -19236,7 +19370,7 @@
         <v>446</v>
       </c>
       <c r="G472" s="6" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H472" s="6" t="s">
         <v>414</v>
@@ -19268,7 +19402,7 @@
         <v>446</v>
       </c>
       <c r="G473" s="6" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H473" s="6" t="s">
         <v>449</v>
@@ -19300,7 +19434,7 @@
         <v>446</v>
       </c>
       <c r="G474" s="6" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H474" s="6" t="s">
         <v>137</v>
@@ -19332,7 +19466,7 @@
         <v>739</v>
       </c>
       <c r="G475" s="22" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H475" s="22" t="s">
         <v>740</v>
@@ -19364,7 +19498,7 @@
         <v>450</v>
       </c>
       <c r="G476" s="11" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H476" s="11" t="s">
         <v>451</v>
@@ -19396,7 +19530,7 @@
         <v>450</v>
       </c>
       <c r="G477" s="11" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H477" s="11" t="s">
         <v>61</v>
@@ -19428,7 +19562,7 @@
         <v>450</v>
       </c>
       <c r="G478" s="11" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H478" s="11" t="s">
         <v>452</v>
@@ -19460,7 +19594,7 @@
         <v>450</v>
       </c>
       <c r="G479" s="11" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H479" s="11" t="s">
         <v>153</v>
@@ -19492,7 +19626,7 @@
         <v>450</v>
       </c>
       <c r="G480" s="11" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H480" s="11" t="s">
         <v>453</v>
@@ -19524,7 +19658,7 @@
         <v>450</v>
       </c>
       <c r="G481" s="11" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H481" s="11" t="s">
         <v>373</v>
@@ -19556,7 +19690,7 @@
         <v>450</v>
       </c>
       <c r="G482" s="11" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H482" s="11" t="s">
         <v>391</v>
@@ -19588,7 +19722,7 @@
         <v>450</v>
       </c>
       <c r="G483" s="11" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H483" s="11" t="s">
         <v>282</v>
@@ -19620,7 +19754,7 @@
         <v>450</v>
       </c>
       <c r="G484" s="11" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H484" s="11" t="s">
         <v>129</v>
@@ -19652,7 +19786,7 @@
         <v>450</v>
       </c>
       <c r="G485" s="11" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H485" s="11" t="s">
         <v>454</v>
@@ -19684,7 +19818,7 @@
         <v>450</v>
       </c>
       <c r="G486" s="11" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H486" s="11" t="s">
         <v>276</v>
@@ -19716,7 +19850,7 @@
         <v>450</v>
       </c>
       <c r="G487" s="11" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H487" s="11" t="s">
         <v>415</v>
@@ -19748,7 +19882,7 @@
         <v>450</v>
       </c>
       <c r="G488" s="11" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H488" s="11" t="s">
         <v>222</v>
@@ -19780,7 +19914,7 @@
         <v>456</v>
       </c>
       <c r="G489" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H489" s="6" t="s">
         <v>161</v>
@@ -19812,7 +19946,7 @@
         <v>456</v>
       </c>
       <c r="G490" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H490" s="6" t="s">
         <v>345</v>
@@ -19844,7 +19978,7 @@
         <v>456</v>
       </c>
       <c r="G491" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H491" s="6" t="s">
         <v>457</v>
@@ -19876,7 +20010,7 @@
         <v>456</v>
       </c>
       <c r="G492" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H492" s="6" t="s">
         <v>49</v>
@@ -19908,7 +20042,7 @@
         <v>456</v>
       </c>
       <c r="G493" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H493" s="6" t="s">
         <v>115</v>
@@ -19940,7 +20074,7 @@
         <v>456</v>
       </c>
       <c r="G494" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H494" s="6" t="s">
         <v>403</v>
@@ -19972,7 +20106,7 @@
         <v>741</v>
       </c>
       <c r="G495" s="22" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H495" s="22" t="s">
         <v>49</v>
@@ -20004,7 +20138,7 @@
         <v>459</v>
       </c>
       <c r="G496" s="4" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H496" s="4" t="s">
         <v>146</v>
@@ -20036,7 +20170,7 @@
         <v>459</v>
       </c>
       <c r="G497" s="4" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H497" s="4" t="s">
         <v>112</v>
@@ -20068,7 +20202,7 @@
         <v>459</v>
       </c>
       <c r="G498" s="4" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H498" s="4" t="s">
         <v>462</v>
@@ -20100,7 +20234,7 @@
         <v>459</v>
       </c>
       <c r="G499" s="4" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H499" s="4" t="s">
         <v>293</v>
@@ -20132,7 +20266,7 @@
         <v>742</v>
       </c>
       <c r="G500" s="22" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H500" s="22" t="s">
         <v>489</v>
@@ -20164,7 +20298,7 @@
         <v>463</v>
       </c>
       <c r="G501" s="6" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H501" s="6" t="s">
         <v>464</v>
@@ -20196,7 +20330,7 @@
         <v>463</v>
       </c>
       <c r="G502" s="6" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H502" s="6" t="s">
         <v>83</v>
@@ -20228,7 +20362,7 @@
         <v>463</v>
       </c>
       <c r="G503" s="6" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H503" s="6" t="s">
         <v>465</v>
@@ -20260,7 +20394,7 @@
         <v>463</v>
       </c>
       <c r="G504" s="6" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H504" s="6" t="s">
         <v>103</v>
@@ -20292,7 +20426,7 @@
         <v>463</v>
       </c>
       <c r="G505" s="6" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H505" s="6" t="s">
         <v>104</v>
@@ -20324,7 +20458,7 @@
         <v>463</v>
       </c>
       <c r="G506" s="6" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H506" s="6" t="s">
         <v>375</v>
@@ -20356,7 +20490,7 @@
         <v>463</v>
       </c>
       <c r="G507" s="6" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H507" s="6" t="s">
         <v>415</v>
@@ -20388,7 +20522,7 @@
         <v>463</v>
       </c>
       <c r="G508" s="6" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H508" s="6" t="s">
         <v>221</v>
@@ -20420,7 +20554,7 @@
         <v>468</v>
       </c>
       <c r="G509" s="4" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H509" s="4" t="s">
         <v>469</v>
@@ -20452,7 +20586,7 @@
         <v>468</v>
       </c>
       <c r="G510" s="4" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H510" s="4" t="s">
         <v>222</v>
@@ -20484,7 +20618,7 @@
         <v>763</v>
       </c>
       <c r="G511" s="6" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H511" s="14" t="s">
         <v>769</v>
@@ -20516,7 +20650,7 @@
         <v>743</v>
       </c>
       <c r="G512" s="22" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H512" s="22" t="s">
         <v>490</v>
@@ -20548,7 +20682,7 @@
         <v>470</v>
       </c>
       <c r="G513" s="4" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H513" s="4" t="s">
         <v>363</v>
@@ -20580,7 +20714,7 @@
         <v>470</v>
       </c>
       <c r="G514" s="4" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H514" s="4" t="s">
         <v>471</v>
@@ -20612,7 +20746,7 @@
         <v>470</v>
       </c>
       <c r="G515" s="4" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H515" s="4" t="s">
         <v>476</v>
@@ -20644,7 +20778,7 @@
         <v>470</v>
       </c>
       <c r="G516" s="4" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H516" s="4" t="s">
         <v>472</v>
@@ -20676,7 +20810,7 @@
         <v>470</v>
       </c>
       <c r="G517" s="4" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H517" s="4" t="s">
         <v>304</v>
@@ -20708,7 +20842,7 @@
         <v>470</v>
       </c>
       <c r="G518" s="4" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H518" s="4" t="s">
         <v>473</v>
@@ -20740,7 +20874,7 @@
         <v>470</v>
       </c>
       <c r="G519" s="4" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H519" s="4" t="s">
         <v>474</v>
@@ -20772,7 +20906,7 @@
         <v>470</v>
       </c>
       <c r="G520" s="4" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H520" s="4" t="s">
         <v>391</v>
@@ -20804,7 +20938,7 @@
         <v>470</v>
       </c>
       <c r="G521" s="4" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H521" s="4" t="s">
         <v>453</v>
@@ -20836,7 +20970,7 @@
         <v>470</v>
       </c>
       <c r="G522" s="4" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H522" s="4" t="s">
         <v>475</v>
@@ -20868,7 +21002,7 @@
         <v>470</v>
       </c>
       <c r="G523" s="4" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H523" s="4" t="s">
         <v>395</v>
@@ -20900,7 +21034,7 @@
         <v>470</v>
       </c>
       <c r="G524" s="4" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H524" s="4" t="s">
         <v>478</v>
@@ -20932,7 +21066,7 @@
         <v>470</v>
       </c>
       <c r="G525" s="4" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H525" s="4" t="s">
         <v>68</v>
@@ -20964,7 +21098,7 @@
         <v>470</v>
       </c>
       <c r="G526" s="4" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H526" s="4" t="s">
         <v>479</v>
@@ -20996,7 +21130,7 @@
         <v>470</v>
       </c>
       <c r="G527" s="4" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H527" s="4" t="s">
         <v>480</v>
@@ -21028,7 +21162,7 @@
         <v>470</v>
       </c>
       <c r="G528" s="4" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H528" s="4" t="s">
         <v>116</v>
@@ -21060,7 +21194,7 @@
         <v>470</v>
       </c>
       <c r="G529" s="4" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H529" s="4" t="s">
         <v>481</v>
@@ -21092,7 +21226,7 @@
         <v>485</v>
       </c>
       <c r="G530" s="6" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H530" s="6" t="s">
         <v>486</v>
@@ -21124,7 +21258,7 @@
         <v>485</v>
       </c>
       <c r="G531" s="6" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H531" s="6" t="s">
         <v>487</v>
@@ -21156,7 +21290,7 @@
         <v>485</v>
       </c>
       <c r="G532" s="6" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H532" s="6" t="s">
         <v>387</v>
@@ -21188,7 +21322,7 @@
         <v>485</v>
       </c>
       <c r="G533" s="6" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H533" s="6" t="s">
         <v>475</v>
@@ -21220,7 +21354,7 @@
         <v>485</v>
       </c>
       <c r="G534" s="6" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H534" s="6" t="s">
         <v>488</v>
@@ -21252,7 +21386,7 @@
         <v>485</v>
       </c>
       <c r="G535" s="6" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H535" s="6" t="s">
         <v>178</v>
@@ -21284,7 +21418,7 @@
         <v>485</v>
       </c>
       <c r="G536" s="6" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H536" s="6" t="s">
         <v>189</v>
@@ -21316,7 +21450,7 @@
         <v>485</v>
       </c>
       <c r="G537" s="6" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H537" s="6" t="s">
         <v>489</v>
@@ -21348,7 +21482,7 @@
         <v>485</v>
       </c>
       <c r="G538" s="6" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H538" s="6" t="s">
         <v>490</v>
@@ -21380,7 +21514,7 @@
         <v>485</v>
       </c>
       <c r="G539" s="6" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H539" s="6" t="s">
         <v>283</v>
@@ -21412,7 +21546,7 @@
         <v>485</v>
       </c>
       <c r="G540" s="6" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H540" s="6" t="s">
         <v>491</v>
@@ -21444,7 +21578,7 @@
         <v>744</v>
       </c>
       <c r="G541" s="22" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H541" s="22" t="s">
         <v>745</v>
@@ -21476,7 +21610,7 @@
         <v>746</v>
       </c>
       <c r="G542" s="22" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H542" s="23" t="s">
         <v>747</v>
@@ -21508,7 +21642,7 @@
         <v>493</v>
       </c>
       <c r="G543" s="11" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H543" s="11" t="s">
         <v>748</v>
@@ -21540,7 +21674,7 @@
         <v>493</v>
       </c>
       <c r="G544" s="11" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H544" s="11" t="s">
         <v>494</v>
@@ -21572,7 +21706,7 @@
         <v>493</v>
       </c>
       <c r="G545" s="11" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H545" s="16" t="s">
         <v>495</v>
@@ -21604,7 +21738,7 @@
         <v>493</v>
       </c>
       <c r="G546" s="11" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H546" s="11" t="s">
         <v>45</v>
@@ -21636,7 +21770,7 @@
         <v>493</v>
       </c>
       <c r="G547" s="11" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H547" s="11" t="s">
         <v>498</v>
@@ -21668,7 +21802,7 @@
         <v>493</v>
       </c>
       <c r="G548" s="11" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H548" s="11" t="s">
         <v>500</v>
@@ -21700,7 +21834,7 @@
         <v>493</v>
       </c>
       <c r="G549" s="11" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H549" s="11" t="s">
         <v>501</v>
@@ -21732,7 +21866,7 @@
         <v>493</v>
       </c>
       <c r="G550" s="11" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H550" s="11" t="s">
         <v>503</v>
@@ -21764,7 +21898,7 @@
         <v>493</v>
       </c>
       <c r="G551" s="11" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H551" s="11" t="s">
         <v>81</v>
@@ -21796,7 +21930,7 @@
         <v>493</v>
       </c>
       <c r="G552" s="11" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H552" s="11" t="s">
         <v>504</v>
@@ -21828,7 +21962,7 @@
         <v>505</v>
       </c>
       <c r="G553" s="6" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H553" s="6" t="s">
         <v>135</v>
@@ -21860,7 +21994,7 @@
         <v>505</v>
       </c>
       <c r="G554" s="6" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H554" s="6" t="s">
         <v>487</v>
@@ -21892,7 +22026,7 @@
         <v>505</v>
       </c>
       <c r="G555" s="6" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H555" s="6" t="s">
         <v>506</v>
@@ -21924,7 +22058,7 @@
         <v>505</v>
       </c>
       <c r="G556" s="6" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H556" s="6" t="s">
         <v>285</v>
@@ -21956,7 +22090,7 @@
         <v>505</v>
       </c>
       <c r="G557" s="6" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H557" s="6" t="s">
         <v>508</v>
@@ -21988,7 +22122,7 @@
         <v>505</v>
       </c>
       <c r="G558" s="6" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H558" s="6" t="s">
         <v>509</v>
@@ -22020,7 +22154,7 @@
         <v>505</v>
       </c>
       <c r="G559" s="6" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H559" s="6" t="s">
         <v>511</v>
@@ -22052,7 +22186,7 @@
         <v>505</v>
       </c>
       <c r="G560" s="6" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H560" s="6" t="s">
         <v>513</v>
@@ -22084,7 +22218,7 @@
         <v>505</v>
       </c>
       <c r="G561" s="6" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H561" s="6" t="s">
         <v>403</v>
@@ -22116,7 +22250,7 @@
         <v>749</v>
       </c>
       <c r="G562" s="22" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H562" s="22" t="s">
         <v>750</v>
@@ -22148,7 +22282,7 @@
         <v>515</v>
       </c>
       <c r="G563" s="11" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H563" s="11" t="s">
         <v>517</v>
@@ -22468,7 +22602,7 @@
         <v>522</v>
       </c>
       <c r="G573" s="6" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H573" s="6" t="s">
         <v>173</v>
@@ -22500,7 +22634,7 @@
         <v>522</v>
       </c>
       <c r="G574" s="6" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H574" s="6" t="s">
         <v>523</v>
@@ -22532,7 +22666,7 @@
         <v>522</v>
       </c>
       <c r="G575" s="6" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H575" s="6" t="s">
         <v>524</v>
@@ -22564,7 +22698,7 @@
         <v>522</v>
       </c>
       <c r="G576" s="6" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H576" s="6" t="s">
         <v>270</v>
@@ -22596,7 +22730,7 @@
         <v>522</v>
       </c>
       <c r="G577" s="6" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H577" s="6" t="s">
         <v>132</v>
@@ -22628,7 +22762,7 @@
         <v>522</v>
       </c>
       <c r="G578" s="6" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H578" s="6" t="s">
         <v>45</v>
@@ -22660,7 +22794,7 @@
         <v>522</v>
       </c>
       <c r="G579" s="6" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H579" s="6" t="s">
         <v>448</v>
@@ -22692,7 +22826,7 @@
         <v>522</v>
       </c>
       <c r="G580" s="6" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H580" s="6" t="s">
         <v>241</v>
@@ -22724,7 +22858,7 @@
         <v>522</v>
       </c>
       <c r="G581" s="6" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H581" s="6" t="s">
         <v>526</v>
@@ -22756,7 +22890,7 @@
         <v>522</v>
       </c>
       <c r="G582" s="6" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H582" s="6" t="s">
         <v>251</v>
@@ -22788,7 +22922,7 @@
         <v>522</v>
       </c>
       <c r="G583" s="6" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H583" s="6" t="s">
         <v>528</v>
@@ -22820,7 +22954,7 @@
         <v>522</v>
       </c>
       <c r="G584" s="6" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H584" s="6" t="s">
         <v>318</v>
@@ -22852,7 +22986,7 @@
         <v>522</v>
       </c>
       <c r="G585" s="6" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H585" s="6" t="s">
         <v>106</v>
@@ -22884,7 +23018,7 @@
         <v>522</v>
       </c>
       <c r="G586" s="6" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H586" s="6" t="s">
         <v>276</v>
@@ -22916,7 +23050,7 @@
         <v>522</v>
       </c>
       <c r="G587" s="6" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H587" s="6" t="s">
         <v>415</v>
@@ -22948,7 +23082,7 @@
         <v>522</v>
       </c>
       <c r="G588" s="6" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H588" s="6" t="s">
         <v>490</v>
@@ -22980,7 +23114,7 @@
         <v>751</v>
       </c>
       <c r="G589" s="22" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H589" s="22" t="s">
         <v>752</v>
@@ -23012,7 +23146,7 @@
         <v>753</v>
       </c>
       <c r="G590" s="22" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H590" s="22" t="s">
         <v>754</v>
@@ -23044,7 +23178,7 @@
         <v>755</v>
       </c>
       <c r="G591" s="22" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H591" s="22" t="s">
         <v>756</v>
@@ -23076,7 +23210,7 @@
         <v>529</v>
       </c>
       <c r="G592" s="4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H592" s="4" t="s">
         <v>42</v>
@@ -23108,7 +23242,7 @@
         <v>529</v>
       </c>
       <c r="G593" s="4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H593" s="4" t="s">
         <v>530</v>
@@ -23140,7 +23274,7 @@
         <v>529</v>
       </c>
       <c r="G594" s="4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H594" s="4" t="s">
         <v>531</v>
@@ -23172,7 +23306,7 @@
         <v>529</v>
       </c>
       <c r="G595" s="4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H595" s="4" t="s">
         <v>532</v>
@@ -23204,7 +23338,7 @@
         <v>529</v>
       </c>
       <c r="G596" s="4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H596" s="4" t="s">
         <v>418</v>
@@ -23236,7 +23370,7 @@
         <v>529</v>
       </c>
       <c r="G597" s="4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H597" s="4" t="s">
         <v>421</v>
@@ -23268,7 +23402,7 @@
         <v>529</v>
       </c>
       <c r="G598" s="4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H598" s="4" t="s">
         <v>533</v>
@@ -23300,7 +23434,7 @@
         <v>529</v>
       </c>
       <c r="G599" s="4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H599" s="4" t="s">
         <v>391</v>
@@ -23332,7 +23466,7 @@
         <v>529</v>
       </c>
       <c r="G600" s="4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H600" s="4" t="s">
         <v>535</v>
@@ -23364,7 +23498,7 @@
         <v>529</v>
       </c>
       <c r="G601" s="4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H601" s="4" t="s">
         <v>488</v>
@@ -23396,7 +23530,7 @@
         <v>529</v>
       </c>
       <c r="G602" s="4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H602" s="4" t="s">
         <v>245</v>
@@ -23428,7 +23562,7 @@
         <v>529</v>
       </c>
       <c r="G603" s="4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H603" s="4" t="s">
         <v>220</v>
@@ -23460,7 +23594,7 @@
         <v>529</v>
       </c>
       <c r="G604" s="4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H604" s="4" t="s">
         <v>137</v>
@@ -23492,7 +23626,7 @@
         <v>529</v>
       </c>
       <c r="G605" s="4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H605" s="4" t="s">
         <v>537</v>
@@ -23524,7 +23658,7 @@
         <v>767</v>
       </c>
       <c r="G606" s="6" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H606" s="6" t="s">
         <v>539</v>
@@ -23556,7 +23690,7 @@
         <v>538</v>
       </c>
       <c r="G607" s="6" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H607" s="6" t="s">
         <v>540</v>
@@ -23588,7 +23722,7 @@
         <v>538</v>
       </c>
       <c r="G608" s="6" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H608" s="6" t="s">
         <v>45</v>
@@ -23620,7 +23754,7 @@
         <v>538</v>
       </c>
       <c r="G609" s="6" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H609" s="6" t="s">
         <v>45</v>
@@ -23652,7 +23786,7 @@
         <v>538</v>
       </c>
       <c r="G610" s="6" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H610" s="6" t="s">
         <v>132</v>
@@ -23684,7 +23818,7 @@
         <v>538</v>
       </c>
       <c r="G611" s="6" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H611" s="6" t="s">
         <v>523</v>
@@ -23716,7 +23850,7 @@
         <v>538</v>
       </c>
       <c r="G612" s="6" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H612" s="6" t="s">
         <v>453</v>
@@ -23748,7 +23882,7 @@
         <v>538</v>
       </c>
       <c r="G613" s="6" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H613" s="6" t="s">
         <v>490</v>
@@ -23780,7 +23914,7 @@
         <v>538</v>
       </c>
       <c r="G614" s="6" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H614" s="6" t="s">
         <v>364</v>
@@ -23812,7 +23946,7 @@
         <v>758</v>
       </c>
       <c r="G615" s="22" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H615" s="22" t="s">
         <v>759</v>
@@ -23844,7 +23978,7 @@
         <v>541</v>
       </c>
       <c r="G616" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H616" s="4" t="s">
         <v>146</v>
@@ -23876,7 +24010,7 @@
         <v>541</v>
       </c>
       <c r="G617" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H617" s="4" t="s">
         <v>542</v>
@@ -23908,7 +24042,7 @@
         <v>541</v>
       </c>
       <c r="G618" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H618" s="4" t="s">
         <v>14</v>
@@ -23940,7 +24074,7 @@
         <v>541</v>
       </c>
       <c r="G619" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H619" s="4" t="s">
         <v>186</v>
@@ -23972,7 +24106,7 @@
         <v>541</v>
       </c>
       <c r="G620" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H620" s="4" t="s">
         <v>544</v>
@@ -24004,7 +24138,7 @@
         <v>541</v>
       </c>
       <c r="G621" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H621" s="4" t="s">
         <v>545</v>
@@ -24036,7 +24170,7 @@
         <v>541</v>
       </c>
       <c r="G622" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H622" s="4" t="s">
         <v>547</v>
@@ -24068,7 +24202,7 @@
         <v>541</v>
       </c>
       <c r="G623" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H623" s="4" t="s">
         <v>548</v>
@@ -24100,7 +24234,7 @@
         <v>549</v>
       </c>
       <c r="G624" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H624" s="6" t="s">
         <v>270</v>
@@ -24132,7 +24266,7 @@
         <v>549</v>
       </c>
       <c r="G625" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H625" s="6" t="s">
         <v>230</v>
@@ -24164,7 +24298,7 @@
         <v>549</v>
       </c>
       <c r="G626" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H626" s="6" t="s">
         <v>551</v>
@@ -24196,7 +24330,7 @@
         <v>549</v>
       </c>
       <c r="G627" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H627" s="6" t="s">
         <v>552</v>
@@ -24228,7 +24362,7 @@
         <v>549</v>
       </c>
       <c r="G628" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H628" s="6" t="s">
         <v>274</v>
@@ -24260,7 +24394,7 @@
         <v>549</v>
       </c>
       <c r="G629" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H629" s="6" t="s">
         <v>447</v>
@@ -24292,7 +24426,7 @@
         <v>549</v>
       </c>
       <c r="G630" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H630" s="6" t="s">
         <v>553</v>
@@ -24324,7 +24458,7 @@
         <v>549</v>
       </c>
       <c r="G631" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H631" s="6" t="s">
         <v>488</v>
@@ -24356,7 +24490,7 @@
         <v>549</v>
       </c>
       <c r="G632" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H632" s="6" t="s">
         <v>779</v>
@@ -24388,7 +24522,7 @@
         <v>549</v>
       </c>
       <c r="G633" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H633" s="6" t="s">
         <v>453</v>
@@ -24420,7 +24554,7 @@
         <v>549</v>
       </c>
       <c r="G634" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H634" s="6" t="s">
         <v>298</v>
@@ -24452,7 +24586,7 @@
         <v>549</v>
       </c>
       <c r="G635" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H635" s="6" t="s">
         <v>554</v>
@@ -24484,7 +24618,7 @@
         <v>549</v>
       </c>
       <c r="G636" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H636" s="6" t="s">
         <v>448</v>
@@ -24516,7 +24650,7 @@
         <v>549</v>
       </c>
       <c r="G637" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H637" s="6" t="s">
         <v>449</v>
@@ -24548,7 +24682,7 @@
         <v>549</v>
       </c>
       <c r="G638" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H638" s="6" t="s">
         <v>555</v>
@@ -24580,7 +24714,7 @@
         <v>549</v>
       </c>
       <c r="G639" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H639" s="6" t="s">
         <v>285</v>
@@ -24612,7 +24746,7 @@
         <v>549</v>
       </c>
       <c r="G640" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H640" s="6" t="s">
         <v>533</v>
@@ -24644,7 +24778,7 @@
         <v>549</v>
       </c>
       <c r="G641" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H641" s="6" t="s">
         <v>390</v>
@@ -24676,7 +24810,7 @@
         <v>549</v>
       </c>
       <c r="G642" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H642" s="6" t="s">
         <v>556</v>
@@ -24708,7 +24842,7 @@
         <v>549</v>
       </c>
       <c r="G643" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H643" s="6" t="s">
         <v>780</v>
@@ -24740,7 +24874,7 @@
         <v>549</v>
       </c>
       <c r="G644" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H644" s="6" t="s">
         <v>557</v>
@@ -24772,7 +24906,7 @@
         <v>549</v>
       </c>
       <c r="G645" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H645" s="6" t="s">
         <v>781</v>
@@ -24804,7 +24938,7 @@
         <v>549</v>
       </c>
       <c r="G646" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H646" s="6" t="s">
         <v>252</v>
@@ -24836,7 +24970,7 @@
         <v>549</v>
       </c>
       <c r="G647" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H647" s="6" t="s">
         <v>372</v>
@@ -24868,7 +25002,7 @@
         <v>549</v>
       </c>
       <c r="G648" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H648" s="6" t="s">
         <v>782</v>
@@ -24900,7 +25034,7 @@
         <v>549</v>
       </c>
       <c r="G649" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H649" s="6" t="s">
         <v>117</v>
@@ -24932,7 +25066,7 @@
         <v>549</v>
       </c>
       <c r="G650" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H650" s="6" t="s">
         <v>490</v>
@@ -25188,7 +25322,7 @@
         <v>566</v>
       </c>
       <c r="G658" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H658" s="4" t="s">
         <v>461</v>
@@ -25220,7 +25354,7 @@
         <v>566</v>
       </c>
       <c r="G659" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H659" s="4" t="s">
         <v>509</v>
@@ -25252,7 +25386,7 @@
         <v>566</v>
       </c>
       <c r="G660" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H660" s="4" t="s">
         <v>487</v>
@@ -25284,7 +25418,7 @@
         <v>566</v>
       </c>
       <c r="G661" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H661" s="4" t="s">
         <v>153</v>
@@ -25316,7 +25450,7 @@
         <v>566</v>
       </c>
       <c r="G662" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H662" s="4" t="s">
         <v>81</v>
@@ -25348,7 +25482,7 @@
         <v>566</v>
       </c>
       <c r="G663" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H663" s="4" t="s">
         <v>567</v>
@@ -25380,7 +25514,7 @@
         <v>566</v>
       </c>
       <c r="G664" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H664" s="4" t="s">
         <v>572</v>
@@ -25412,7 +25546,7 @@
         <v>566</v>
       </c>
       <c r="G665" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H665" s="4" t="s">
         <v>395</v>
@@ -25444,7 +25578,7 @@
         <v>566</v>
       </c>
       <c r="G666" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H666" s="4" t="s">
         <v>276</v>
@@ -25476,7 +25610,7 @@
         <v>566</v>
       </c>
       <c r="G667" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H667" s="4" t="s">
         <v>568</v>
@@ -25508,7 +25642,7 @@
         <v>566</v>
       </c>
       <c r="G668" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H668" s="4" t="s">
         <v>8</v>
@@ -25540,7 +25674,7 @@
         <v>566</v>
       </c>
       <c r="G669" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H669" s="4" t="s">
         <v>173</v>
@@ -25572,7 +25706,7 @@
         <v>566</v>
       </c>
       <c r="G670" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H670" s="4" t="s">
         <v>569</v>
@@ -25604,7 +25738,7 @@
         <v>566</v>
       </c>
       <c r="G671" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H671" s="4" t="s">
         <v>573</v>
@@ -25636,7 +25770,7 @@
         <v>566</v>
       </c>
       <c r="G672" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H672" s="4" t="s">
         <v>570</v>
@@ -25668,7 +25802,7 @@
         <v>566</v>
       </c>
       <c r="G673" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H673" s="4" t="s">
         <v>214</v>
@@ -25700,7 +25834,7 @@
         <v>566</v>
       </c>
       <c r="G674" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H674" s="4" t="s">
         <v>571</v>
@@ -25732,7 +25866,7 @@
         <v>566</v>
       </c>
       <c r="G675" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H675" s="4" t="s">
         <v>597</v>
@@ -25764,7 +25898,7 @@
         <v>578</v>
       </c>
       <c r="G676" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H676" s="6" t="s">
         <v>461</v>
@@ -25796,7 +25930,7 @@
         <v>578</v>
       </c>
       <c r="G677" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H677" s="6" t="s">
         <v>583</v>
@@ -25828,7 +25962,7 @@
         <v>578</v>
       </c>
       <c r="G678" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H678" s="6" t="s">
         <v>293</v>
@@ -25860,7 +25994,7 @@
         <v>578</v>
       </c>
       <c r="G679" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H679" s="6" t="s">
         <v>19</v>
@@ -25892,7 +26026,7 @@
         <v>578</v>
       </c>
       <c r="G680" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H680" s="6" t="s">
         <v>584</v>
@@ -25924,7 +26058,7 @@
         <v>578</v>
       </c>
       <c r="G681" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H681" s="6" t="s">
         <v>198</v>
@@ -25956,7 +26090,7 @@
         <v>578</v>
       </c>
       <c r="G682" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H682" s="6" t="s">
         <v>448</v>
@@ -25988,7 +26122,7 @@
         <v>578</v>
       </c>
       <c r="G683" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H683" s="6" t="s">
         <v>533</v>
@@ -26020,7 +26154,7 @@
         <v>578</v>
       </c>
       <c r="G684" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H684" s="6" t="s">
         <v>585</v>
@@ -26052,7 +26186,7 @@
         <v>578</v>
       </c>
       <c r="G685" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H685" s="6" t="s">
         <v>90</v>
@@ -26084,7 +26218,7 @@
         <v>578</v>
       </c>
       <c r="G686" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H686" s="6" t="s">
         <v>218</v>
@@ -26116,7 +26250,7 @@
         <v>578</v>
       </c>
       <c r="G687" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H687" s="6" t="s">
         <v>586</v>
@@ -26148,7 +26282,7 @@
         <v>578</v>
       </c>
       <c r="G688" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H688" s="6" t="s">
         <v>390</v>
@@ -26180,7 +26314,7 @@
         <v>578</v>
       </c>
       <c r="G689" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H689" s="6" t="s">
         <v>181</v>
@@ -26212,7 +26346,7 @@
         <v>578</v>
       </c>
       <c r="G690" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H690" s="6" t="s">
         <v>219</v>
@@ -26244,7 +26378,7 @@
         <v>578</v>
       </c>
       <c r="G691" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H691" s="6" t="s">
         <v>137</v>
@@ -26276,7 +26410,7 @@
         <v>578</v>
       </c>
       <c r="G692" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H692" s="6" t="s">
         <v>246</v>
@@ -26660,7 +26794,7 @@
         <v>760</v>
       </c>
       <c r="G704" s="4" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H704" s="4" t="s">
         <v>222</v>
@@ -26692,7 +26826,7 @@
         <v>760</v>
       </c>
       <c r="G705" s="4" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H705" s="4" t="s">
         <v>126</v>
@@ -26724,13 +26858,13 @@
         <v>760</v>
       </c>
       <c r="G706" s="4" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H706" s="4" t="s">
         <v>453</v>
       </c>
       <c r="I706" s="4" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="J706" s="26">
         <v>5.6481481481481478E-3</v>
@@ -26756,7 +26890,7 @@
         <v>760</v>
       </c>
       <c r="G707" s="4" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H707" s="4" t="s">
         <v>490</v>
@@ -26788,7 +26922,7 @@
         <v>760</v>
       </c>
       <c r="G708" s="4" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H708" s="4" t="s">
         <v>533</v>
@@ -26820,7 +26954,7 @@
         <v>760</v>
       </c>
       <c r="G709" s="4" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H709" s="4" t="s">
         <v>761</v>
@@ -26852,7 +26986,7 @@
         <v>786</v>
       </c>
       <c r="G710" s="6" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H710" s="6" t="s">
         <v>222</v>
@@ -26884,7 +27018,7 @@
         <v>785</v>
       </c>
       <c r="G711" s="6" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H711" s="6" t="s">
         <v>787</v>
@@ -26916,7 +27050,7 @@
         <v>785</v>
       </c>
       <c r="G712" s="6" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H712" s="6" t="s">
         <v>789</v>
@@ -26948,7 +27082,7 @@
         <v>785</v>
       </c>
       <c r="G713" s="6" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H713" s="6" t="s">
         <v>791</v>
@@ -26980,7 +27114,7 @@
         <v>785</v>
       </c>
       <c r="G714" s="6" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H714" s="6" t="s">
         <v>792</v>
@@ -27012,7 +27146,7 @@
         <v>785</v>
       </c>
       <c r="G715" s="6" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H715" s="6" t="s">
         <v>793</v>
@@ -27044,7 +27178,7 @@
         <v>785</v>
       </c>
       <c r="G716" s="6" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H716" s="6" t="s">
         <v>795</v>
@@ -27076,7 +27210,7 @@
         <v>785</v>
       </c>
       <c r="G717" s="6" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H717" s="6" t="s">
         <v>797</v>
@@ -27108,7 +27242,7 @@
         <v>785</v>
       </c>
       <c r="G718" s="6" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H718" s="6" t="s">
         <v>798</v>
@@ -27140,7 +27274,7 @@
         <v>785</v>
       </c>
       <c r="G719" s="6" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H719" s="6" t="s">
         <v>800</v>
@@ -27172,7 +27306,7 @@
         <v>785</v>
       </c>
       <c r="G720" s="6" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H720" s="6" t="s">
         <v>594</v>
@@ -27204,7 +27338,7 @@
         <v>785</v>
       </c>
       <c r="G721" s="6" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H721" s="6" t="s">
         <v>802</v>
@@ -27236,7 +27370,7 @@
         <v>785</v>
       </c>
       <c r="G722" s="6" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H722" s="6" t="s">
         <v>803</v>
@@ -27268,7 +27402,7 @@
         <v>805</v>
       </c>
       <c r="G723" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H723" s="4" t="s">
         <v>112</v>
@@ -27277,7 +27411,7 @@
         <v>119</v>
       </c>
       <c r="J723" s="26">
-        <v>5.0810185185185186E-3</v>
+        <v>5.0694444444444441E-3</v>
       </c>
     </row>
     <row r="724" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -27300,7 +27434,7 @@
         <v>805</v>
       </c>
       <c r="G724" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H724" s="4" t="s">
         <v>461</v>
@@ -27309,7 +27443,7 @@
         <v>460</v>
       </c>
       <c r="J724" s="26">
-        <v>1.0081018518518519E-2</v>
+        <v>1.0069444444444445E-2</v>
       </c>
     </row>
     <row r="725" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -27332,7 +27466,7 @@
         <v>805</v>
       </c>
       <c r="G725" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H725" s="4" t="s">
         <v>806</v>
@@ -27364,7 +27498,7 @@
         <v>805</v>
       </c>
       <c r="G726" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H726" s="4" t="s">
         <v>809</v>
@@ -27396,7 +27530,7 @@
         <v>805</v>
       </c>
       <c r="G727" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H727" s="4" t="s">
         <v>810</v>
@@ -27405,7 +27539,7 @@
         <v>811</v>
       </c>
       <c r="J727" s="26">
-        <v>2.1527777777777778E-2</v>
+        <v>2.1539351851851851E-2</v>
       </c>
     </row>
     <row r="728" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -27428,7 +27562,7 @@
         <v>805</v>
       </c>
       <c r="G728" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H728" s="4" t="s">
         <v>813</v>
@@ -27460,7 +27594,7 @@
         <v>805</v>
       </c>
       <c r="G729" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H729" s="4" t="s">
         <v>815</v>
@@ -27469,7 +27603,7 @@
         <v>814</v>
       </c>
       <c r="J729" s="26">
-        <v>3.2986111111111112E-2</v>
+        <v>3.2962962962962965E-2</v>
       </c>
     </row>
     <row r="730" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -27492,7 +27626,7 @@
         <v>805</v>
       </c>
       <c r="G730" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H730" s="4" t="s">
         <v>816</v>
@@ -27524,7 +27658,7 @@
         <v>805</v>
       </c>
       <c r="G731" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H731" s="4" t="s">
         <v>817</v>
@@ -27556,7 +27690,7 @@
         <v>805</v>
       </c>
       <c r="G732" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H732" s="4" t="s">
         <v>820</v>
@@ -27588,7 +27722,7 @@
         <v>805</v>
       </c>
       <c r="G733" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H733" s="4" t="s">
         <v>821</v>
@@ -27620,7 +27754,7 @@
         <v>805</v>
       </c>
       <c r="G734" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H734" s="4" t="s">
         <v>822</v>
@@ -27652,7 +27786,7 @@
         <v>805</v>
       </c>
       <c r="G735" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H735" s="4" t="s">
         <v>825</v>
@@ -27661,7 +27795,7 @@
         <v>824</v>
       </c>
       <c r="J735" s="26">
-        <v>6.5219907407407407E-2</v>
+        <v>6.5254629629629635E-2</v>
       </c>
     </row>
     <row r="736" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -27684,7 +27818,7 @@
         <v>805</v>
       </c>
       <c r="G736" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H736" s="4" t="s">
         <v>826</v>
@@ -27693,7 +27827,7 @@
         <v>824</v>
       </c>
       <c r="J736" s="26">
-        <v>6.986111111111111E-2</v>
+        <v>6.9837962962962963E-2</v>
       </c>
     </row>
     <row r="737" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -27716,7 +27850,7 @@
         <v>805</v>
       </c>
       <c r="G737" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H737" s="4" t="s">
         <v>828</v>
@@ -27725,7 +27859,7 @@
         <v>827</v>
       </c>
       <c r="J737" s="26">
-        <v>7.5659722222222225E-2</v>
+        <v>7.5671296296296292E-2</v>
       </c>
     </row>
     <row r="738" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -27748,16 +27882,16 @@
         <v>805</v>
       </c>
       <c r="G738" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H738" s="4" t="s">
-        <v>830</v>
+        <v>983</v>
       </c>
       <c r="I738" s="4" t="s">
         <v>829</v>
       </c>
       <c r="J738" s="26">
-        <v>8.009259259259259E-2</v>
+        <v>8.0057870370370376E-2</v>
       </c>
     </row>
     <row r="739" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -27780,16 +27914,16 @@
         <v>805</v>
       </c>
       <c r="G739" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H739" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="I739" s="4" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="J739" s="26">
-        <v>8.385416666666666E-2</v>
+        <v>8.3877314814814821E-2</v>
       </c>
     </row>
     <row r="740" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -27812,16 +27946,16 @@
         <v>805</v>
       </c>
       <c r="G740" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H740" s="4" t="s">
         <v>545</v>
       </c>
       <c r="I740" s="4" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="J740" s="26">
-        <v>8.7233796296296295E-2</v>
+        <v>8.7245370370370376E-2</v>
       </c>
     </row>
     <row r="741" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -27844,16 +27978,16 @@
         <v>805</v>
       </c>
       <c r="G741" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H741" s="4" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="I741" s="4" t="s">
         <v>191</v>
       </c>
       <c r="J741" s="26">
-        <v>9.2361111111111116E-2</v>
+        <v>9.2337962962962969E-2</v>
       </c>
     </row>
     <row r="742" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -27876,16 +28010,16 @@
         <v>805</v>
       </c>
       <c r="G742" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H742" s="4" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="I742" s="4" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="J742" s="26">
-        <v>9.6701388888888892E-2</v>
+        <v>9.6747685185185187E-2</v>
       </c>
     </row>
     <row r="743" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
@@ -27908,7 +28042,7 @@
         <v>805</v>
       </c>
       <c r="G743" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H743" s="4" t="s">
         <v>330</v>
@@ -27917,7 +28051,519 @@
         <v>111</v>
       </c>
       <c r="J743" s="26">
-        <v>0.10703703703703704</v>
+        <v>0.10702546296296296</v>
+      </c>
+    </row>
+    <row r="744" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A744" s="31">
+        <v>149</v>
+      </c>
+      <c r="B744" s="31">
+        <v>2026</v>
+      </c>
+      <c r="C744" s="31">
+        <v>10</v>
+      </c>
+      <c r="D744" s="31">
+        <v>17</v>
+      </c>
+      <c r="E744" s="31" t="s">
+        <v>984</v>
+      </c>
+      <c r="F744" s="32" t="s">
+        <v>985</v>
+      </c>
+      <c r="G744" s="32" t="s">
+        <v>986</v>
+      </c>
+      <c r="H744" s="32" t="s">
+        <v>987</v>
+      </c>
+      <c r="I744" s="32" t="s">
+        <v>988</v>
+      </c>
+      <c r="J744" s="33">
+        <v>6.7129629629629631E-3</v>
+      </c>
+    </row>
+    <row r="745" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A745" s="31">
+        <v>149</v>
+      </c>
+      <c r="B745" s="31">
+        <v>2026</v>
+      </c>
+      <c r="C745" s="31">
+        <v>10</v>
+      </c>
+      <c r="D745" s="31">
+        <v>17</v>
+      </c>
+      <c r="E745" s="31" t="s">
+        <v>984</v>
+      </c>
+      <c r="F745" s="32" t="s">
+        <v>985</v>
+      </c>
+      <c r="G745" s="32" t="s">
+        <v>986</v>
+      </c>
+      <c r="H745" s="32" t="s">
+        <v>989</v>
+      </c>
+      <c r="I745" s="32" t="s">
+        <v>990</v>
+      </c>
+      <c r="J745" s="33">
+        <v>1.4293981481481482E-2</v>
+      </c>
+    </row>
+    <row r="746" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A746" s="31">
+        <v>149</v>
+      </c>
+      <c r="B746" s="31">
+        <v>2026</v>
+      </c>
+      <c r="C746" s="31">
+        <v>10</v>
+      </c>
+      <c r="D746" s="31">
+        <v>17</v>
+      </c>
+      <c r="E746" s="31" t="s">
+        <v>984</v>
+      </c>
+      <c r="F746" s="32" t="s">
+        <v>985</v>
+      </c>
+      <c r="G746" s="32" t="s">
+        <v>986</v>
+      </c>
+      <c r="H746" s="32" t="s">
+        <v>991</v>
+      </c>
+      <c r="I746" s="32" t="s">
+        <v>990</v>
+      </c>
+      <c r="J746" s="33">
+        <v>1.8576388888888889E-2</v>
+      </c>
+    </row>
+    <row r="747" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A747" s="31">
+        <v>149</v>
+      </c>
+      <c r="B747" s="31">
+        <v>2026</v>
+      </c>
+      <c r="C747" s="31">
+        <v>10</v>
+      </c>
+      <c r="D747" s="31">
+        <v>17</v>
+      </c>
+      <c r="E747" s="31" t="s">
+        <v>984</v>
+      </c>
+      <c r="F747" s="32" t="s">
+        <v>985</v>
+      </c>
+      <c r="G747" s="32" t="s">
+        <v>986</v>
+      </c>
+      <c r="H747" s="32" t="s">
+        <v>993</v>
+      </c>
+      <c r="I747" s="32" t="s">
+        <v>992</v>
+      </c>
+      <c r="J747" s="33">
+        <v>2.4502314814814814E-2</v>
+      </c>
+    </row>
+    <row r="748" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A748" s="31">
+        <v>149</v>
+      </c>
+      <c r="B748" s="31">
+        <v>2026</v>
+      </c>
+      <c r="C748" s="31">
+        <v>10</v>
+      </c>
+      <c r="D748" s="31">
+        <v>17</v>
+      </c>
+      <c r="E748" s="31" t="s">
+        <v>984</v>
+      </c>
+      <c r="F748" s="32" t="s">
+        <v>985</v>
+      </c>
+      <c r="G748" s="32" t="s">
+        <v>986</v>
+      </c>
+      <c r="H748" s="32" t="s">
+        <v>995</v>
+      </c>
+      <c r="I748" s="32" t="s">
+        <v>994</v>
+      </c>
+      <c r="J748" s="33">
+        <v>3.0555555555555555E-2</v>
+      </c>
+    </row>
+    <row r="749" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A749" s="31">
+        <v>149</v>
+      </c>
+      <c r="B749" s="31">
+        <v>2026</v>
+      </c>
+      <c r="C749" s="31">
+        <v>10</v>
+      </c>
+      <c r="D749" s="31">
+        <v>17</v>
+      </c>
+      <c r="E749" s="31" t="s">
+        <v>984</v>
+      </c>
+      <c r="F749" s="32" t="s">
+        <v>985</v>
+      </c>
+      <c r="G749" s="32" t="s">
+        <v>986</v>
+      </c>
+      <c r="H749" s="32" t="s">
+        <v>997</v>
+      </c>
+      <c r="I749" s="32" t="s">
+        <v>996</v>
+      </c>
+      <c r="J749" s="33">
+        <v>3.5000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="750" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A750" s="31">
+        <v>149</v>
+      </c>
+      <c r="B750" s="31">
+        <v>2026</v>
+      </c>
+      <c r="C750" s="31">
+        <v>10</v>
+      </c>
+      <c r="D750" s="31">
+        <v>17</v>
+      </c>
+      <c r="E750" s="31" t="s">
+        <v>984</v>
+      </c>
+      <c r="F750" s="32" t="s">
+        <v>985</v>
+      </c>
+      <c r="G750" s="32" t="s">
+        <v>986</v>
+      </c>
+      <c r="H750" s="32" t="s">
+        <v>998</v>
+      </c>
+      <c r="I750" s="32" t="s">
+        <v>467</v>
+      </c>
+      <c r="J750" s="33">
+        <v>3.9537037037037037E-2</v>
+      </c>
+    </row>
+    <row r="751" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A751" s="31">
+        <v>149</v>
+      </c>
+      <c r="B751" s="31">
+        <v>2026</v>
+      </c>
+      <c r="C751" s="31">
+        <v>10</v>
+      </c>
+      <c r="D751" s="31">
+        <v>17</v>
+      </c>
+      <c r="E751" s="31" t="s">
+        <v>984</v>
+      </c>
+      <c r="F751" s="32" t="s">
+        <v>985</v>
+      </c>
+      <c r="G751" s="32" t="s">
+        <v>986</v>
+      </c>
+      <c r="H751" s="32" t="s">
+        <v>999</v>
+      </c>
+      <c r="I751" s="32" t="s">
+        <v>1000</v>
+      </c>
+      <c r="J751" s="33">
+        <v>4.490740740740741E-2</v>
+      </c>
+    </row>
+    <row r="752" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A752" s="31">
+        <v>149</v>
+      </c>
+      <c r="B752" s="31">
+        <v>2026</v>
+      </c>
+      <c r="C752" s="31">
+        <v>10</v>
+      </c>
+      <c r="D752" s="31">
+        <v>17</v>
+      </c>
+      <c r="E752" s="31" t="s">
+        <v>984</v>
+      </c>
+      <c r="F752" s="32" t="s">
+        <v>985</v>
+      </c>
+      <c r="G752" s="32" t="s">
+        <v>986</v>
+      </c>
+      <c r="H752" s="32" t="s">
+        <v>1001</v>
+      </c>
+      <c r="I752" s="32" t="s">
+        <v>1000</v>
+      </c>
+      <c r="J752" s="33">
+        <v>4.8252314814814817E-2</v>
+      </c>
+    </row>
+    <row r="753" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A753" s="31">
+        <v>149</v>
+      </c>
+      <c r="B753" s="31">
+        <v>2026</v>
+      </c>
+      <c r="C753" s="31">
+        <v>10</v>
+      </c>
+      <c r="D753" s="31">
+        <v>17</v>
+      </c>
+      <c r="E753" s="31" t="s">
+        <v>984</v>
+      </c>
+      <c r="F753" s="32" t="s">
+        <v>985</v>
+      </c>
+      <c r="G753" s="32" t="s">
+        <v>986</v>
+      </c>
+      <c r="H753" s="32" t="s">
+        <v>1002</v>
+      </c>
+      <c r="I753" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="J753" s="33">
+        <v>5.347222222222222E-2</v>
+      </c>
+    </row>
+    <row r="754" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A754" s="31">
+        <v>149</v>
+      </c>
+      <c r="B754" s="31">
+        <v>2026</v>
+      </c>
+      <c r="C754" s="31">
+        <v>10</v>
+      </c>
+      <c r="D754" s="31">
+        <v>17</v>
+      </c>
+      <c r="E754" s="31" t="s">
+        <v>984</v>
+      </c>
+      <c r="F754" s="32" t="s">
+        <v>985</v>
+      </c>
+      <c r="G754" s="32" t="s">
+        <v>986</v>
+      </c>
+      <c r="H754" s="32" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I754" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="J754" s="33">
+        <v>5.7152777777777775E-2</v>
+      </c>
+    </row>
+    <row r="755" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A755" s="31">
+        <v>149</v>
+      </c>
+      <c r="B755" s="31">
+        <v>2026</v>
+      </c>
+      <c r="C755" s="31">
+        <v>10</v>
+      </c>
+      <c r="D755" s="31">
+        <v>17</v>
+      </c>
+      <c r="E755" s="31" t="s">
+        <v>984</v>
+      </c>
+      <c r="F755" s="32" t="s">
+        <v>985</v>
+      </c>
+      <c r="G755" s="32" t="s">
+        <v>986</v>
+      </c>
+      <c r="H755" s="32" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I755" s="32" t="s">
+        <v>1004</v>
+      </c>
+      <c r="J755" s="33">
+        <v>6.2847222222222221E-2</v>
+      </c>
+    </row>
+    <row r="756" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A756" s="31">
+        <v>149</v>
+      </c>
+      <c r="B756" s="31">
+        <v>2026</v>
+      </c>
+      <c r="C756" s="31">
+        <v>10</v>
+      </c>
+      <c r="D756" s="31">
+        <v>17</v>
+      </c>
+      <c r="E756" s="31" t="s">
+        <v>984</v>
+      </c>
+      <c r="F756" s="32" t="s">
+        <v>985</v>
+      </c>
+      <c r="G756" s="32" t="s">
+        <v>986</v>
+      </c>
+      <c r="H756" s="32" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I756" s="32" t="s">
+        <v>1007</v>
+      </c>
+      <c r="J756" s="33">
+        <v>6.7245370370370372E-2</v>
+      </c>
+    </row>
+    <row r="757" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A757" s="31">
+        <v>149</v>
+      </c>
+      <c r="B757" s="31">
+        <v>2026</v>
+      </c>
+      <c r="C757" s="31">
+        <v>10</v>
+      </c>
+      <c r="D757" s="31">
+        <v>17</v>
+      </c>
+      <c r="E757" s="31" t="s">
+        <v>984</v>
+      </c>
+      <c r="F757" s="32" t="s">
+        <v>985</v>
+      </c>
+      <c r="G757" s="32" t="s">
+        <v>986</v>
+      </c>
+      <c r="H757" s="32" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I757" s="32" t="s">
+        <v>1009</v>
+      </c>
+      <c r="J757" s="33">
+        <v>7.0972222222222228E-2</v>
+      </c>
+    </row>
+    <row r="758" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A758" s="31">
+        <v>149</v>
+      </c>
+      <c r="B758" s="31">
+        <v>2026</v>
+      </c>
+      <c r="C758" s="31">
+        <v>10</v>
+      </c>
+      <c r="D758" s="31">
+        <v>17</v>
+      </c>
+      <c r="E758" s="31" t="s">
+        <v>984</v>
+      </c>
+      <c r="F758" s="32" t="s">
+        <v>985</v>
+      </c>
+      <c r="G758" s="32" t="s">
+        <v>986</v>
+      </c>
+      <c r="H758" s="32" t="s">
+        <v>1010</v>
+      </c>
+      <c r="I758" s="32" t="s">
+        <v>1011</v>
+      </c>
+      <c r="J758" s="33">
+        <v>7.4988425925925931E-2</v>
+      </c>
+    </row>
+    <row r="759" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A759" s="31">
+        <v>149</v>
+      </c>
+      <c r="B759" s="31">
+        <v>2026</v>
+      </c>
+      <c r="C759" s="31">
+        <v>10</v>
+      </c>
+      <c r="D759" s="31">
+        <v>17</v>
+      </c>
+      <c r="E759" s="31" t="s">
+        <v>984</v>
+      </c>
+      <c r="F759" s="32" t="s">
+        <v>985</v>
+      </c>
+      <c r="G759" s="32" t="s">
+        <v>986</v>
+      </c>
+      <c r="H759" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="I759" s="32" t="s">
+        <v>1012</v>
+      </c>
+      <c r="J759" s="33">
+        <v>8.037037037037037E-2</v>
       </c>
     </row>
   </sheetData>

--- a/songs_data.xlsx
+++ b/songs_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y\Desktop\Nagi Live Archives\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DFD4C5E-5733-4E88-A210-1E76C0BCAF76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{383391ED-4147-4FBC-AB9C-CBB0D10DFE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{90EDF358-D884-4DF4-A049-DD2596755BAC}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3908" uniqueCount="1013">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3908" uniqueCount="1012">
   <si>
     <t>配信タイトル</t>
     <rPh sb="0" eb="2">
@@ -3669,10 +3669,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>チャイナアドバイス(おじさんver)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ルーキー</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -3712,11 +3708,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>中島みゆき</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>イザナギ・エルヴァ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チャイナアドバイス</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -28083,7 +28079,7 @@
         <v>988</v>
       </c>
       <c r="J744" s="33">
-        <v>6.7129629629629631E-3</v>
+        <v>6.6782407407407407E-3</v>
       </c>
     </row>
     <row r="745" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
@@ -28115,7 +28111,7 @@
         <v>990</v>
       </c>
       <c r="J745" s="33">
-        <v>1.4293981481481482E-2</v>
+        <v>1.4340277777777778E-2</v>
       </c>
     </row>
     <row r="746" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
@@ -28147,7 +28143,7 @@
         <v>990</v>
       </c>
       <c r="J746" s="33">
-        <v>1.8576388888888889E-2</v>
+        <v>1.8587962962962962E-2</v>
       </c>
     </row>
     <row r="747" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
@@ -28179,7 +28175,7 @@
         <v>992</v>
       </c>
       <c r="J747" s="33">
-        <v>2.4502314814814814E-2</v>
+        <v>2.462962962962963E-2</v>
       </c>
     </row>
     <row r="748" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
@@ -28211,7 +28207,7 @@
         <v>994</v>
       </c>
       <c r="J748" s="33">
-        <v>3.0555555555555555E-2</v>
+        <v>3.0381944444444444E-2</v>
       </c>
     </row>
     <row r="749" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
@@ -28243,7 +28239,7 @@
         <v>996</v>
       </c>
       <c r="J749" s="33">
-        <v>3.5000000000000003E-2</v>
+        <v>3.4988425925925923E-2</v>
       </c>
     </row>
     <row r="750" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
@@ -28275,7 +28271,7 @@
         <v>467</v>
       </c>
       <c r="J750" s="33">
-        <v>3.9537037037037037E-2</v>
+        <v>3.9606481481481479E-2</v>
       </c>
     </row>
     <row r="751" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
@@ -28307,7 +28303,7 @@
         <v>1000</v>
       </c>
       <c r="J751" s="33">
-        <v>4.490740740740741E-2</v>
+        <v>4.4895833333333336E-2</v>
       </c>
     </row>
     <row r="752" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
@@ -28333,13 +28329,13 @@
         <v>986</v>
       </c>
       <c r="H752" s="32" t="s">
-        <v>1001</v>
+        <v>1011</v>
       </c>
       <c r="I752" s="32" t="s">
         <v>1000</v>
       </c>
       <c r="J752" s="33">
-        <v>4.8252314814814817E-2</v>
+        <v>4.8240740740740744E-2</v>
       </c>
     </row>
     <row r="753" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
@@ -28365,13 +28361,13 @@
         <v>986</v>
       </c>
       <c r="H753" s="32" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="I753" s="32" t="s">
         <v>234</v>
       </c>
       <c r="J753" s="33">
-        <v>5.347222222222222E-2</v>
+        <v>5.3414351851851852E-2</v>
       </c>
     </row>
     <row r="754" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
@@ -28397,13 +28393,13 @@
         <v>986</v>
       </c>
       <c r="H754" s="32" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="I754" s="32" t="s">
         <v>234</v>
       </c>
       <c r="J754" s="33">
-        <v>5.7152777777777775E-2</v>
+        <v>5.7013888888888892E-2</v>
       </c>
     </row>
     <row r="755" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
@@ -28429,10 +28425,10 @@
         <v>986</v>
       </c>
       <c r="H755" s="32" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="I755" s="32" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="J755" s="33">
         <v>6.2847222222222221E-2</v>
@@ -28461,13 +28457,13 @@
         <v>986</v>
       </c>
       <c r="H756" s="32" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I756" s="32" t="s">
         <v>1006</v>
       </c>
-      <c r="I756" s="32" t="s">
-        <v>1007</v>
-      </c>
       <c r="J756" s="33">
-        <v>6.7245370370370372E-2</v>
+        <v>6.7534722222222218E-2</v>
       </c>
     </row>
     <row r="757" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
@@ -28493,13 +28489,13 @@
         <v>986</v>
       </c>
       <c r="H757" s="32" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I757" s="32" t="s">
         <v>1008</v>
       </c>
-      <c r="I757" s="32" t="s">
-        <v>1009</v>
-      </c>
       <c r="J757" s="33">
-        <v>7.0972222222222228E-2</v>
+        <v>7.0960648148148148E-2</v>
       </c>
     </row>
     <row r="758" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
@@ -28525,13 +28521,13 @@
         <v>986</v>
       </c>
       <c r="H758" s="32" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="I758" s="32" t="s">
-        <v>1011</v>
+        <v>257</v>
       </c>
       <c r="J758" s="33">
-        <v>7.4988425925925931E-2</v>
+        <v>7.497685185185185E-2</v>
       </c>
     </row>
     <row r="759" spans="1:10" s="32" customFormat="1" x14ac:dyDescent="0.45">
@@ -28560,10 +28556,10 @@
         <v>204</v>
       </c>
       <c r="I759" s="32" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="J759" s="33">
-        <v>8.037037037037037E-2</v>
+        <v>8.0335648148148142E-2</v>
       </c>
     </row>
   </sheetData>

--- a/songs_data.xlsx
+++ b/songs_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y\Desktop\Nagi Live Archives\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEBAB926-22FF-4ECD-AF59-D5B92E49B880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519CBA71-3649-40B8-9838-360B87E5F742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{90EDF358-D884-4DF4-A049-DD2596755BAC}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3908" uniqueCount="1012">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3958" uniqueCount="1034">
   <si>
     <t>配信タイトル</t>
     <rPh sb="0" eb="2">
@@ -3714,6 +3714,97 @@
   </si>
   <si>
     <t>待夢</t>
+  </si>
+  <si>
+    <t>ライブ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【実写歌枠】弾き語りと邦ロック！同接50人&amp;高評価100目標！【イザナギ・エルヴァ】</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.youtube.com/live/zrWMRylNO9A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヨゾラノ流星群</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>神聖かまってちゃん</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>できっこないを やらなくちゃ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サンボマスター</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Boy</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>踊ってばかりの国</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アドベンチャー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サカナクション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目が明く藍色</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GEZAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>待夢</t>
+    <rPh sb="0" eb="1">
+      <t>マ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>唯一無二</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イザナギ・エルヴァ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スプートニク</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>THE 2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>孤独の太陽</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>monobright</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>逆光</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ado</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -4259,7 +4350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DE68349-627D-443B-8777-75196758F221}">
-  <dimension ref="A1:J759"/>
+  <dimension ref="A1:J769"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.19921875" style="1" customWidth="1"/>
@@ -28562,6 +28653,326 @@
         <v>8.0335648148148142E-2</v>
       </c>
     </row>
+    <row r="760" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A760" s="5">
+        <v>150</v>
+      </c>
+      <c r="B760" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C760" s="5">
+        <v>10</v>
+      </c>
+      <c r="D760" s="5">
+        <v>25</v>
+      </c>
+      <c r="E760" s="5" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F760" s="6" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G760" s="6" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H760" s="6" t="s">
+        <v>1015</v>
+      </c>
+      <c r="I760" s="6" t="s">
+        <v>1016</v>
+      </c>
+      <c r="J760" s="25">
+        <v>3.5532407407407409E-3</v>
+      </c>
+    </row>
+    <row r="761" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A761" s="5">
+        <v>150</v>
+      </c>
+      <c r="B761" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C761" s="5">
+        <v>10</v>
+      </c>
+      <c r="D761" s="5">
+        <v>25</v>
+      </c>
+      <c r="E761" s="5" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F761" s="6" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G761" s="6" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H761" s="6" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I761" s="6" t="s">
+        <v>1018</v>
+      </c>
+      <c r="J761" s="25">
+        <v>6.851851851851852E-3</v>
+      </c>
+    </row>
+    <row r="762" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A762" s="5">
+        <v>150</v>
+      </c>
+      <c r="B762" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C762" s="5">
+        <v>10</v>
+      </c>
+      <c r="D762" s="5">
+        <v>25</v>
+      </c>
+      <c r="E762" s="5" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F762" s="6" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G762" s="6" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H762" s="6" t="s">
+        <v>1019</v>
+      </c>
+      <c r="I762" s="6" t="s">
+        <v>1020</v>
+      </c>
+      <c r="J762" s="25">
+        <v>1.105324074074074E-2</v>
+      </c>
+    </row>
+    <row r="763" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A763" s="5">
+        <v>150</v>
+      </c>
+      <c r="B763" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C763" s="5">
+        <v>10</v>
+      </c>
+      <c r="D763" s="5">
+        <v>25</v>
+      </c>
+      <c r="E763" s="5" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F763" s="6" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G763" s="6" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H763" s="6" t="s">
+        <v>1021</v>
+      </c>
+      <c r="I763" s="6" t="s">
+        <v>1022</v>
+      </c>
+      <c r="J763" s="25">
+        <v>1.6527777777777777E-2</v>
+      </c>
+    </row>
+    <row r="764" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A764" s="5">
+        <v>150</v>
+      </c>
+      <c r="B764" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C764" s="5">
+        <v>10</v>
+      </c>
+      <c r="D764" s="5">
+        <v>25</v>
+      </c>
+      <c r="E764" s="5" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F764" s="6" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G764" s="6" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H764" s="6" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I764" s="6" t="s">
+        <v>1022</v>
+      </c>
+      <c r="J764" s="25">
+        <v>2.2488425925925926E-2</v>
+      </c>
+    </row>
+    <row r="765" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A765" s="5">
+        <v>150</v>
+      </c>
+      <c r="B765" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C765" s="5">
+        <v>10</v>
+      </c>
+      <c r="D765" s="5">
+        <v>25</v>
+      </c>
+      <c r="E765" s="5" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F765" s="6" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G765" s="6" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H765" s="6" t="s">
+        <v>1025</v>
+      </c>
+      <c r="I765" s="6" t="s">
+        <v>1024</v>
+      </c>
+      <c r="J765" s="25">
+        <v>2.8969907407407406E-2</v>
+      </c>
+    </row>
+    <row r="766" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A766" s="5">
+        <v>150</v>
+      </c>
+      <c r="B766" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C766" s="5">
+        <v>10</v>
+      </c>
+      <c r="D766" s="5">
+        <v>25</v>
+      </c>
+      <c r="E766" s="5" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F766" s="6" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G766" s="6" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H766" s="6" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I766" s="6" t="s">
+        <v>1027</v>
+      </c>
+      <c r="J766" s="25">
+        <v>3.335648148148148E-2</v>
+      </c>
+    </row>
+    <row r="767" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A767" s="5">
+        <v>150</v>
+      </c>
+      <c r="B767" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C767" s="5">
+        <v>10</v>
+      </c>
+      <c r="D767" s="5">
+        <v>25</v>
+      </c>
+      <c r="E767" s="5" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F767" s="6" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G767" s="6" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H767" s="6" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I767" s="6" t="s">
+        <v>1029</v>
+      </c>
+      <c r="J767" s="25">
+        <v>3.9560185185185184E-2</v>
+      </c>
+    </row>
+    <row r="768" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A768" s="5">
+        <v>150</v>
+      </c>
+      <c r="B768" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C768" s="5">
+        <v>10</v>
+      </c>
+      <c r="D768" s="5">
+        <v>25</v>
+      </c>
+      <c r="E768" s="5" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F768" s="6" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G768" s="6" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H768" s="6" t="s">
+        <v>1030</v>
+      </c>
+      <c r="I768" s="6" t="s">
+        <v>1031</v>
+      </c>
+      <c r="J768" s="25">
+        <v>4.3136574074074077E-2</v>
+      </c>
+    </row>
+    <row r="769" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A769" s="5">
+        <v>150</v>
+      </c>
+      <c r="B769" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C769" s="5">
+        <v>10</v>
+      </c>
+      <c r="D769" s="5">
+        <v>25</v>
+      </c>
+      <c r="E769" s="5" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F769" s="6" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G769" s="6" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H769" s="6" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I769" s="6" t="s">
+        <v>1033</v>
+      </c>
+      <c r="J769" s="25">
+        <v>4.7546296296296295E-2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
